--- a/output/group_consolidation.xlsx
+++ b/output/group_consolidation.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="274">
   <si>
     <t xml:space="preserve">Illustrative Group</t>
   </si>
@@ -160,7 +160,7 @@
     <t xml:space="preserve">How each entity is treated under IFRS</t>
   </si>
   <si>
-    <t xml:space="preserve">Group structure and accounting basis</t>
+    <t xml:space="preserve">Parent incorporated in the UAE; consolidated financial statements prepared under IFRS Accounting Standards</t>
   </si>
   <si>
     <t xml:space="preserve">Entity</t>
@@ -181,19 +181,19 @@
     <t xml:space="preserve">How it is treated in this workbook</t>
   </si>
   <si>
-    <t xml:space="preserve">Parent Co.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parent and reporting entity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFRS 10, IAS 1</t>
+    <t xml:space="preserve">Parent Co. (UAE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parent and reporting entity, incorporated in the UAE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IFRS 10, IAS 1, IAS 21</t>
   </si>
   <si>
     <t xml:space="preserve">Prepares the consolidated statements</t>
   </si>
   <si>
-    <t xml:space="preserve">Combined in full. Functional and presentation currency USD.</t>
+    <t xml:space="preserve">The UAE requires companies to prepare their financial statements under IFRS, so the group reports under IFRS. Combined in full. Functional and presentation currency USD: most sales, pricing and financing are in USD (IAS 21.9), and the UAE dirham is pegged to it.</t>
   </si>
   <si>
     <t xml:space="preserve">Subsidiary One (US)</t>
@@ -223,7 +223,16 @@
     <t xml:space="preserve">Full consolidation (acquisition method) with NCI</t>
   </si>
   <si>
-    <t xml:space="preserve">Translated from EUR to USD first. Combined line by line. The investment is eliminated against share capital and pre-acquisition reserves; any excess of cost is goodwill. The other 20% is a non-controlling interest, shown in equity, with its share of profit and translation differences.</t>
+    <t xml:space="preserve">Translated from EUR to USD first. Combined line by line. The investment is eliminated against share capital and pre-acquisition reserves; any excess of cost is goodwill. Goodwill is held in EUR and retranslated at the closing rate. The other 20% is a non-controlling interest, shown in equity, with its share of profit and translation differences.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subsidiary Three (UK)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subsidiary: 70% held by Subsidiary One (US), so the parent controls it indirectly (sub-subsidiary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Translated from GBP to USD first. Combined line by line. The investment is eliminated against share capital and pre-acquisition reserves; any excess of cost is goodwill. Group effective interest is 70%; goodwill and NCI are measured on that interest. Goodwill is held in GBP and retranslated at the closing rate. The other 30% is a non-controlling interest, shown in equity, with its share of profit and translation differences.</t>
   </si>
   <si>
     <t xml:space="preserve">Associate One (UAE)</t>
@@ -271,7 +280,7 @@
     <t xml:space="preserve">IFRS 10.6-7, B35</t>
   </si>
   <si>
-    <t xml:space="preserve">An investor controls an investee when it has power over it, is exposed to variable returns from it and can use its power to affect those returns. Both subsidiaries are controlled through a majority of the voting rights, so they are consolidated from the date control was obtained.</t>
+    <t xml:space="preserve">An investor controls an investee when it has power over it, is exposed to variable returns from it and can use its power to affect those returns. Subsidiaries One and Two are controlled directly through a majority of the voting rights, and Subsidiary Three through Subsidiary One. Each is consolidated from the date control was obtained.</t>
   </si>
   <si>
     <t xml:space="preserve">2. Significant influence (associates)</t>
@@ -289,16 +298,16 @@
     <t xml:space="preserve">IFRS 10.B87, B92-B93; IAS 28.33-36</t>
   </si>
   <si>
-    <t xml:space="preserve">All entities use the group's IFRS accounting policies and a 31 December year end, so no alignment adjustments are needed. A different year end would need adjusting for significant transactions and may differ by no more than three months.</t>
+    <t xml:space="preserve">All entities use the group's IFRS accounting policies and a 31 December year end, so no alignment adjustments are needed. Entities in countries that do not use IFRS locally (such as the US) report to the group on IFRS policies. A different year end would need adjusting for significant transactions and may differ by no more than three months.</t>
   </si>
   <si>
     <t xml:space="preserve">4. Foreign currency translation</t>
   </si>
   <si>
-    <t xml:space="preserve">IAS 21.39-41, 21.44; IAS 28.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subsidiary Two (EUR) is translated into USD: assets and liabilities at the closing rate, income and expenses at the average rate (an approximation of transaction-date rates) and share capital at the historical rate. The difference goes to the translation reserve in other comprehensive income, and the NCI's share is allocated to NCI. Associate One reports in AED, which is pegged to the USD, so no exchange difference arises; for a floating currency it would also go to the translation reserve.</t>
+    <t xml:space="preserve">IAS 21.39-41, 21.44, 21.47; IAS 28.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subsidiary Two (EUR) is translated into USD: assets and liabilities at the closing rate, income and expenses at the average rate (an approximation of transaction-date rates) and share capital at the historical rate. The difference goes to the translation reserve in other comprehensive income, and the NCI's share is allocated to NCI. Subsidiary Three (GBP) is translated the same way, and its goodwill is treated as its own asset: held in GBP and retranslated at the closing rate, with the difference in the translation reserve. Associate One reports in AED, which is pegged to the USD, so no exchange difference arises; for a floating currency it would also go to the translation reserve.</t>
   </si>
   <si>
     <t xml:space="preserve">5. Combine line by line (subsidiaries only)</t>
@@ -328,7 +337,16 @@
     <t xml:space="preserve">NCI is measured at its proportionate share of the subsidiary's identifiable net assets (the IFRS 3 choice made here, so no goodwill is attributed to NCI). It is shown in equity, separately from the parent's equity, and receives its share of profit and of translation differences.</t>
   </si>
   <si>
-    <t xml:space="preserve">8. Intragroup transactions</t>
+    <t xml:space="preserve">8. Indirect holdings (sub-subsidiaries)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IFRS 10.B86, Appendix A; IFRS 3.19, 3.32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subsidiary Three is 70% owned by Subsidiary One, which the parent owns in full. Control passes down the chain, so Subsidiary Three is the parent's subsidiary and is consolidated in full. Goodwill and NCI use the group's effective interest (100% x 70% = 70%). If the holder were not wholly owned, its NCI's share of the cost of investment would be deducted from NCI, and NCI would also include the holder's NCI's indirect share of the sub-subsidiary.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. Intragroup transactions</t>
   </si>
   <si>
     <t xml:space="preserve">IFRS 10.B86(c)</t>
@@ -337,7 +355,7 @@
     <t xml:space="preserve">Intragroup balances, sales, purchases and unrealised profit in closing inventory are eliminated in full. The unrealised profit is charged to the selling entity; the seller is 100% owned, so NCI is not affected.</t>
   </si>
   <si>
-    <t xml:space="preserve">9. Equity method (associates)</t>
+    <t xml:space="preserve">10. Equity method (associates)</t>
   </si>
   <si>
     <t xml:space="preserve">IAS 28.10, 28.16</t>
@@ -346,7 +364,7 @@
     <t xml:space="preserve">An associate is not combined line by line. The investment is recognised at cost and then increased or decreased by the group's share of the associate's profit or loss after acquisition. Dividends received reduce the carrying amount instead of being income, so the parent's dividend income is reversed.</t>
   </si>
   <si>
-    <t xml:space="preserve">10. Goodwill on associates</t>
+    <t xml:space="preserve">11. Goodwill on associates</t>
   </si>
   <si>
     <t xml:space="preserve">IAS 28.32, 28.42</t>
@@ -355,7 +373,7 @@
     <t xml:space="preserve">The excess of cost over the group's share of the associate's net assets is included in the carrying amount of the investment. It is not shown separately, not amortised and not tested for impairment on its own.</t>
   </si>
   <si>
-    <t xml:space="preserve">11. Transactions with associates</t>
+    <t xml:space="preserve">12. Transactions with associates</t>
   </si>
   <si>
     <t xml:space="preserve">IAS 28.28-29</t>
@@ -364,7 +382,7 @@
     <t xml:space="preserve">Only the group's share of unrealised profit on sales between the group and an associate is eliminated. For a sale to the associate (downstream) it reduces the investment; for a purchase from the associate (upstream) it reduces group inventory. Balances with associates are not eliminated, because associates are outside the group.</t>
   </si>
   <si>
-    <t xml:space="preserve">12. Impairment of associates</t>
+    <t xml:space="preserve">13. Impairment of associates</t>
   </si>
   <si>
     <t xml:space="preserve">IAS 28.40-43; IAS 36</t>
@@ -373,7 +391,7 @@
     <t xml:space="preserve">After applying the equity method, the group checks for objective evidence of impairment. If there is, the whole carrying amount is tested as a single asset under IAS 36 and any loss reduces the investment. Associate Two carries an impairment loss.</t>
   </si>
   <si>
-    <t xml:space="preserve">13. Losses of associates</t>
+    <t xml:space="preserve">14. Losses of associates</t>
   </si>
   <si>
     <t xml:space="preserve">IAS 28.38-39</t>
@@ -382,7 +400,7 @@
     <t xml:space="preserve">If the group's share of losses equals or exceeds its interest, it stops recognising further losses unless it has an obligation to fund them. Not triggered here.</t>
   </si>
   <si>
-    <t xml:space="preserve">14. Presentation</t>
+    <t xml:space="preserve">15. Presentation</t>
   </si>
   <si>
     <t xml:space="preserve">IAS 1.54(e), 1.82(c), 1.81B; IFRS 10.22</t>
@@ -391,7 +409,7 @@
     <t xml:space="preserve">Investments in associates and the share of their profit are separate line items. Profit and equity are split between owners of the parent and NCI.</t>
   </si>
   <si>
-    <t xml:space="preserve">15. Disclosure</t>
+    <t xml:space="preserve">16. Disclosure</t>
   </si>
   <si>
     <t xml:space="preserve">IFRS 12.21, B12-B14</t>
@@ -400,7 +418,7 @@
     <t xml:space="preserve">Summarised financial information for each material associate and a reconciliation to its carrying amount (shown on the Associates sheet).</t>
   </si>
   <si>
-    <t xml:space="preserve">16. IFRS 18 (from 2027)</t>
+    <t xml:space="preserve">17. IFRS 18 (from 2027)</t>
   </si>
   <si>
     <t xml:space="preserve">IFRS 18</t>
@@ -430,6 +448,9 @@
     <t xml:space="preserve">SUB2 (USD)</t>
   </si>
   <si>
+    <t xml:space="preserve">SUB3 (USD)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Aggregate</t>
   </si>
   <si>
@@ -490,6 +511,12 @@
     <t xml:space="preserve">NCI share of Subsidiary Two (Germany) post-acquisition reserves</t>
   </si>
   <si>
+    <t xml:space="preserve">Investment in Subsidiary Three (UK)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NCI share of Subsidiary Three (UK) post-acquisition reserves</t>
+  </si>
+  <si>
     <t xml:space="preserve">Intercompany balance: Parent owes Sub One for goods bought</t>
   </si>
   <si>
@@ -667,6 +694,15 @@
     <t xml:space="preserve">SUB2 USD</t>
   </si>
   <si>
+    <t xml:space="preserve">SUB3 local</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUB3 rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUB3 USD</t>
+  </si>
+  <si>
     <t xml:space="preserve">Assets and liabilities at closing rate, income and expenses at average rate, share capital at historical rate, opening retained earnings at the USD amount carried forward. The translation reserve balances the translated trial balance.</t>
   </si>
   <si>
@@ -682,6 +718,9 @@
     <t xml:space="preserve">SUB2 (EUR)</t>
   </si>
   <si>
+    <t xml:space="preserve">SUB3 (GBP)</t>
+  </si>
+  <si>
     <t xml:space="preserve">A</t>
   </si>
   <si>
@@ -700,15 +739,21 @@
     <t xml:space="preserve">Group structure, exchange rates and intercompany data</t>
   </si>
   <si>
-    <t xml:space="preserve">Investment cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pre-acq. retained earnings</t>
+    <t xml:space="preserve">Investment cost (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-acq. retained earnings (local)</t>
   </si>
   <si>
     <t xml:space="preserve">Opening RE (USD)</t>
   </si>
   <si>
+    <t xml:space="preserve">Held by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group effective interest</t>
+  </si>
+  <si>
     <t xml:space="preserve">PARENT</t>
   </si>
   <si>
@@ -719,6 +764,12 @@
   </si>
   <si>
     <t xml:space="preserve">EUR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUB3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GBP</t>
   </si>
   <si>
     <t xml:space="preserve">Closing</t>
@@ -966,7 +1017,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1096,6 +1147,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1389,8 +1444,8 @@
         <v>4</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">-(Consolidation!I21+Consolidation!I22)</f>
-        <v>22124</v>
+        <f aca="false">-(Consolidation!J21+Consolidation!J22)</f>
+        <v>24172</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1398,8 +1453,8 @@
         <v>5</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">-(Consolidation!I25+Consolidation!I26)</f>
-        <v>-13060</v>
+        <f aca="false">-(Consolidation!J25+Consolidation!J26)</f>
+        <v>-14340</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1408,7 +1463,7 @@
       </c>
       <c r="C8" s="8" t="n">
         <f aca="false">C6+C7</f>
-        <v>9064</v>
+        <v>9832</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1416,8 +1471,8 @@
         <v>7</v>
       </c>
       <c r="C9" s="6" t="n">
-        <f aca="false">-Consolidation!I27</f>
-        <v>-4922</v>
+        <f aca="false">-Consolidation!J27</f>
+        <v>-5306</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1426,7 +1481,7 @@
       </c>
       <c r="C10" s="8" t="n">
         <f aca="false">C8+C9</f>
-        <v>4142</v>
+        <v>4526</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1434,7 +1489,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="6" t="n">
-        <f aca="false">-Consolidation!I24</f>
+        <f aca="false">-Consolidation!J24</f>
         <v>259.718</v>
       </c>
     </row>
@@ -1443,7 +1498,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="6" t="n">
-        <f aca="false">-Consolidation!I23</f>
+        <f aca="false">-Consolidation!J23</f>
         <v>-0</v>
       </c>
     </row>
@@ -1452,8 +1507,8 @@
         <v>11</v>
       </c>
       <c r="C13" s="6" t="n">
-        <f aca="false">-Consolidation!I28</f>
-        <v>-372.7</v>
+        <f aca="false">-Consolidation!J28</f>
+        <v>-398.3</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1462,7 +1517,7 @@
       </c>
       <c r="C14" s="8" t="n">
         <f aca="false">SUM(C10:C13)</f>
-        <v>4029.018</v>
+        <v>4387.418</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1470,8 +1525,8 @@
         <v>13</v>
       </c>
       <c r="C15" s="6" t="n">
-        <f aca="false">-Consolidation!I29</f>
-        <v>-852.6</v>
+        <f aca="false">-Consolidation!J29</f>
+        <v>-942.2</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1480,7 +1535,7 @@
       </c>
       <c r="C16" s="9" t="n">
         <f aca="false">C14+C15</f>
-        <v>3176.418</v>
+        <v>3445.218</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1489,7 +1544,7 @@
       </c>
       <c r="C18" s="6" t="n">
         <f aca="false">C16-C19</f>
-        <v>3082.678</v>
+        <v>3270.838</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1497,8 +1552,8 @@
         <v>16</v>
       </c>
       <c r="C19" s="6" t="n">
-        <f aca="false">(1-Inputs!$E$7)*-SUM(Translation!I18:I25)+(1-Inputs!$E$8)*-SUM(Translation!L18:L25)</f>
-        <v>93.74</v>
+        <f aca="false">(1-Inputs!$J$7)*-SUM(Translation!I18:I25)+(1-Inputs!$J$8)*-SUM(Translation!L18:L25)+(1-Inputs!$J$9)*-SUM(Translation!O18:O25)</f>
+        <v>174.38</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1542,7 +1597,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1552,79 +1607,79 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">ROUND(ABS('Trial Balances'!E26)+ABS('Trial Balances'!F26)+ABS('Trial Balances'!G26),2)</f>
+        <f aca="false">ROUND(ABS('Trial Balances'!E26)+ABS('Trial Balances'!F26)+ABS('Trial Balances'!G26)+ABS('Trial Balances'!H26),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">ROUND(ABS(Eliminations!F44),2)</f>
+        <f aca="false">ROUND(ABS(Eliminations!F55),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="C8" s="6" t="n">
-        <f aca="false">ROUND(ABS(Consolidation!I30),2)</f>
+        <f aca="false">ROUND(ABS(Consolidation!J30),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="C9" s="6" t="n">
-        <f aca="false">ROUND(ABS(Consolidation!I8)+ABS(Consolidation!I15),2)</f>
+        <f aca="false">ROUND(ABS(Consolidation!J8)+ABS(Consolidation!J15),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="C10" s="6" t="n">
-        <f aca="false">ROUND(ABS(Consolidation!I22)+ABS(Consolidation!I26),2)</f>
+        <f aca="false">ROUND(ABS(Consolidation!J22)+ABS(Consolidation!J26),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="C11" s="6" t="n">
-        <f aca="false">ROUND(ABS(Consolidation!I11),2)</f>
+        <f aca="false">ROUND(ABS(Consolidation!J11),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="C12" s="6" t="n">
-        <f aca="false">ROUND(ABS(Consolidation!I23),2)</f>
+        <f aca="false">ROUND(ABS(Consolidation!J23),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="C13" s="6" t="n">
-        <f aca="false">ROUND(ABS(Consolidation!I12-Associates!F31),2)</f>
+        <f aca="false">ROUND(ABS(Consolidation!J12-Associates!F31),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="C14" s="6" t="n">
         <f aca="false">ROUND(ABS(Associates!F39),2)</f>
@@ -1633,7 +1688,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="C15" s="6" t="n">
         <f aca="false">ROUND(ABS('Consolidated BS'!C29),2)</f>
@@ -1642,7 +1697,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="7" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="C17" s="7" t="str">
         <f aca="false">IF(SUM(C6:C15)=0,"OK","ERROR")</f>
@@ -1699,8 +1754,8 @@
         <v>20</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">Consolidation!I13</f>
-        <v>500</v>
+        <f aca="false">Consolidation!J13</f>
+        <v>576.2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1708,8 +1763,8 @@
         <v>21</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">Consolidation!I10</f>
-        <v>10444</v>
+        <f aca="false">Consolidation!J10</f>
+        <v>11587</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1717,7 +1772,7 @@
         <v>22</v>
       </c>
       <c r="C8" s="6" t="n">
-        <f aca="false">Consolidation!I12</f>
+        <f aca="false">Consolidation!J12</f>
         <v>1838.563</v>
       </c>
     </row>
@@ -1727,7 +1782,7 @@
       </c>
       <c r="C9" s="8" t="n">
         <f aca="false">SUM(C6:C8)</f>
-        <v>12782.563</v>
+        <v>14001.763</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1735,8 +1790,8 @@
         <v>24</v>
       </c>
       <c r="C10" s="6" t="n">
-        <f aca="false">Consolidation!I9</f>
-        <v>2690</v>
+        <f aca="false">Consolidation!J9</f>
+        <v>2918.6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1744,8 +1799,8 @@
         <v>25</v>
       </c>
       <c r="C11" s="6" t="n">
-        <f aca="false">Consolidation!I7</f>
-        <v>3756</v>
+        <f aca="false">Consolidation!J7</f>
+        <v>4073.5</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1753,7 +1808,7 @@
         <v>26</v>
       </c>
       <c r="C12" s="6" t="n">
-        <f aca="false">Consolidation!I8</f>
+        <f aca="false">Consolidation!J8</f>
         <v>0</v>
       </c>
     </row>
@@ -1762,8 +1817,8 @@
         <v>27</v>
       </c>
       <c r="C13" s="6" t="n">
-        <f aca="false">Consolidation!I6</f>
-        <v>2363.69</v>
+        <f aca="false">Consolidation!J6</f>
+        <v>2566.89</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1772,7 +1827,7 @@
       </c>
       <c r="C14" s="8" t="n">
         <f aca="false">SUM(C10:C13)</f>
-        <v>8809.69</v>
+        <v>9558.99</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1781,7 +1836,7 @@
       </c>
       <c r="C15" s="9" t="n">
         <f aca="false">C9+C14</f>
-        <v>21592.253</v>
+        <v>23560.753</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1789,7 +1844,7 @@
         <v>30</v>
       </c>
       <c r="C17" s="6" t="n">
-        <f aca="false">-Consolidation!I17</f>
+        <f aca="false">-Consolidation!J17</f>
         <v>5000</v>
       </c>
     </row>
@@ -1798,8 +1853,8 @@
         <v>31</v>
       </c>
       <c r="C18" s="6" t="n">
-        <f aca="false">-Consolidation!I18+'Consolidated IS'!C18</f>
-        <v>6733.213</v>
+        <f aca="false">-Consolidation!J18+'Consolidated IS'!C18</f>
+        <v>7097.773</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1807,8 +1862,8 @@
         <v>32</v>
       </c>
       <c r="C19" s="6" t="n">
-        <f aca="false">-Consolidation!I19</f>
-        <v>-24.5600000000001</v>
+        <f aca="false">-Consolidation!J19</f>
+        <v>-15.0300000000001</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1817,7 +1872,7 @@
       </c>
       <c r="C20" s="8" t="n">
         <f aca="false">SUM(C17:C19)</f>
-        <v>11708.653</v>
+        <v>12082.743</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1825,8 +1880,8 @@
         <v>34</v>
       </c>
       <c r="C21" s="6" t="n">
-        <f aca="false">-Consolidation!I20+'Consolidated IS'!C19</f>
-        <v>399.6</v>
+        <f aca="false">-Consolidation!J20+'Consolidated IS'!C19</f>
+        <v>784.41</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1835,7 +1890,7 @@
       </c>
       <c r="C22" s="8" t="n">
         <f aca="false">C20+C21</f>
-        <v>12108.253</v>
+        <v>12867.153</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1843,8 +1898,8 @@
         <v>36</v>
       </c>
       <c r="C23" s="6" t="n">
-        <f aca="false">-Consolidation!I16</f>
-        <v>6648</v>
+        <f aca="false">-Consolidation!J16</f>
+        <v>7629</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1852,8 +1907,8 @@
         <v>37</v>
       </c>
       <c r="C24" s="6" t="n">
-        <f aca="false">-Consolidation!I14</f>
-        <v>2836</v>
+        <f aca="false">-Consolidation!J14</f>
+        <v>3064.6</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1861,7 +1916,7 @@
         <v>38</v>
       </c>
       <c r="C25" s="6" t="n">
-        <f aca="false">-Consolidation!I15</f>
+        <f aca="false">-Consolidation!J15</f>
         <v>-0</v>
       </c>
     </row>
@@ -1871,7 +1926,7 @@
       </c>
       <c r="C26" s="8" t="n">
         <f aca="false">SUM(C23:C25)</f>
-        <v>9484</v>
+        <v>10693.6</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1880,7 +1935,7 @@
       </c>
       <c r="C27" s="9" t="n">
         <f aca="false">C22+C26</f>
-        <v>21592.253</v>
+        <v>23560.753</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1908,7 +1963,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:G32"/>
+  <dimension ref="B1:G34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -1955,7 +2010,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="12" t="s">
         <v>50</v>
       </c>
@@ -1994,7 +2049,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="69" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="12" t="s">
         <v>60</v>
       </c>
@@ -2015,7 +2070,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="69" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="12" t="s">
         <v>65</v>
       </c>
@@ -2023,72 +2078,79 @@
         <v>66</v>
       </c>
       <c r="D9" s="15" t="n">
+        <f aca="false">Inputs!$E$9</f>
+        <v>0.7</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="69" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="15" t="n">
         <f aca="false">Associates!D8</f>
         <v>0.3</v>
       </c>
-      <c r="E9" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="69" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="12" t="s">
+      <c r="E10" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="F10" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="G10" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="69" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="15" t="n">
         <f aca="false">Associates!E8</f>
         <v>0.25</v>
       </c>
-      <c r="E10" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="2" t="s">
-        <v>74</v>
+      <c r="E11" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" s="16" t="s">
+      <c r="B14" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-    </row>
-    <row r="15" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="12" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
     </row>
     <row r="16" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="12" t="s">
@@ -2104,7 +2166,7 @@
       <c r="F16" s="18"/>
       <c r="G16" s="18"/>
     </row>
-    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="12" t="s">
         <v>84</v>
       </c>
@@ -2118,7 +2180,7 @@
       <c r="F17" s="18"/>
       <c r="G17" s="18"/>
     </row>
-    <row r="18" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="12" t="s">
         <v>87</v>
       </c>
@@ -2132,7 +2194,7 @@
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
     </row>
-    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="12" t="s">
         <v>90</v>
       </c>
@@ -2160,7 +2222,7 @@
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
     </row>
-    <row r="21" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="12" t="s">
         <v>96</v>
       </c>
@@ -2174,7 +2236,7 @@
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
     </row>
-    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="12" t="s">
         <v>99</v>
       </c>
@@ -2188,7 +2250,7 @@
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
     </row>
-    <row r="23" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="12" t="s">
         <v>102</v>
       </c>
@@ -2244,7 +2306,7 @@
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
     </row>
-    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="12" t="s">
         <v>114</v>
       </c>
@@ -2286,7 +2348,7 @@
       <c r="F29" s="18"/>
       <c r="G29" s="18"/>
     </row>
-    <row r="30" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="12" t="s">
         <v>123</v>
       </c>
@@ -2300,14 +2362,41 @@
       <c r="F30" s="18"/>
       <c r="G30" s="18"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="3" t="s">
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="12" t="s">
         <v>126</v>
       </c>
+      <c r="C31" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+    </row>
+    <row r="32" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="3" t="s">
+        <v>132</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="D14:G14"/>
+  <mergeCells count="18">
     <mergeCell ref="D15:G15"/>
     <mergeCell ref="D16:G16"/>
     <mergeCell ref="D17:G17"/>
@@ -2324,6 +2413,8 @@
     <mergeCell ref="D28:G28"/>
     <mergeCell ref="D29:G29"/>
     <mergeCell ref="D30:G30"/>
+    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="D32:G32"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2340,13 +2431,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:I30"/>
+  <dimension ref="B1:J30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="4" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="4" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2356,7 +2447,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2366,28 +2457,31 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>135</v>
+        <v>141</v>
+      </c>
+      <c r="J5" s="19" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2409,17 +2503,21 @@
         <f aca="false">Translation!L6</f>
         <v>432</v>
       </c>
-      <c r="G6" s="6" t="n">
-        <f aca="false">SUM(D6:F6)</f>
-        <v>2363.69</v>
-      </c>
-      <c r="H6" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$43,Eliminations!$D$6:$D$43,$B6)</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="21" t="n">
-        <f aca="false">G6+H6</f>
-        <v>2363.69</v>
+      <c r="G6" s="20" t="n">
+        <f aca="false">Translation!O6</f>
+        <v>203.2</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <f aca="false">SUM(D6:G6)</f>
+        <v>2566.89</v>
+      </c>
+      <c r="I6" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B6)</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="21" t="n">
+        <f aca="false">H6+I6</f>
+        <v>2566.89</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2441,17 +2539,21 @@
         <f aca="false">Translation!L7</f>
         <v>756</v>
       </c>
-      <c r="G7" s="6" t="n">
-        <f aca="false">SUM(D7:F7)</f>
-        <v>3756</v>
-      </c>
-      <c r="H7" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$43,Eliminations!$D$6:$D$43,$B7)</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="21" t="n">
-        <f aca="false">G7+H7</f>
-        <v>3756</v>
+      <c r="G7" s="20" t="n">
+        <f aca="false">Translation!O7</f>
+        <v>317.5</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <f aca="false">SUM(D7:G7)</f>
+        <v>4073.5</v>
+      </c>
+      <c r="I7" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B7)</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="21" t="n">
+        <f aca="false">H7+I7</f>
+        <v>4073.5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2459,7 +2561,7 @@
         <v>1150</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="D8" s="20" t="n">
         <f aca="false">Translation!F8</f>
@@ -2473,16 +2575,20 @@
         <f aca="false">Translation!L8</f>
         <v>0</v>
       </c>
-      <c r="G8" s="6" t="n">
-        <f aca="false">SUM(D8:F8)</f>
+      <c r="G8" s="20" t="n">
+        <f aca="false">Translation!O8</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <f aca="false">SUM(D8:G8)</f>
         <v>690</v>
       </c>
-      <c r="H8" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$43,Eliminations!$D$6:$D$43,$B8)</f>
+      <c r="I8" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B8)</f>
         <v>-690</v>
       </c>
-      <c r="I8" s="21" t="n">
-        <f aca="false">G8+H8</f>
+      <c r="J8" s="21" t="n">
+        <f aca="false">H8+I8</f>
         <v>0</v>
       </c>
     </row>
@@ -2505,17 +2611,21 @@
         <f aca="false">Translation!L9</f>
         <v>540</v>
       </c>
-      <c r="G9" s="6" t="n">
-        <f aca="false">SUM(D9:F9)</f>
-        <v>2740</v>
-      </c>
-      <c r="H9" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$43,Eliminations!$D$6:$D$43,$B9)</f>
+      <c r="G9" s="20" t="n">
+        <f aca="false">Translation!O9</f>
+        <v>228.6</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <f aca="false">SUM(D9:G9)</f>
+        <v>2968.6</v>
+      </c>
+      <c r="I9" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B9)</f>
         <v>-50</v>
       </c>
-      <c r="I9" s="21" t="n">
-        <f aca="false">G9+H9</f>
-        <v>2690</v>
+      <c r="J9" s="21" t="n">
+        <f aca="false">H9+I9</f>
+        <v>2918.6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2537,17 +2647,21 @@
         <f aca="false">Translation!L10</f>
         <v>1944</v>
       </c>
-      <c r="G10" s="6" t="n">
-        <f aca="false">SUM(D10:F10)</f>
-        <v>10444</v>
-      </c>
-      <c r="H10" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$43,Eliminations!$D$6:$D$43,$B10)</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="21" t="n">
-        <f aca="false">G10+H10</f>
-        <v>10444</v>
+      <c r="G10" s="20" t="n">
+        <f aca="false">Translation!O10</f>
+        <v>1143</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <f aca="false">SUM(D10:G10)</f>
+        <v>11587</v>
+      </c>
+      <c r="I10" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B10)</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="21" t="n">
+        <f aca="false">H10+I10</f>
+        <v>11587</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2555,7 +2669,7 @@
         <v>1600</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="D11" s="20" t="n">
         <f aca="false">Translation!F11</f>
@@ -2563,22 +2677,26 @@
       </c>
       <c r="E11" s="20" t="n">
         <f aca="false">Translation!I11</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F11" s="20" t="n">
         <f aca="false">Translation!L11</f>
         <v>0</v>
       </c>
-      <c r="G11" s="6" t="n">
-        <f aca="false">SUM(D11:F11)</f>
-        <v>3580</v>
-      </c>
-      <c r="H11" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$43,Eliminations!$D$6:$D$43,$B11)</f>
-        <v>-3580</v>
-      </c>
-      <c r="I11" s="21" t="n">
-        <f aca="false">G11+H11</f>
+      <c r="G11" s="20" t="n">
+        <f aca="false">Translation!O11</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <f aca="false">SUM(D11:G11)</f>
+        <v>4180</v>
+      </c>
+      <c r="I11" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B11)</f>
+        <v>-4180</v>
+      </c>
+      <c r="J11" s="21" t="n">
+        <f aca="false">H11+I11</f>
         <v>0</v>
       </c>
     </row>
@@ -2587,7 +2705,7 @@
         <v>1650</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="D12" s="20" t="n">
         <f aca="false">Translation!F12</f>
@@ -2601,16 +2719,20 @@
         <f aca="false">Translation!L12</f>
         <v>0</v>
       </c>
-      <c r="G12" s="6" t="n">
-        <f aca="false">SUM(D12:F12)</f>
+      <c r="G12" s="20" t="n">
+        <f aca="false">Translation!O12</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <f aca="false">SUM(D12:G12)</f>
         <v>1500</v>
       </c>
-      <c r="H12" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$43,Eliminations!$D$6:$D$43,$B12)</f>
+      <c r="I12" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B12)</f>
         <v>338.563</v>
       </c>
-      <c r="I12" s="21" t="n">
-        <f aca="false">G12+H12</f>
+      <c r="J12" s="21" t="n">
+        <f aca="false">H12+I12</f>
         <v>1838.563</v>
       </c>
     </row>
@@ -2630,17 +2752,20 @@
       <c r="F13" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="6" t="n">
-        <f aca="false">SUM(D13:F13)</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$43,Eliminations!$D$6:$D$43,$B13)</f>
-        <v>500</v>
-      </c>
-      <c r="I13" s="21" t="n">
-        <f aca="false">G13+H13</f>
-        <v>500</v>
+      <c r="G13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <f aca="false">SUM(D13:G13)</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B13)</f>
+        <v>576.2</v>
+      </c>
+      <c r="J13" s="21" t="n">
+        <f aca="false">H13+I13</f>
+        <v>576.2</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2662,17 +2787,21 @@
         <f aca="false">Translation!L13</f>
         <v>-486</v>
       </c>
-      <c r="G14" s="6" t="n">
-        <f aca="false">SUM(D14:F14)</f>
-        <v>-2836</v>
-      </c>
-      <c r="H14" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$43,Eliminations!$D$6:$D$43,$B14)</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="21" t="n">
-        <f aca="false">G14+H14</f>
-        <v>-2836</v>
+      <c r="G14" s="20" t="n">
+        <f aca="false">Translation!O13</f>
+        <v>-228.6</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <f aca="false">SUM(D14:G14)</f>
+        <v>-3064.6</v>
+      </c>
+      <c r="I14" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B14)</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="21" t="n">
+        <f aca="false">H14+I14</f>
+        <v>-3064.6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2680,7 +2809,7 @@
         <v>2150</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="D15" s="20" t="n">
         <f aca="false">Translation!F14</f>
@@ -2694,16 +2823,20 @@
         <f aca="false">Translation!L14</f>
         <v>-540</v>
       </c>
-      <c r="G15" s="6" t="n">
-        <f aca="false">SUM(D15:F15)</f>
+      <c r="G15" s="20" t="n">
+        <f aca="false">Translation!O14</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <f aca="false">SUM(D15:G15)</f>
         <v>-690</v>
       </c>
-      <c r="H15" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$43,Eliminations!$D$6:$D$43,$B15)</f>
+      <c r="I15" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B15)</f>
         <v>690</v>
       </c>
-      <c r="I15" s="21" t="n">
-        <f aca="false">G15+H15</f>
+      <c r="J15" s="21" t="n">
+        <f aca="false">H15+I15</f>
         <v>0</v>
       </c>
     </row>
@@ -2720,23 +2853,27 @@
       </c>
       <c r="E16" s="20" t="n">
         <f aca="false">Translation!I15</f>
-        <v>-1000</v>
+        <v>-1600</v>
       </c>
       <c r="F16" s="20" t="n">
         <f aca="false">Translation!L15</f>
         <v>-648</v>
       </c>
-      <c r="G16" s="6" t="n">
-        <f aca="false">SUM(D16:F16)</f>
-        <v>-6648</v>
-      </c>
-      <c r="H16" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$43,Eliminations!$D$6:$D$43,$B16)</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="21" t="n">
-        <f aca="false">G16+H16</f>
-        <v>-6648</v>
+      <c r="G16" s="20" t="n">
+        <f aca="false">Translation!O15</f>
+        <v>-381</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <f aca="false">SUM(D16:G16)</f>
+        <v>-7629</v>
+      </c>
+      <c r="I16" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B16)</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="21" t="n">
+        <f aca="false">H16+I16</f>
+        <v>-7629</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2758,16 +2895,20 @@
         <f aca="false">Translation!L16</f>
         <v>-1100</v>
       </c>
-      <c r="G17" s="6" t="n">
-        <f aca="false">SUM(D17:F17)</f>
-        <v>-7100</v>
-      </c>
-      <c r="H17" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$43,Eliminations!$D$6:$D$43,$B17)</f>
-        <v>2100</v>
-      </c>
-      <c r="I17" s="21" t="n">
-        <f aca="false">G17+H17</f>
+      <c r="G17" s="20" t="n">
+        <f aca="false">Translation!O16</f>
+        <v>-625</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <f aca="false">SUM(D17:G17)</f>
+        <v>-7725</v>
+      </c>
+      <c r="I17" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B17)</f>
+        <v>2725</v>
+      </c>
+      <c r="J17" s="21" t="n">
+        <f aca="false">H17+I17</f>
         <v>-5000</v>
       </c>
     </row>
@@ -2776,7 +2917,7 @@
         <v>3100</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="D18" s="20" t="n">
         <f aca="false">Translation!F17</f>
@@ -2790,17 +2931,21 @@
         <f aca="false">Translation!L17</f>
         <v>-460</v>
       </c>
-      <c r="G18" s="6" t="n">
-        <f aca="false">SUM(D18:F18)</f>
-        <v>-4720</v>
-      </c>
-      <c r="H18" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$43,Eliminations!$D$6:$D$43,$B18)</f>
-        <v>1069.465</v>
-      </c>
-      <c r="I18" s="21" t="n">
-        <f aca="false">G18+H18</f>
-        <v>-3650.535</v>
+      <c r="G18" s="20" t="n">
+        <f aca="false">Translation!O17</f>
+        <v>-377</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <f aca="false">SUM(D18:G18)</f>
+        <v>-5097</v>
+      </c>
+      <c r="I18" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B18)</f>
+        <v>1270.065</v>
+      </c>
+      <c r="J18" s="21" t="n">
+        <f aca="false">H18+I18</f>
+        <v>-3826.935</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2822,17 +2967,21 @@
         <f aca="false">Translation!L26</f>
         <v>30.7000000000002</v>
       </c>
-      <c r="G19" s="6" t="n">
-        <f aca="false">SUM(D19:F19)</f>
-        <v>30.7000000000002</v>
-      </c>
-      <c r="H19" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$43,Eliminations!$D$6:$D$43,$B19)</f>
-        <v>-6.14000000000003</v>
-      </c>
-      <c r="I19" s="21" t="n">
-        <f aca="false">G19+H19</f>
-        <v>24.5600000000001</v>
+      <c r="G19" s="20" t="n">
+        <f aca="false">Translation!O26</f>
+        <v>-11.9</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <f aca="false">SUM(D19:G19)</f>
+        <v>18.8000000000002</v>
+      </c>
+      <c r="I19" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B19)</f>
+        <v>-3.77000000000003</v>
+      </c>
+      <c r="J19" s="21" t="n">
+        <f aca="false">H19+I19</f>
+        <v>15.0300000000001</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2851,17 +3000,20 @@
       <c r="F20" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="6" t="n">
-        <f aca="false">SUM(D20:F20)</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$43,Eliminations!$D$6:$D$43,$B20)</f>
-        <v>-305.86</v>
-      </c>
-      <c r="I20" s="21" t="n">
-        <f aca="false">G20+H20</f>
-        <v>-305.86</v>
+      <c r="G20" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <f aca="false">SUM(D20:G20)</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B20)</f>
+        <v>-610.03</v>
+      </c>
+      <c r="J20" s="21" t="n">
+        <f aca="false">H20+I20</f>
+        <v>-610.03</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2883,17 +3035,21 @@
         <f aca="false">Translation!L18</f>
         <v>-3924</v>
       </c>
-      <c r="G21" s="6" t="n">
-        <f aca="false">SUM(D21:F21)</f>
-        <v>-22124</v>
-      </c>
-      <c r="H21" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$43,Eliminations!$D$6:$D$43,$B21)</f>
-        <v>0</v>
-      </c>
-      <c r="I21" s="21" t="n">
-        <f aca="false">G21+H21</f>
-        <v>-22124</v>
+      <c r="G21" s="20" t="n">
+        <f aca="false">Translation!O18</f>
+        <v>-2048</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <f aca="false">SUM(D21:G21)</f>
+        <v>-24172</v>
+      </c>
+      <c r="I21" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B21)</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="21" t="n">
+        <f aca="false">H21+I21</f>
+        <v>-24172</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2901,7 +3057,7 @@
         <v>4050</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="D22" s="20" t="n">
         <f aca="false">Translation!F19</f>
@@ -2915,16 +3071,20 @@
         <f aca="false">Translation!L19</f>
         <v>0</v>
       </c>
-      <c r="G22" s="6" t="n">
-        <f aca="false">SUM(D22:F22)</f>
+      <c r="G22" s="20" t="n">
+        <f aca="false">Translation!O19</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <f aca="false">SUM(D22:G22)</f>
         <v>-800</v>
       </c>
-      <c r="H22" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$43,Eliminations!$D$6:$D$43,$B22)</f>
+      <c r="I22" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B22)</f>
         <v>800</v>
       </c>
-      <c r="I22" s="21" t="n">
-        <f aca="false">G22+H22</f>
+      <c r="J22" s="21" t="n">
+        <f aca="false">H22+I22</f>
         <v>0</v>
       </c>
     </row>
@@ -2933,7 +3093,7 @@
         <v>4100</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="D23" s="20" t="n">
         <f aca="false">Translation!F20</f>
@@ -2947,16 +3107,20 @@
         <f aca="false">Translation!L20</f>
         <v>0</v>
       </c>
-      <c r="G23" s="6" t="n">
-        <f aca="false">SUM(D23:F23)</f>
+      <c r="G23" s="20" t="n">
+        <f aca="false">Translation!O20</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <f aca="false">SUM(D23:G23)</f>
         <v>-131.69</v>
       </c>
-      <c r="H23" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$43,Eliminations!$D$6:$D$43,$B23)</f>
+      <c r="I23" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B23)</f>
         <v>131.69</v>
       </c>
-      <c r="I23" s="21" t="n">
-        <f aca="false">G23+H23</f>
+      <c r="J23" s="21" t="n">
+        <f aca="false">H23+I23</f>
         <v>0</v>
       </c>
     </row>
@@ -2965,7 +3129,7 @@
         <v>4200</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="D24" s="20" t="n">
         <v>0</v>
@@ -2976,16 +3140,19 @@
       <c r="F24" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="6" t="n">
-        <f aca="false">SUM(D24:F24)</f>
-        <v>0</v>
-      </c>
-      <c r="H24" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$43,Eliminations!$D$6:$D$43,$B24)</f>
+      <c r="G24" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <f aca="false">SUM(D24:G24)</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B24)</f>
         <v>-259.718</v>
       </c>
-      <c r="I24" s="21" t="n">
-        <f aca="false">G24+H24</f>
+      <c r="J24" s="21" t="n">
+        <f aca="false">H24+I24</f>
         <v>-259.718</v>
       </c>
     </row>
@@ -3008,17 +3175,21 @@
         <f aca="false">Translation!L21</f>
         <v>2398</v>
       </c>
-      <c r="G25" s="6" t="n">
-        <f aca="false">SUM(D25:F25)</f>
-        <v>12998</v>
-      </c>
-      <c r="H25" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$43,Eliminations!$D$6:$D$43,$B25)</f>
+      <c r="G25" s="20" t="n">
+        <f aca="false">Translation!O21</f>
+        <v>1280</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <f aca="false">SUM(D25:G25)</f>
+        <v>14278</v>
+      </c>
+      <c r="I25" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B25)</f>
         <v>62</v>
       </c>
-      <c r="I25" s="21" t="n">
-        <f aca="false">G25+H25</f>
-        <v>13060</v>
+      <c r="J25" s="21" t="n">
+        <f aca="false">H25+I25</f>
+        <v>14340</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3026,7 +3197,7 @@
         <v>5050</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="D26" s="20" t="n">
         <f aca="false">Translation!F22</f>
@@ -3040,16 +3211,20 @@
         <f aca="false">Translation!L22</f>
         <v>0</v>
       </c>
-      <c r="G26" s="6" t="n">
-        <f aca="false">SUM(D26:F26)</f>
+      <c r="G26" s="20" t="n">
+        <f aca="false">Translation!O22</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <f aca="false">SUM(D26:G26)</f>
         <v>800</v>
       </c>
-      <c r="H26" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$43,Eliminations!$D$6:$D$43,$B26)</f>
+      <c r="I26" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B26)</f>
         <v>-800</v>
       </c>
-      <c r="I26" s="21" t="n">
-        <f aca="false">G26+H26</f>
+      <c r="J26" s="21" t="n">
+        <f aca="false">H26+I26</f>
         <v>0</v>
       </c>
     </row>
@@ -3072,17 +3247,21 @@
         <f aca="false">Translation!L23</f>
         <v>872</v>
       </c>
-      <c r="G27" s="6" t="n">
-        <f aca="false">SUM(D27:F27)</f>
-        <v>4922</v>
-      </c>
-      <c r="H27" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$43,Eliminations!$D$6:$D$43,$B27)</f>
-        <v>0</v>
-      </c>
-      <c r="I27" s="21" t="n">
-        <f aca="false">G27+H27</f>
-        <v>4922</v>
+      <c r="G27" s="20" t="n">
+        <f aca="false">Translation!O23</f>
+        <v>384</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <f aca="false">SUM(D27:G27)</f>
+        <v>5306</v>
+      </c>
+      <c r="I27" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B27)</f>
+        <v>0</v>
+      </c>
+      <c r="J27" s="21" t="n">
+        <f aca="false">H27+I27</f>
+        <v>5306</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3104,17 +3283,21 @@
         <f aca="false">Translation!L24</f>
         <v>32.7</v>
       </c>
-      <c r="G28" s="6" t="n">
-        <f aca="false">SUM(D28:F28)</f>
-        <v>372.7</v>
-      </c>
-      <c r="H28" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$43,Eliminations!$D$6:$D$43,$B28)</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="21" t="n">
-        <f aca="false">G28+H28</f>
-        <v>372.7</v>
+      <c r="G28" s="20" t="n">
+        <f aca="false">Translation!O24</f>
+        <v>25.6</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <f aca="false">SUM(D28:G28)</f>
+        <v>398.3</v>
+      </c>
+      <c r="I28" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B28)</f>
+        <v>0</v>
+      </c>
+      <c r="J28" s="21" t="n">
+        <f aca="false">H28+I28</f>
+        <v>398.3</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3136,22 +3319,26 @@
         <f aca="false">Translation!L25</f>
         <v>152.6</v>
       </c>
-      <c r="G29" s="6" t="n">
-        <f aca="false">SUM(D29:F29)</f>
-        <v>852.6</v>
-      </c>
-      <c r="H29" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$43,Eliminations!$D$6:$D$43,$B29)</f>
-        <v>0</v>
-      </c>
-      <c r="I29" s="21" t="n">
-        <f aca="false">G29+H29</f>
-        <v>852.6</v>
+      <c r="G29" s="20" t="n">
+        <f aca="false">Translation!O25</f>
+        <v>89.6</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <f aca="false">SUM(D29:G29)</f>
+        <v>942.2</v>
+      </c>
+      <c r="I29" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B29)</f>
+        <v>0</v>
+      </c>
+      <c r="J29" s="21" t="n">
+        <f aca="false">H29+I29</f>
+        <v>942.2</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C30" s="7" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="D30" s="8" t="n">
         <f aca="false">ROUND(SUM(D6:D29),2)</f>
@@ -3175,6 +3362,10 @@
       </c>
       <c r="I30" s="8" t="n">
         <f aca="false">ROUND(SUM(I6:I29),2)</f>
+        <v>0</v>
+      </c>
+      <c r="J30" s="8" t="n">
+        <f aca="false">ROUND(SUM(J6:J29),2)</f>
         <v>0</v>
       </c>
     </row>
@@ -3194,7 +3385,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:F44"/>
+  <dimension ref="B1:F55"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -3212,7 +3403,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3222,19 +3413,19 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3242,7 +3433,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>3000</v>
@@ -3260,16 +3451,16 @@
         <v>1</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>3100</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="F7" s="20" t="n">
-        <f aca="false">Inputs!$G$7</f>
+        <f aca="false">(Inputs!$G$7*Inputs!$F$13)</f>
         <v>1200</v>
       </c>
     </row>
@@ -3278,7 +3469,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>1700</v>
@@ -3287,7 +3478,7 @@
         <v>20</v>
       </c>
       <c r="F8" s="20" t="n">
-        <f aca="false">Inputs!$F$7-Inputs!$E$7*((-Translation!I16)+Inputs!$G$7)</f>
+        <f aca="false">(Inputs!$J$6*Inputs!$F$7-Inputs!$J$7*((-Translation!I16)+(Inputs!$G$7*Inputs!$F$13)))*Inputs!$D$13/Inputs!$F$13</f>
         <v>500</v>
       </c>
     </row>
@@ -3296,13 +3487,13 @@
         <v>1</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>1600</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="F9" s="20" t="n">
         <f aca="false">-Inputs!$F$7</f>
@@ -3314,7 +3505,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>3300</v>
@@ -3323,7 +3514,7 @@
         <v>34</v>
       </c>
       <c r="F10" s="20" t="n">
-        <f aca="false">-(1-Inputs!$E$7)*((-Translation!I16)+Inputs!$G$7)</f>
+        <f aca="false">-((1-Inputs!$J$7)*((-Translation!I16)+(Inputs!$G$7*Inputs!$F$13))-(1-Inputs!$J$6)*Inputs!$F$7)</f>
         <v>-0</v>
       </c>
     </row>
@@ -3332,7 +3523,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>3000</v>
@@ -3350,16 +3541,16 @@
         <v>2</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>3100</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="F12" s="20" t="n">
-        <f aca="false">Inputs!$G$8</f>
+        <f aca="false">(Inputs!$G$8*Inputs!$F$14)</f>
         <v>0</v>
       </c>
     </row>
@@ -3368,7 +3559,7 @@
         <v>2</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>1700</v>
@@ -3377,7 +3568,7 @@
         <v>20</v>
       </c>
       <c r="F13" s="20" t="n">
-        <f aca="false">Inputs!$F$8-Inputs!$E$8*((-Translation!L16)+Inputs!$G$8)</f>
+        <f aca="false">(Inputs!$J$6*Inputs!$F$8-Inputs!$J$8*((-Translation!L16)+(Inputs!$G$8*Inputs!$F$14)))*Inputs!$D$14/Inputs!$F$14</f>
         <v>0</v>
       </c>
     </row>
@@ -3386,13 +3577,13 @@
         <v>2</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>1600</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="F14" s="20" t="n">
         <f aca="false">-Inputs!$F$8</f>
@@ -3404,7 +3595,7 @@
         <v>2</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>3300</v>
@@ -3413,26 +3604,26 @@
         <v>34</v>
       </c>
       <c r="F15" s="20" t="n">
-        <f aca="false">-(1-Inputs!$E$8)*((-Translation!L16)+Inputs!$G$8)</f>
+        <f aca="false">-((1-Inputs!$J$8)*((-Translation!L16)+(Inputs!$G$8*Inputs!$F$14))-(1-Inputs!$J$6)*Inputs!$F$8)</f>
         <v>-220</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>140</v>
+        <v>32</v>
       </c>
       <c r="F16" s="20" t="n">
-        <f aca="false">(1-Inputs!$E$8)*(-Translation!L17-Inputs!$G$8)</f>
-        <v>92</v>
+        <f aca="false">(Inputs!$J$6*Inputs!$F$8-Inputs!$J$8*((-Translation!L16)+(Inputs!$G$8*Inputs!$F$14)))*(1-Inputs!$D$14/Inputs!$F$14)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3440,17 +3631,17 @@
         <v>3</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>3300</v>
+        <v>3100</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>34</v>
+        <v>147</v>
       </c>
       <c r="F17" s="20" t="n">
-        <f aca="false">-(1-Inputs!$E$8)*(-Translation!L17-Inputs!$G$8)</f>
-        <v>-92</v>
+        <f aca="false">(1-Inputs!$J$8)*(-Translation!L17-(Inputs!$G$8*Inputs!$F$14))</f>
+        <v>92</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3458,17 +3649,17 @@
         <v>3</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F18" s="20" t="n">
-        <f aca="false">-(1-Inputs!$E$8)*Translation!L26</f>
-        <v>-6.14000000000003</v>
+        <f aca="false">-(1-Inputs!$J$8)*(-Translation!L17-(Inputs!$G$8*Inputs!$F$14))</f>
+        <v>-92</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3476,35 +3667,35 @@
         <v>3</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>3300</v>
+        <v>3200</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F19" s="20" t="n">
-        <f aca="false">(1-Inputs!$E$8)*Translation!L26</f>
-        <v>6.14000000000003</v>
+        <f aca="false">-(1-Inputs!$J$8)*Translation!L26</f>
+        <v>-6.14000000000003</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>2150</v>
+        <v>3300</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="F20" s="20" t="n">
-        <f aca="false">Inputs!$F$18</f>
-        <v>150</v>
+        <f aca="false">(1-Inputs!$J$8)*Translation!L26</f>
+        <v>6.14000000000003</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3512,421 +3703,619 @@
         <v>4</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1150</v>
+        <v>3000</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>136</v>
+        <v>30</v>
       </c>
       <c r="F21" s="20" t="n">
-        <f aca="false">-Inputs!$F$18</f>
-        <v>-150</v>
+        <f aca="false">(-Translation!O16)</f>
+        <v>625</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>2150</v>
+        <v>3100</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="F22" s="20" t="n">
-        <f aca="false">Inputs!$F$19</f>
-        <v>540</v>
+        <f aca="false">(Inputs!$G$9*Inputs!$F$16)</f>
+        <v>125</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1150</v>
+        <v>1700</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="F23" s="20" t="n">
-        <f aca="false">-Inputs!$F$19</f>
-        <v>-540</v>
+        <f aca="false">(Inputs!$J$7*Inputs!$F$9-Inputs!$J$9*((-Translation!O16)+(Inputs!$G$9*Inputs!$F$16)))*Inputs!$D$16/Inputs!$F$16</f>
+        <v>76.2</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>4050</v>
+        <v>1600</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F24" s="20" t="n">
-        <f aca="false">Inputs!$F$20</f>
-        <v>800</v>
+        <f aca="false">-Inputs!$F$9</f>
+        <v>-600</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>5050</v>
+        <v>3300</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>144</v>
+        <v>34</v>
       </c>
       <c r="F25" s="20" t="n">
-        <f aca="false">-Inputs!$F$20</f>
-        <v>-800</v>
+        <f aca="false">-((1-Inputs!$J$9)*((-Translation!O16)+(Inputs!$G$9*Inputs!$F$16))-(1-Inputs!$J$7)*Inputs!$F$9)</f>
+        <v>-225</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>5000</v>
+        <v>3200</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F26" s="20" t="n">
-        <f aca="false">Inputs!$F$21</f>
-        <v>50</v>
+        <f aca="false">(Inputs!$J$7*Inputs!$F$9-Inputs!$J$9*((-Translation!O16)+(Inputs!$G$9*Inputs!$F$16)))*(1-Inputs!$D$16/Inputs!$F$16)</f>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>1200</v>
+        <v>3100</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>24</v>
+        <v>147</v>
       </c>
       <c r="F27" s="20" t="n">
-        <f aca="false">-Inputs!$F$21</f>
-        <v>-50</v>
+        <f aca="false">(1-Inputs!$J$9)*(-Translation!O17-(Inputs!$G$9*Inputs!$F$16))</f>
+        <v>75.6</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>3300</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F28" s="20" t="n">
+        <f aca="false">-(1-Inputs!$J$9)*(-Translation!O17-(Inputs!$G$9*Inputs!$F$16))</f>
+        <v>-75.6</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>3200</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F29" s="20" t="n">
+        <f aca="false">-(1-Inputs!$J$9)*Translation!O26</f>
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>3300</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F30" s="20" t="n">
+        <f aca="false">(1-Inputs!$J$9)*Translation!O26</f>
+        <v>-3.57</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>2150</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F31" s="20" t="n">
+        <f aca="false">Inputs!$F$20</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>1150</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F32" s="20" t="n">
+        <f aca="false">-Inputs!$F$20</f>
+        <v>-150</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>2150</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F33" s="20" t="n">
+        <f aca="false">Inputs!$F$21</f>
+        <v>540</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>1150</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F34" s="20" t="n">
+        <f aca="false">-Inputs!$F$21</f>
+        <v>-540</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="D28" s="5" t="n">
+      <c r="C35" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>4050</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F35" s="20" t="n">
+        <f aca="false">Inputs!$F$22</f>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>5050</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F36" s="20" t="n">
+        <f aca="false">-Inputs!$F$22</f>
+        <v>-800</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F37" s="20" t="n">
+        <f aca="false">Inputs!$F$23</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F38" s="20" t="n">
+        <f aca="false">-Inputs!$F$23</f>
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D39" s="5" t="n">
         <v>1650</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="F28" s="20" t="n">
+      <c r="E39" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F39" s="20" t="n">
         <f aca="false">Associates!D25</f>
         <v>122.535</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="D29" s="5" t="n">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D40" s="5" t="n">
         <v>3100</v>
       </c>
-      <c r="E29" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="F29" s="20" t="n">
+      <c r="E40" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F40" s="20" t="n">
         <f aca="false">-Associates!D25</f>
         <v>-122.535</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="D30" s="5" t="n">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D41" s="5" t="n">
         <v>1650</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="F30" s="20" t="n">
+      <c r="E41" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F41" s="20" t="n">
         <f aca="false">Associates!D27</f>
         <v>179.718</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="D31" s="5" t="n">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D42" s="5" t="n">
         <v>4200</v>
       </c>
-      <c r="E31" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="F31" s="20" t="n">
+      <c r="E42" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="F42" s="20" t="n">
         <f aca="false">-Associates!D27</f>
         <v>-179.718</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="D32" s="5" t="n">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D43" s="5" t="n">
         <v>4100</v>
       </c>
-      <c r="E32" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="F32" s="20" t="n">
+      <c r="E43" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F43" s="20" t="n">
         <f aca="false">-Associates!D28</f>
         <v>81.69</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="D33" s="5" t="n">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D44" s="5" t="n">
         <v>1650</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="F33" s="20" t="n">
+      <c r="E44" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F44" s="20" t="n">
         <f aca="false">Associates!D28</f>
         <v>-81.69</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="D34" s="5" t="n">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D45" s="5" t="n">
         <v>5000</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E45" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F34" s="20" t="n">
+      <c r="F45" s="20" t="n">
         <f aca="false">-Associates!D30</f>
         <v>12</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="D35" s="5" t="n">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D46" s="5" t="n">
         <v>1650</v>
       </c>
-      <c r="E35" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="F35" s="20" t="n">
+      <c r="E46" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F46" s="20" t="n">
         <f aca="false">Associates!D30</f>
         <v>-12</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="D36" s="5" t="n">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D47" s="5" t="n">
         <v>1650</v>
       </c>
-      <c r="E36" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="F36" s="20" t="n">
+      <c r="E47" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F47" s="20" t="n">
         <f aca="false">Associates!E25</f>
         <v>100</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="D37" s="5" t="n">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D48" s="5" t="n">
         <v>3100</v>
       </c>
-      <c r="E37" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="F37" s="20" t="n">
+      <c r="E48" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F48" s="20" t="n">
         <f aca="false">-Associates!E25</f>
         <v>-100</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="D38" s="5" t="n">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D49" s="5" t="n">
         <v>1650</v>
       </c>
-      <c r="E38" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="F38" s="20" t="n">
+      <c r="E49" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F49" s="20" t="n">
         <f aca="false">Associates!E27</f>
         <v>120</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="D39" s="5" t="n">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D50" s="5" t="n">
         <v>4200</v>
       </c>
-      <c r="E39" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="F39" s="20" t="n">
+      <c r="E50" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="F50" s="20" t="n">
         <f aca="false">-Associates!E27</f>
         <v>-120</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="D40" s="5" t="n">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D51" s="5" t="n">
         <v>4100</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="F40" s="20" t="n">
+      <c r="E51" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F51" s="20" t="n">
         <f aca="false">-Associates!E28</f>
         <v>50</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="D41" s="5" t="n">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D52" s="5" t="n">
         <v>1650</v>
       </c>
-      <c r="E41" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="F41" s="20" t="n">
+      <c r="E52" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F52" s="20" t="n">
         <f aca="false">Associates!E28</f>
         <v>-50</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D42" s="5" t="n">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D53" s="5" t="n">
         <v>4200</v>
       </c>
-      <c r="E42" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="F42" s="20" t="n">
+      <c r="E53" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="F53" s="20" t="n">
         <f aca="false">-Associates!E29</f>
         <v>40</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D43" s="5" t="n">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D54" s="5" t="n">
         <v>1650</v>
       </c>
-      <c r="E43" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="F43" s="20" t="n">
+      <c r="E54" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F54" s="20" t="n">
         <f aca="false">Associates!E29</f>
         <v>-40</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E44" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="F44" s="8" t="n">
-        <f aca="false">ROUND(SUM(F6:F43),2)</f>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E55" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="F55" s="8" t="n">
+        <f aca="false">ROUND(SUM(F6:F54),2)</f>
         <v>0</v>
       </c>
     </row>
@@ -3962,7 +4351,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3974,35 +4363,35 @@
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="19" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4018,7 +4407,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>900</v>
@@ -4033,7 +4422,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>9000</v>
@@ -4044,7 +4433,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>3000</v>
@@ -4055,7 +4444,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>4500</v>
@@ -4066,7 +4455,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>2200</v>
@@ -4077,7 +4466,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>1000</v>
@@ -4088,7 +4477,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>0</v>
@@ -4103,51 +4492,51 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="D16" s="25" t="n">
-        <f aca="false">Inputs!$F$14</f>
+        <f aca="false">Inputs!$F$15</f>
         <v>0.2723</v>
       </c>
       <c r="E16" s="25" t="n">
-        <f aca="false">Inputs!$F$12</f>
+        <f aca="false">Inputs!$F$13</f>
         <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="D17" s="25" t="n">
-        <f aca="false">Inputs!$E$14</f>
+        <f aca="false">Inputs!$E$15</f>
         <v>0.2723</v>
       </c>
       <c r="E17" s="25" t="n">
-        <f aca="false">Inputs!$E$12</f>
+        <f aca="false">Inputs!$E$13</f>
         <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="D18" s="25" t="n">
-        <f aca="false">Inputs!$D$14</f>
+        <f aca="false">Inputs!$D$15</f>
         <v>0.2723</v>
       </c>
       <c r="E18" s="25" t="n">
-        <f aca="false">Inputs!$D$12</f>
+        <f aca="false">Inputs!$D$13</f>
         <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="7" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="D21" s="26" t="n">
         <f aca="false">D8*D10*D16</f>
@@ -4164,7 +4553,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="D22" s="26" t="n">
         <f aca="false">D9-D21</f>
@@ -4181,7 +4570,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="D24" s="26" t="n">
         <f aca="false">D9</f>
@@ -4198,7 +4587,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="5" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="D25" s="26" t="n">
         <f aca="false">D8*(D12-D11)*D16</f>
@@ -4215,7 +4604,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="7" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="D26" s="27" t="n">
         <f aca="false">D24+D25</f>
@@ -4232,7 +4621,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="5" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="D27" s="26" t="n">
         <f aca="false">D8*D13*D17</f>
@@ -4249,7 +4638,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="5" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="D28" s="26" t="n">
         <f aca="false">-D8*D14*D17</f>
@@ -4266,7 +4655,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="5" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D29" s="26" t="n">
         <f aca="false">-D15</f>
@@ -4283,14 +4672,14 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="D30" s="26" t="n">
-        <f aca="false">-D8*SUMIFS(Inputs!$F$18:$F$22,Inputs!$B$18:$B$22,"associate_unrealised_profit",Inputs!$E$18:$E$22,"ASSOC1")</f>
+        <f aca="false">-D8*SUMIFS(Inputs!$F$20:$F$24,Inputs!$B$20:$B$24,"associate_unrealised_profit",Inputs!$E$20:$E$24,"ASSOC1")</f>
         <v>-12</v>
       </c>
       <c r="E30" s="26" t="n">
-        <f aca="false">-E8*SUMIFS(Inputs!$F$18:$F$22,Inputs!$B$18:$B$22,"associate_unrealised_profit",Inputs!$E$18:$E$22,"ASSOC2")</f>
+        <f aca="false">-E8*SUMIFS(Inputs!$F$20:$F$24,Inputs!$B$20:$B$24,"associate_unrealised_profit",Inputs!$E$20:$E$24,"ASSOC2")</f>
         <v>-0</v>
       </c>
       <c r="F30" s="21" t="n">
@@ -4300,7 +4689,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="7" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="D31" s="28" t="n">
         <f aca="false">SUM(D26:D30)</f>
@@ -4317,12 +4706,12 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="7" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="5" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="D34" s="26" t="n">
         <f aca="false">D10+D12-D11+D13-D14</f>
@@ -4335,7 +4724,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="5" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="D35" s="26" t="n">
         <f aca="false">D8*D34*D18</f>
@@ -4369,7 +4758,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="5" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D37" s="26" t="n">
         <f aca="false">D29</f>
@@ -4386,7 +4775,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="5" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="D38" s="26" t="n">
         <f aca="false">D30</f>
@@ -4403,7 +4792,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="5" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="D39" s="26" t="n">
         <f aca="false">D31-SUM(D35:D38)</f>
@@ -4420,7 +4809,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="7" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="D40" s="28" t="n">
         <f aca="false">SUM(D35:D39)</f>
@@ -4437,14 +4826,14 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="5" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="D42" s="26" t="n">
-        <f aca="false">D8*SUMIFS(Inputs!$F$18:$F$22,Inputs!$B$18:$B$22,"associate_unrealised_profit",Inputs!$D$18:$D$22,"ASSOC1")</f>
+        <f aca="false">D8*SUMIFS(Inputs!$F$20:$F$24,Inputs!$B$20:$B$24,"associate_unrealised_profit",Inputs!$D$20:$D$24,"ASSOC1")</f>
         <v>0</v>
       </c>
       <c r="E42" s="26" t="n">
-        <f aca="false">E8*SUMIFS(Inputs!$F$18:$F$22,Inputs!$B$18:$B$22,"associate_unrealised_profit",Inputs!$D$18:$D$22,"ASSOC2")</f>
+        <f aca="false">E8*SUMIFS(Inputs!$F$20:$F$24,Inputs!$B$20:$B$24,"associate_unrealised_profit",Inputs!$D$20:$D$24,"ASSOC2")</f>
         <v>0</v>
       </c>
       <c r="F42" s="21" t="n">
@@ -4454,7 +4843,7 @@
     </row>
     <row r="44" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="29" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -4473,7 +4862,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:L28"/>
+  <dimension ref="B1:O28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -4485,7 +4874,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4495,7 +4886,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4505,37 +4896,46 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="J5" s="19" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="L5" s="19" t="s">
-        <v>211</v>
+        <v>220</v>
+      </c>
+      <c r="M5" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="N5" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="O5" s="19" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4550,7 +4950,7 @@
         <v>1331.69</v>
       </c>
       <c r="E6" s="30" t="n">
-        <f aca="false">Inputs!$D$12</f>
+        <f aca="false">Inputs!$D$13</f>
         <v>1</v>
       </c>
       <c r="F6" s="6" t="n">
@@ -4562,7 +4962,7 @@
         <v>600</v>
       </c>
       <c r="H6" s="30" t="n">
-        <f aca="false">Inputs!$D$12</f>
+        <f aca="false">Inputs!$D$13</f>
         <v>1</v>
       </c>
       <c r="I6" s="6" t="n">
@@ -4574,13 +4974,25 @@
         <v>400</v>
       </c>
       <c r="K6" s="30" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1.08</v>
       </c>
       <c r="L6" s="6" t="n">
         <f aca="false">J6*K6</f>
         <v>432</v>
       </c>
+      <c r="M6" s="20" t="n">
+        <f aca="false">'Trial Balances'!H6</f>
+        <v>160</v>
+      </c>
+      <c r="N6" s="30" t="n">
+        <f aca="false">Inputs!$D$16</f>
+        <v>1.27</v>
+      </c>
+      <c r="O6" s="6" t="n">
+        <f aca="false">M6*N6</f>
+        <v>203.2</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="n">
@@ -4594,7 +5006,7 @@
         <v>2100</v>
       </c>
       <c r="E7" s="30" t="n">
-        <f aca="false">Inputs!$D$12</f>
+        <f aca="false">Inputs!$D$13</f>
         <v>1</v>
       </c>
       <c r="F7" s="6" t="n">
@@ -4606,7 +5018,7 @@
         <v>900</v>
       </c>
       <c r="H7" s="30" t="n">
-        <f aca="false">Inputs!$D$12</f>
+        <f aca="false">Inputs!$D$13</f>
         <v>1</v>
       </c>
       <c r="I7" s="6" t="n">
@@ -4618,27 +5030,39 @@
         <v>700</v>
       </c>
       <c r="K7" s="30" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1.08</v>
       </c>
       <c r="L7" s="6" t="n">
         <f aca="false">J7*K7</f>
         <v>756</v>
       </c>
+      <c r="M7" s="20" t="n">
+        <f aca="false">'Trial Balances'!H7</f>
+        <v>250</v>
+      </c>
+      <c r="N7" s="30" t="n">
+        <f aca="false">Inputs!$D$16</f>
+        <v>1.27</v>
+      </c>
+      <c r="O7" s="6" t="n">
+        <f aca="false">M7*N7</f>
+        <v>317.5</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="n">
         <v>1150</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="D8" s="20" t="n">
         <f aca="false">'Trial Balances'!E8</f>
         <v>540</v>
       </c>
       <c r="E8" s="30" t="n">
-        <f aca="false">Inputs!$D$12</f>
+        <f aca="false">Inputs!$D$13</f>
         <v>1</v>
       </c>
       <c r="F8" s="6" t="n">
@@ -4650,7 +5074,7 @@
         <v>150</v>
       </c>
       <c r="H8" s="30" t="n">
-        <f aca="false">Inputs!$D$12</f>
+        <f aca="false">Inputs!$D$13</f>
         <v>1</v>
       </c>
       <c r="I8" s="6" t="n">
@@ -4662,11 +5086,23 @@
         <v>0</v>
       </c>
       <c r="K8" s="30" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1.08</v>
       </c>
       <c r="L8" s="6" t="n">
         <f aca="false">J8*K8</f>
+        <v>0</v>
+      </c>
+      <c r="M8" s="20" t="n">
+        <f aca="false">'Trial Balances'!H8</f>
+        <v>0</v>
+      </c>
+      <c r="N8" s="30" t="n">
+        <f aca="false">Inputs!$D$16</f>
+        <v>1.27</v>
+      </c>
+      <c r="O8" s="6" t="n">
+        <f aca="false">M8*N8</f>
         <v>0</v>
       </c>
     </row>
@@ -4682,7 +5118,7 @@
         <v>1500</v>
       </c>
       <c r="E9" s="30" t="n">
-        <f aca="false">Inputs!$D$12</f>
+        <f aca="false">Inputs!$D$13</f>
         <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
@@ -4694,7 +5130,7 @@
         <v>700</v>
       </c>
       <c r="H9" s="30" t="n">
-        <f aca="false">Inputs!$D$12</f>
+        <f aca="false">Inputs!$D$13</f>
         <v>1</v>
       </c>
       <c r="I9" s="6" t="n">
@@ -4706,13 +5142,25 @@
         <v>500</v>
       </c>
       <c r="K9" s="30" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1.08</v>
       </c>
       <c r="L9" s="6" t="n">
         <f aca="false">J9*K9</f>
         <v>540</v>
       </c>
+      <c r="M9" s="20" t="n">
+        <f aca="false">'Trial Balances'!H9</f>
+        <v>180</v>
+      </c>
+      <c r="N9" s="30" t="n">
+        <f aca="false">Inputs!$D$16</f>
+        <v>1.27</v>
+      </c>
+      <c r="O9" s="6" t="n">
+        <f aca="false">M9*N9</f>
+        <v>228.6</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="n">
@@ -4726,7 +5174,7 @@
         <v>6000</v>
       </c>
       <c r="E10" s="30" t="n">
-        <f aca="false">Inputs!$D$12</f>
+        <f aca="false">Inputs!$D$13</f>
         <v>1</v>
       </c>
       <c r="F10" s="6" t="n">
@@ -4738,7 +5186,7 @@
         <v>2500</v>
       </c>
       <c r="H10" s="30" t="n">
-        <f aca="false">Inputs!$D$12</f>
+        <f aca="false">Inputs!$D$13</f>
         <v>1</v>
       </c>
       <c r="I10" s="6" t="n">
@@ -4750,27 +5198,39 @@
         <v>1800</v>
       </c>
       <c r="K10" s="30" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1.08</v>
       </c>
       <c r="L10" s="6" t="n">
         <f aca="false">J10*K10</f>
         <v>1944</v>
       </c>
+      <c r="M10" s="20" t="n">
+        <f aca="false">'Trial Balances'!H10</f>
+        <v>900</v>
+      </c>
+      <c r="N10" s="30" t="n">
+        <f aca="false">Inputs!$D$16</f>
+        <v>1.27</v>
+      </c>
+      <c r="O10" s="6" t="n">
+        <f aca="false">M10*N10</f>
+        <v>1143</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="n">
         <v>1600</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="D11" s="20" t="n">
         <f aca="false">'Trial Balances'!E11</f>
         <v>3580</v>
       </c>
       <c r="E11" s="30" t="n">
-        <f aca="false">Inputs!$D$12</f>
+        <f aca="false">Inputs!$D$13</f>
         <v>1</v>
       </c>
       <c r="F11" s="6" t="n">
@@ -4779,26 +5239,38 @@
       </c>
       <c r="G11" s="20" t="n">
         <f aca="false">'Trial Balances'!F11</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H11" s="30" t="n">
-        <f aca="false">Inputs!$D$12</f>
+        <f aca="false">Inputs!$D$13</f>
         <v>1</v>
       </c>
       <c r="I11" s="6" t="n">
         <f aca="false">G11*H11</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="J11" s="20" t="n">
         <f aca="false">'Trial Balances'!G11</f>
         <v>0</v>
       </c>
       <c r="K11" s="30" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1.08</v>
       </c>
       <c r="L11" s="6" t="n">
         <f aca="false">J11*K11</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="20" t="n">
+        <f aca="false">'Trial Balances'!H11</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="30" t="n">
+        <f aca="false">Inputs!$D$16</f>
+        <v>1.27</v>
+      </c>
+      <c r="O11" s="6" t="n">
+        <f aca="false">M11*N11</f>
         <v>0</v>
       </c>
     </row>
@@ -4807,14 +5279,14 @@
         <v>1650</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="D12" s="20" t="n">
         <f aca="false">'Trial Balances'!E12</f>
         <v>1500</v>
       </c>
       <c r="E12" s="30" t="n">
-        <f aca="false">Inputs!$D$12</f>
+        <f aca="false">Inputs!$D$13</f>
         <v>1</v>
       </c>
       <c r="F12" s="6" t="n">
@@ -4826,7 +5298,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="30" t="n">
-        <f aca="false">Inputs!$D$12</f>
+        <f aca="false">Inputs!$D$13</f>
         <v>1</v>
       </c>
       <c r="I12" s="6" t="n">
@@ -4838,11 +5310,23 @@
         <v>0</v>
       </c>
       <c r="K12" s="30" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1.08</v>
       </c>
       <c r="L12" s="6" t="n">
         <f aca="false">J12*K12</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="20" t="n">
+        <f aca="false">'Trial Balances'!H12</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="30" t="n">
+        <f aca="false">Inputs!$D$16</f>
+        <v>1.27</v>
+      </c>
+      <c r="O12" s="6" t="n">
+        <f aca="false">M12*N12</f>
         <v>0</v>
       </c>
     </row>
@@ -4858,7 +5342,7 @@
         <v>-1700</v>
       </c>
       <c r="E13" s="30" t="n">
-        <f aca="false">Inputs!$D$12</f>
+        <f aca="false">Inputs!$D$13</f>
         <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
@@ -4870,7 +5354,7 @@
         <v>-650</v>
       </c>
       <c r="H13" s="30" t="n">
-        <f aca="false">Inputs!$D$12</f>
+        <f aca="false">Inputs!$D$13</f>
         <v>1</v>
       </c>
       <c r="I13" s="6" t="n">
@@ -4882,27 +5366,39 @@
         <v>-450</v>
       </c>
       <c r="K13" s="30" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1.08</v>
       </c>
       <c r="L13" s="6" t="n">
         <f aca="false">J13*K13</f>
         <v>-486</v>
       </c>
+      <c r="M13" s="20" t="n">
+        <f aca="false">'Trial Balances'!H13</f>
+        <v>-180</v>
+      </c>
+      <c r="N13" s="30" t="n">
+        <f aca="false">Inputs!$D$16</f>
+        <v>1.27</v>
+      </c>
+      <c r="O13" s="6" t="n">
+        <f aca="false">M13*N13</f>
+        <v>-228.6</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="n">
         <v>2150</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="D14" s="20" t="n">
         <f aca="false">'Trial Balances'!E14</f>
         <v>-150</v>
       </c>
       <c r="E14" s="30" t="n">
-        <f aca="false">Inputs!$D$12</f>
+        <f aca="false">Inputs!$D$13</f>
         <v>1</v>
       </c>
       <c r="F14" s="6" t="n">
@@ -4914,7 +5410,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="30" t="n">
-        <f aca="false">Inputs!$D$12</f>
+        <f aca="false">Inputs!$D$13</f>
         <v>1</v>
       </c>
       <c r="I14" s="6" t="n">
@@ -4926,13 +5422,25 @@
         <v>-500</v>
       </c>
       <c r="K14" s="30" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1.08</v>
       </c>
       <c r="L14" s="6" t="n">
         <f aca="false">J14*K14</f>
         <v>-540</v>
       </c>
+      <c r="M14" s="20" t="n">
+        <f aca="false">'Trial Balances'!H14</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="30" t="n">
+        <f aca="false">Inputs!$D$16</f>
+        <v>1.27</v>
+      </c>
+      <c r="O14" s="6" t="n">
+        <f aca="false">M14*N14</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="n">
@@ -4946,7 +5454,7 @@
         <v>-5000</v>
       </c>
       <c r="E15" s="30" t="n">
-        <f aca="false">Inputs!$D$12</f>
+        <f aca="false">Inputs!$D$13</f>
         <v>1</v>
       </c>
       <c r="F15" s="6" t="n">
@@ -4955,28 +5463,40 @@
       </c>
       <c r="G15" s="20" t="n">
         <f aca="false">'Trial Balances'!F15</f>
-        <v>-1000</v>
+        <v>-1600</v>
       </c>
       <c r="H15" s="30" t="n">
-        <f aca="false">Inputs!$D$12</f>
+        <f aca="false">Inputs!$D$13</f>
         <v>1</v>
       </c>
       <c r="I15" s="6" t="n">
         <f aca="false">G15*H15</f>
-        <v>-1000</v>
+        <v>-1600</v>
       </c>
       <c r="J15" s="20" t="n">
         <f aca="false">'Trial Balances'!G15</f>
         <v>-600</v>
       </c>
       <c r="K15" s="30" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1.08</v>
       </c>
       <c r="L15" s="6" t="n">
         <f aca="false">J15*K15</f>
         <v>-648</v>
       </c>
+      <c r="M15" s="20" t="n">
+        <f aca="false">'Trial Balances'!H15</f>
+        <v>-300</v>
+      </c>
+      <c r="N15" s="30" t="n">
+        <f aca="false">Inputs!$D$16</f>
+        <v>1.27</v>
+      </c>
+      <c r="O15" s="6" t="n">
+        <f aca="false">M15*N15</f>
+        <v>-381</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="n">
@@ -4990,7 +5510,7 @@
         <v>-5000</v>
       </c>
       <c r="E16" s="30" t="n">
-        <f aca="false">Inputs!$F$12</f>
+        <f aca="false">Inputs!$F$13</f>
         <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
@@ -5002,7 +5522,7 @@
         <v>-1000</v>
       </c>
       <c r="H16" s="30" t="n">
-        <f aca="false">Inputs!$F$12</f>
+        <f aca="false">Inputs!$F$13</f>
         <v>1</v>
       </c>
       <c r="I16" s="6" t="n">
@@ -5014,27 +5534,39 @@
         <v>-1000</v>
       </c>
       <c r="K16" s="30" t="n">
-        <f aca="false">Inputs!$F$13</f>
+        <f aca="false">Inputs!$F$14</f>
         <v>1.1</v>
       </c>
       <c r="L16" s="6" t="n">
         <f aca="false">J16*K16</f>
         <v>-1100</v>
       </c>
+      <c r="M16" s="20" t="n">
+        <f aca="false">'Trial Balances'!H16</f>
+        <v>-500</v>
+      </c>
+      <c r="N16" s="30" t="n">
+        <f aca="false">Inputs!$F$16</f>
+        <v>1.25</v>
+      </c>
+      <c r="O16" s="6" t="n">
+        <f aca="false">M16*N16</f>
+        <v>-625</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="n">
         <v>3100</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="D17" s="20" t="n">
         <f aca="false">'Trial Balances'!E17</f>
         <v>-2800</v>
       </c>
       <c r="E17" s="30" t="n">
-        <f aca="false">Inputs!$F$12</f>
+        <f aca="false">Inputs!$F$13</f>
         <v>1</v>
       </c>
       <c r="F17" s="6" t="n">
@@ -5046,7 +5578,7 @@
         <v>-1460</v>
       </c>
       <c r="H17" s="30" t="n">
-        <f aca="false">Inputs!$F$12</f>
+        <f aca="false">Inputs!$F$13</f>
         <v>1</v>
       </c>
       <c r="I17" s="6" t="n">
@@ -5065,6 +5597,18 @@
         <f aca="false">-Inputs!$H$8</f>
         <v>-460</v>
       </c>
+      <c r="M17" s="20" t="n">
+        <f aca="false">'Trial Balances'!H17</f>
+        <v>-300</v>
+      </c>
+      <c r="N17" s="30" t="n">
+        <f aca="false">IF(M17=0,0,O17/M17)</f>
+        <v>1.25666666666667</v>
+      </c>
+      <c r="O17" s="6" t="n">
+        <f aca="false">-Inputs!$H$9</f>
+        <v>-377</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="n">
@@ -5078,7 +5622,7 @@
         <v>-14000</v>
       </c>
       <c r="E18" s="30" t="n">
-        <f aca="false">Inputs!$E$12</f>
+        <f aca="false">Inputs!$E$13</f>
         <v>1</v>
       </c>
       <c r="F18" s="6" t="n">
@@ -5090,7 +5634,7 @@
         <v>-4200</v>
       </c>
       <c r="H18" s="30" t="n">
-        <f aca="false">Inputs!$E$12</f>
+        <f aca="false">Inputs!$E$13</f>
         <v>1</v>
       </c>
       <c r="I18" s="6" t="n">
@@ -5102,27 +5646,39 @@
         <v>-3600</v>
       </c>
       <c r="K18" s="30" t="n">
-        <f aca="false">Inputs!$E$13</f>
+        <f aca="false">Inputs!$E$14</f>
         <v>1.09</v>
       </c>
       <c r="L18" s="6" t="n">
         <f aca="false">J18*K18</f>
         <v>-3924</v>
       </c>
+      <c r="M18" s="20" t="n">
+        <f aca="false">'Trial Balances'!H18</f>
+        <v>-1600</v>
+      </c>
+      <c r="N18" s="30" t="n">
+        <f aca="false">Inputs!$E$16</f>
+        <v>1.28</v>
+      </c>
+      <c r="O18" s="6" t="n">
+        <f aca="false">M18*N18</f>
+        <v>-2048</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="5" t="n">
         <v>4050</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="D19" s="20" t="n">
         <f aca="false">'Trial Balances'!E19</f>
         <v>0</v>
       </c>
       <c r="E19" s="30" t="n">
-        <f aca="false">Inputs!$E$12</f>
+        <f aca="false">Inputs!$E$13</f>
         <v>1</v>
       </c>
       <c r="F19" s="6" t="n">
@@ -5134,7 +5690,7 @@
         <v>-800</v>
       </c>
       <c r="H19" s="30" t="n">
-        <f aca="false">Inputs!$E$12</f>
+        <f aca="false">Inputs!$E$13</f>
         <v>1</v>
       </c>
       <c r="I19" s="6" t="n">
@@ -5146,11 +5702,23 @@
         <v>0</v>
       </c>
       <c r="K19" s="30" t="n">
-        <f aca="false">Inputs!$E$13</f>
+        <f aca="false">Inputs!$E$14</f>
         <v>1.09</v>
       </c>
       <c r="L19" s="6" t="n">
         <f aca="false">J19*K19</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="20" t="n">
+        <f aca="false">'Trial Balances'!H19</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="30" t="n">
+        <f aca="false">Inputs!$E$16</f>
+        <v>1.28</v>
+      </c>
+      <c r="O19" s="6" t="n">
+        <f aca="false">M19*N19</f>
         <v>0</v>
       </c>
     </row>
@@ -5159,14 +5727,14 @@
         <v>4100</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="D20" s="20" t="n">
         <f aca="false">'Trial Balances'!E20</f>
         <v>-131.69</v>
       </c>
       <c r="E20" s="30" t="n">
-        <f aca="false">Inputs!$E$12</f>
+        <f aca="false">Inputs!$E$13</f>
         <v>1</v>
       </c>
       <c r="F20" s="6" t="n">
@@ -5178,7 +5746,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="30" t="n">
-        <f aca="false">Inputs!$E$12</f>
+        <f aca="false">Inputs!$E$13</f>
         <v>1</v>
       </c>
       <c r="I20" s="6" t="n">
@@ -5190,11 +5758,23 @@
         <v>0</v>
       </c>
       <c r="K20" s="30" t="n">
-        <f aca="false">Inputs!$E$13</f>
+        <f aca="false">Inputs!$E$14</f>
         <v>1.09</v>
       </c>
       <c r="L20" s="6" t="n">
         <f aca="false">J20*K20</f>
+        <v>0</v>
+      </c>
+      <c r="M20" s="20" t="n">
+        <f aca="false">'Trial Balances'!H20</f>
+        <v>0</v>
+      </c>
+      <c r="N20" s="30" t="n">
+        <f aca="false">Inputs!$E$16</f>
+        <v>1.28</v>
+      </c>
+      <c r="O20" s="6" t="n">
+        <f aca="false">M20*N20</f>
         <v>0</v>
       </c>
     </row>
@@ -5210,7 +5790,7 @@
         <v>7600</v>
       </c>
       <c r="E21" s="30" t="n">
-        <f aca="false">Inputs!$E$12</f>
+        <f aca="false">Inputs!$E$13</f>
         <v>1</v>
       </c>
       <c r="F21" s="6" t="n">
@@ -5222,7 +5802,7 @@
         <v>3000</v>
       </c>
       <c r="H21" s="30" t="n">
-        <f aca="false">Inputs!$E$12</f>
+        <f aca="false">Inputs!$E$13</f>
         <v>1</v>
       </c>
       <c r="I21" s="6" t="n">
@@ -5234,27 +5814,39 @@
         <v>2200</v>
       </c>
       <c r="K21" s="30" t="n">
-        <f aca="false">Inputs!$E$13</f>
+        <f aca="false">Inputs!$E$14</f>
         <v>1.09</v>
       </c>
       <c r="L21" s="6" t="n">
         <f aca="false">J21*K21</f>
         <v>2398</v>
       </c>
+      <c r="M21" s="20" t="n">
+        <f aca="false">'Trial Balances'!H21</f>
+        <v>1000</v>
+      </c>
+      <c r="N21" s="30" t="n">
+        <f aca="false">Inputs!$E$16</f>
+        <v>1.28</v>
+      </c>
+      <c r="O21" s="6" t="n">
+        <f aca="false">M21*N21</f>
+        <v>1280</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="n">
         <v>5050</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="D22" s="20" t="n">
         <f aca="false">'Trial Balances'!E22</f>
         <v>800</v>
       </c>
       <c r="E22" s="30" t="n">
-        <f aca="false">Inputs!$E$12</f>
+        <f aca="false">Inputs!$E$13</f>
         <v>1</v>
       </c>
       <c r="F22" s="6" t="n">
@@ -5266,7 +5858,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="30" t="n">
-        <f aca="false">Inputs!$E$12</f>
+        <f aca="false">Inputs!$E$13</f>
         <v>1</v>
       </c>
       <c r="I22" s="6" t="n">
@@ -5278,11 +5870,23 @@
         <v>0</v>
       </c>
       <c r="K22" s="30" t="n">
-        <f aca="false">Inputs!$E$13</f>
+        <f aca="false">Inputs!$E$14</f>
         <v>1.09</v>
       </c>
       <c r="L22" s="6" t="n">
         <f aca="false">J22*K22</f>
+        <v>0</v>
+      </c>
+      <c r="M22" s="20" t="n">
+        <f aca="false">'Trial Balances'!H22</f>
+        <v>0</v>
+      </c>
+      <c r="N22" s="30" t="n">
+        <f aca="false">Inputs!$E$16</f>
+        <v>1.28</v>
+      </c>
+      <c r="O22" s="6" t="n">
+        <f aca="false">M22*N22</f>
         <v>0</v>
       </c>
     </row>
@@ -5298,7 +5902,7 @@
         <v>3100</v>
       </c>
       <c r="E23" s="30" t="n">
-        <f aca="false">Inputs!$E$12</f>
+        <f aca="false">Inputs!$E$13</f>
         <v>1</v>
       </c>
       <c r="F23" s="6" t="n">
@@ -5310,7 +5914,7 @@
         <v>950</v>
       </c>
       <c r="H23" s="30" t="n">
-        <f aca="false">Inputs!$E$12</f>
+        <f aca="false">Inputs!$E$13</f>
         <v>1</v>
       </c>
       <c r="I23" s="6" t="n">
@@ -5322,13 +5926,25 @@
         <v>800</v>
       </c>
       <c r="K23" s="30" t="n">
-        <f aca="false">Inputs!$E$13</f>
+        <f aca="false">Inputs!$E$14</f>
         <v>1.09</v>
       </c>
       <c r="L23" s="6" t="n">
         <f aca="false">J23*K23</f>
         <v>872</v>
       </c>
+      <c r="M23" s="20" t="n">
+        <f aca="false">'Trial Balances'!H23</f>
+        <v>300</v>
+      </c>
+      <c r="N23" s="30" t="n">
+        <f aca="false">Inputs!$E$16</f>
+        <v>1.28</v>
+      </c>
+      <c r="O23" s="6" t="n">
+        <f aca="false">M23*N23</f>
+        <v>384</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="n">
@@ -5342,7 +5958,7 @@
         <v>280</v>
       </c>
       <c r="E24" s="30" t="n">
-        <f aca="false">Inputs!$E$12</f>
+        <f aca="false">Inputs!$E$13</f>
         <v>1</v>
       </c>
       <c r="F24" s="6" t="n">
@@ -5354,7 +5970,7 @@
         <v>60</v>
       </c>
       <c r="H24" s="30" t="n">
-        <f aca="false">Inputs!$E$12</f>
+        <f aca="false">Inputs!$E$13</f>
         <v>1</v>
       </c>
       <c r="I24" s="6" t="n">
@@ -5366,13 +5982,25 @@
         <v>30</v>
       </c>
       <c r="K24" s="30" t="n">
-        <f aca="false">Inputs!$E$13</f>
+        <f aca="false">Inputs!$E$14</f>
         <v>1.09</v>
       </c>
       <c r="L24" s="6" t="n">
         <f aca="false">J24*K24</f>
         <v>32.7</v>
       </c>
+      <c r="M24" s="20" t="n">
+        <f aca="false">'Trial Balances'!H24</f>
+        <v>20</v>
+      </c>
+      <c r="N24" s="30" t="n">
+        <f aca="false">Inputs!$E$16</f>
+        <v>1.28</v>
+      </c>
+      <c r="O24" s="6" t="n">
+        <f aca="false">M24*N24</f>
+        <v>25.6</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="5" t="n">
@@ -5386,7 +6014,7 @@
         <v>450</v>
       </c>
       <c r="E25" s="30" t="n">
-        <f aca="false">Inputs!$E$12</f>
+        <f aca="false">Inputs!$E$13</f>
         <v>1</v>
       </c>
       <c r="F25" s="6" t="n">
@@ -5398,7 +6026,7 @@
         <v>250</v>
       </c>
       <c r="H25" s="30" t="n">
-        <f aca="false">Inputs!$E$12</f>
+        <f aca="false">Inputs!$E$13</f>
         <v>1</v>
       </c>
       <c r="I25" s="6" t="n">
@@ -5410,13 +6038,25 @@
         <v>140</v>
       </c>
       <c r="K25" s="30" t="n">
-        <f aca="false">Inputs!$E$13</f>
+        <f aca="false">Inputs!$E$14</f>
         <v>1.09</v>
       </c>
       <c r="L25" s="6" t="n">
         <f aca="false">J25*K25</f>
         <v>152.6</v>
       </c>
+      <c r="M25" s="20" t="n">
+        <f aca="false">'Trial Balances'!H25</f>
+        <v>70</v>
+      </c>
+      <c r="N25" s="30" t="n">
+        <f aca="false">Inputs!$E$16</f>
+        <v>1.28</v>
+      </c>
+      <c r="O25" s="6" t="n">
+        <f aca="false">M25*N25</f>
+        <v>89.6</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="n">
@@ -5437,10 +6077,14 @@
         <f aca="false">-SUM(L6:L25)</f>
         <v>30.7000000000002</v>
       </c>
+      <c r="O26" s="8" t="n">
+        <f aca="false">-SUM(O6:O25)</f>
+        <v>-11.9</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="3" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -5459,14 +6103,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:G26"/>
+  <dimension ref="B1:H26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="5" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5476,32 +6120,35 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="3" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>216</v>
+        <v>228</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5512,7 +6159,7 @@
         <v>27</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="E6" s="31" t="n">
         <v>1331.69</v>
@@ -5522,6 +6169,9 @@
       </c>
       <c r="G6" s="31" t="n">
         <v>400</v>
+      </c>
+      <c r="H6" s="31" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5532,7 +6182,7 @@
         <v>25</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="E7" s="31" t="n">
         <v>2100</v>
@@ -5542,6 +6192,9 @@
       </c>
       <c r="G7" s="31" t="n">
         <v>700</v>
+      </c>
+      <c r="H7" s="31" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5549,10 +6202,10 @@
         <v>1150</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="E8" s="31" t="n">
         <v>540</v>
@@ -5561,6 +6214,9 @@
         <v>150</v>
       </c>
       <c r="G8" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5572,7 +6228,7 @@
         <v>24</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="E9" s="31" t="n">
         <v>1500</v>
@@ -5582,6 +6238,9 @@
       </c>
       <c r="G9" s="31" t="n">
         <v>500</v>
+      </c>
+      <c r="H9" s="31" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5592,7 +6251,7 @@
         <v>21</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="E10" s="31" t="n">
         <v>6000</v>
@@ -5602,6 +6261,9 @@
       </c>
       <c r="G10" s="31" t="n">
         <v>1800</v>
+      </c>
+      <c r="H10" s="31" t="n">
+        <v>900</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5609,18 +6271,21 @@
         <v>1600</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="E11" s="31" t="n">
         <v>3580</v>
       </c>
       <c r="F11" s="31" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G11" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5629,10 +6294,10 @@
         <v>1650</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="E12" s="31" t="n">
         <v>1500</v>
@@ -5641,6 +6306,9 @@
         <v>0</v>
       </c>
       <c r="G12" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5652,7 +6320,7 @@
         <v>37</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="E13" s="31" t="n">
         <v>-1700</v>
@@ -5662,6 +6330,9 @@
       </c>
       <c r="G13" s="31" t="n">
         <v>-450</v>
+      </c>
+      <c r="H13" s="31" t="n">
+        <v>-180</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5669,10 +6340,10 @@
         <v>2150</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="E14" s="31" t="n">
         <v>-150</v>
@@ -5682,6 +6353,9 @@
       </c>
       <c r="G14" s="31" t="n">
         <v>-500</v>
+      </c>
+      <c r="H14" s="31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5692,16 +6366,19 @@
         <v>36</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="E15" s="31" t="n">
         <v>-5000</v>
       </c>
       <c r="F15" s="31" t="n">
-        <v>-1000</v>
+        <v>-1600</v>
       </c>
       <c r="G15" s="31" t="n">
         <v>-600</v>
+      </c>
+      <c r="H15" s="31" t="n">
+        <v>-300</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5712,7 +6389,7 @@
         <v>30</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="E16" s="31" t="n">
         <v>-5000</v>
@@ -5722,6 +6399,9 @@
       </c>
       <c r="G16" s="31" t="n">
         <v>-1000</v>
+      </c>
+      <c r="H16" s="31" t="n">
+        <v>-500</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5729,10 +6409,10 @@
         <v>3100</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="E17" s="31" t="n">
         <v>-2800</v>
@@ -5742,6 +6422,9 @@
       </c>
       <c r="G17" s="31" t="n">
         <v>-420</v>
+      </c>
+      <c r="H17" s="31" t="n">
+        <v>-300</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5752,7 +6435,7 @@
         <v>4</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="E18" s="31" t="n">
         <v>-14000</v>
@@ -5762,6 +6445,9 @@
       </c>
       <c r="G18" s="31" t="n">
         <v>-3600</v>
+      </c>
+      <c r="H18" s="31" t="n">
+        <v>-1600</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5769,10 +6455,10 @@
         <v>4050</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="E19" s="31" t="n">
         <v>0</v>
@@ -5781,6 +6467,9 @@
         <v>-800</v>
       </c>
       <c r="G19" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5789,10 +6478,10 @@
         <v>4100</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="E20" s="31" t="n">
         <v>-131.69</v>
@@ -5801,6 +6490,9 @@
         <v>0</v>
       </c>
       <c r="G20" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5812,7 +6504,7 @@
         <v>5</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="E21" s="31" t="n">
         <v>7600</v>
@@ -5822,6 +6514,9 @@
       </c>
       <c r="G21" s="31" t="n">
         <v>2200</v>
+      </c>
+      <c r="H21" s="31" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5829,10 +6524,10 @@
         <v>5050</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="E22" s="31" t="n">
         <v>800</v>
@@ -5841,6 +6536,9 @@
         <v>0</v>
       </c>
       <c r="G22" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5852,7 +6550,7 @@
         <v>7</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="E23" s="31" t="n">
         <v>3100</v>
@@ -5862,6 +6560,9 @@
       </c>
       <c r="G23" s="31" t="n">
         <v>800</v>
+      </c>
+      <c r="H23" s="31" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5872,7 +6573,7 @@
         <v>11</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="E24" s="31" t="n">
         <v>280</v>
@@ -5882,6 +6583,9 @@
       </c>
       <c r="G24" s="31" t="n">
         <v>30</v>
+      </c>
+      <c r="H24" s="31" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5892,7 +6596,7 @@
         <v>13</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="E25" s="31" t="n">
         <v>450</v>
@@ -5903,10 +6607,13 @@
       <c r="G25" s="31" t="n">
         <v>140</v>
       </c>
+      <c r="H25" s="31" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="7" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="E26" s="8" t="n">
         <f aca="false">SUM(E6:E25)</f>
@@ -5918,6 +6625,10 @@
       </c>
       <c r="G26" s="8" t="n">
         <f aca="false">SUM(G6:G25)</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <f aca="false">SUM(H6:H25)</f>
         <v>0</v>
       </c>
     </row>
@@ -5937,7 +6648,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:H22"/>
+  <dimension ref="B1:J24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -5948,6 +6659,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5957,7 +6670,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5970,33 +6683,39 @@
         <v>44</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="E5" s="19" t="s">
         <v>46</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>225</v>
+        <v>238</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="J5" s="19" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>50</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
@@ -6008,16 +6727,20 @@
         <v>0</v>
       </c>
       <c r="H6" s="31"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="33" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>55</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>1</v>
@@ -6029,16 +6752,23 @@
         <v>1200</v>
       </c>
       <c r="H7" s="31"/>
+      <c r="I7" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="J7" s="33" t="n">
+        <f aca="false">E7*J6</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>60</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>0.8</v>
@@ -6052,163 +6782,214 @@
       <c r="H8" s="31" t="n">
         <v>460</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="19" t="s">
-        <v>230</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>232</v>
+      <c r="I8" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="J8" s="33" t="n">
+        <f aca="false">E8*J6</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="E9" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F9" s="31" t="n">
+        <v>600</v>
+      </c>
+      <c r="G9" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="H9" s="31" t="n">
+        <v>377</v>
+      </c>
+      <c r="I9" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="J9" s="33" t="n">
+        <f aca="false">E9*J7</f>
+        <v>0.7</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D12" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="33" t="n">
-        <v>1</v>
+      <c r="B12" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="D13" s="33" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E13" s="33" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="F13" s="33" t="n">
-        <v>1.1</v>
+        <v>182</v>
+      </c>
+      <c r="D13" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D14" s="33" t="n">
+        <v>244</v>
+      </c>
+      <c r="D14" s="34" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E14" s="34" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="F14" s="34" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D15" s="34" t="n">
         <v>0.2723</v>
       </c>
-      <c r="E14" s="33" t="n">
+      <c r="E15" s="34" t="n">
         <v>0.2723</v>
       </c>
-      <c r="F14" s="33" t="n">
+      <c r="F15" s="34" t="n">
         <v>0.2723</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>233</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>234</v>
-      </c>
-      <c r="F17" s="19" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="D18" s="5" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="D16" s="34" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E16" s="34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F16" s="34" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="F18" s="31" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="F19" s="31" t="n">
-        <v>540</v>
+      <c r="C19" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="5" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="F20" s="31" t="n">
-        <v>800</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>227</v>
-      </c>
       <c r="E21" s="5" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="F21" s="31" t="n">
-        <v>50</v>
+        <v>540</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>167</v>
+        <v>241</v>
       </c>
       <c r="F22" s="31" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="F23" s="31" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F24" s="31" t="n">
         <v>40</v>
       </c>
     </row>

--- a/output/group_consolidation.xlsx
+++ b/output/group_consolidation.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="288">
   <si>
     <t xml:space="preserve">Illustrative Group</t>
   </si>
@@ -235,6 +235,15 @@
     <t xml:space="preserve">Translated from GBP to USD first. Combined line by line. The investment is eliminated against share capital and pre-acquisition reserves; any excess of cost is goodwill. Group effective interest is 70%; goodwill and NCI are measured on that interest. Goodwill is held in GBP and retranslated at the closing rate. The other 30% is a non-controlling interest, shown in equity, with its share of profit and translation differences.</t>
   </si>
   <si>
+    <t xml:space="preserve">Subsidiary Four (France)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subsidiary: 75% held by Subsidiary Two (Germany), so the parent controls it indirectly (sub-subsidiary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Translated from EUR to USD first. Combined line by line. The investment is eliminated against share capital and pre-acquisition reserves; any excess of cost is goodwill. Group effective interest is 60%; goodwill and NCI are measured on that interest. The EUR holding company's investment is removed at the closing rate and its translation difference reversed. Goodwill is held in EUR and retranslated at the closing rate. The other 40% is a non-controlling interest, shown in equity, with its share of profit and translation differences.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Associate One (UAE)</t>
   </si>
   <si>
@@ -280,7 +289,7 @@
     <t xml:space="preserve">IFRS 10.6-7, B35</t>
   </si>
   <si>
-    <t xml:space="preserve">An investor controls an investee when it has power over it, is exposed to variable returns from it and can use its power to affect those returns. Subsidiaries One and Two are controlled directly through a majority of the voting rights, and Subsidiary Three through Subsidiary One. Each is consolidated from the date control was obtained.</t>
+    <t xml:space="preserve">An investor controls an investee when it has power over it, is exposed to variable returns from it and can use its power to affect those returns. Subsidiaries One and Two are controlled directly through a majority of the voting rights, Subsidiary Three through Subsidiary One and Subsidiary Four through Subsidiary Two. Each is consolidated from the date control was obtained.</t>
   </si>
   <si>
     <t xml:space="preserve">2. Significant influence (associates)</t>
@@ -343,10 +352,19 @@
     <t xml:space="preserve">IFRS 10.B86, Appendix A; IFRS 3.19, 3.32</t>
   </si>
   <si>
-    <t xml:space="preserve">Subsidiary Three is 70% owned by Subsidiary One, which the parent owns in full. Control passes down the chain, so Subsidiary Three is the parent's subsidiary and is consolidated in full. Goodwill and NCI use the group's effective interest (100% x 70% = 70%). If the holder were not wholly owned, its NCI's share of the cost of investment would be deducted from NCI, and NCI would also include the holder's NCI's indirect share of the sub-subsidiary.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9. Intragroup transactions</t>
+    <t xml:space="preserve">Control passes down the chain, so a subsidiary of a subsidiary is the parent's subsidiary and is consolidated in full. Goodwill and NCI use the group's effective interest: Subsidiary Three 100% x 70% = 70%, Subsidiary Four 80% x 75% = 60%. NCI in Subsidiary Four is 40%: the 25% direct minority plus the Subsidiary Two minority's 20% x 75% indirect share, less that minority's 20% share of Subsidiary Two's cost of investment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. Foreign holding company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAS 21.39, 21.47; IFRS 10.B86(b)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subsidiary Two holds Subsidiary Four in euros. Its investment is in its translated trial balance at the closing rate, so that amount is eliminated. Goodwill is measured with the cost at the historical rate, and the translation difference on the investment is reversed: the group's share from the translation reserve and the Subsidiary Two minority's share from NCI.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10. Intragroup transactions</t>
   </si>
   <si>
     <t xml:space="preserve">IFRS 10.B86(c)</t>
@@ -355,7 +373,7 @@
     <t xml:space="preserve">Intragroup balances, sales, purchases and unrealised profit in closing inventory are eliminated in full. The unrealised profit is charged to the selling entity; the seller is 100% owned, so NCI is not affected.</t>
   </si>
   <si>
-    <t xml:space="preserve">10. Equity method (associates)</t>
+    <t xml:space="preserve">11. Equity method (associates)</t>
   </si>
   <si>
     <t xml:space="preserve">IAS 28.10, 28.16</t>
@@ -364,7 +382,7 @@
     <t xml:space="preserve">An associate is not combined line by line. The investment is recognised at cost and then increased or decreased by the group's share of the associate's profit or loss after acquisition. Dividends received reduce the carrying amount instead of being income, so the parent's dividend income is reversed.</t>
   </si>
   <si>
-    <t xml:space="preserve">11. Goodwill on associates</t>
+    <t xml:space="preserve">12. Goodwill on associates</t>
   </si>
   <si>
     <t xml:space="preserve">IAS 28.32, 28.42</t>
@@ -373,7 +391,7 @@
     <t xml:space="preserve">The excess of cost over the group's share of the associate's net assets is included in the carrying amount of the investment. It is not shown separately, not amortised and not tested for impairment on its own.</t>
   </si>
   <si>
-    <t xml:space="preserve">12. Transactions with associates</t>
+    <t xml:space="preserve">13. Transactions with associates</t>
   </si>
   <si>
     <t xml:space="preserve">IAS 28.28-29</t>
@@ -382,7 +400,7 @@
     <t xml:space="preserve">Only the group's share of unrealised profit on sales between the group and an associate is eliminated. For a sale to the associate (downstream) it reduces the investment; for a purchase from the associate (upstream) it reduces group inventory. Balances with associates are not eliminated, because associates are outside the group.</t>
   </si>
   <si>
-    <t xml:space="preserve">13. Impairment of associates</t>
+    <t xml:space="preserve">14. Impairment of associates</t>
   </si>
   <si>
     <t xml:space="preserve">IAS 28.40-43; IAS 36</t>
@@ -391,7 +409,7 @@
     <t xml:space="preserve">After applying the equity method, the group checks for objective evidence of impairment. If there is, the whole carrying amount is tested as a single asset under IAS 36 and any loss reduces the investment. Associate Two carries an impairment loss.</t>
   </si>
   <si>
-    <t xml:space="preserve">14. Losses of associates</t>
+    <t xml:space="preserve">15. Losses of associates</t>
   </si>
   <si>
     <t xml:space="preserve">IAS 28.38-39</t>
@@ -400,7 +418,7 @@
     <t xml:space="preserve">If the group's share of losses equals or exceeds its interest, it stops recognising further losses unless it has an obligation to fund them. Not triggered here.</t>
   </si>
   <si>
-    <t xml:space="preserve">15. Presentation</t>
+    <t xml:space="preserve">16. Presentation</t>
   </si>
   <si>
     <t xml:space="preserve">IAS 1.54(e), 1.82(c), 1.81B; IFRS 10.22</t>
@@ -409,7 +427,7 @@
     <t xml:space="preserve">Investments in associates and the share of their profit are separate line items. Profit and equity are split between owners of the parent and NCI.</t>
   </si>
   <si>
-    <t xml:space="preserve">16. Disclosure</t>
+    <t xml:space="preserve">17. Disclosure</t>
   </si>
   <si>
     <t xml:space="preserve">IFRS 12.21, B12-B14</t>
@@ -418,7 +436,7 @@
     <t xml:space="preserve">Summarised financial information for each material associate and a reconciliation to its carrying amount (shown on the Associates sheet).</t>
   </si>
   <si>
-    <t xml:space="preserve">17. IFRS 18 (from 2027)</t>
+    <t xml:space="preserve">18. IFRS 18 (from 2027)</t>
   </si>
   <si>
     <t xml:space="preserve">IFRS 18</t>
@@ -451,6 +469,9 @@
     <t xml:space="preserve">SUB3 (USD)</t>
   </si>
   <si>
+    <t xml:space="preserve">SUB4 (USD)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Aggregate</t>
   </si>
   <si>
@@ -517,6 +538,12 @@
     <t xml:space="preserve">NCI share of Subsidiary Three (UK) post-acquisition reserves</t>
   </si>
   <si>
+    <t xml:space="preserve">Investment in Subsidiary Four (France)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NCI share of Subsidiary Four (France) post-acquisition reserves</t>
+  </si>
+  <si>
     <t xml:space="preserve">Intercompany balance: Parent owes Sub One for goods bought</t>
   </si>
   <si>
@@ -703,6 +730,15 @@
     <t xml:space="preserve">SUB3 USD</t>
   </si>
   <si>
+    <t xml:space="preserve">SUB4 local</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUB4 rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUB4 USD</t>
+  </si>
+  <si>
     <t xml:space="preserve">Assets and liabilities at closing rate, income and expenses at average rate, share capital at historical rate, opening retained earnings at the USD amount carried forward. The translation reserve balances the translated trial balance.</t>
   </si>
   <si>
@@ -721,6 +757,9 @@
     <t xml:space="preserve">SUB3 (GBP)</t>
   </si>
   <si>
+    <t xml:space="preserve">SUB4 (EUR)</t>
+  </si>
+  <si>
     <t xml:space="preserve">A</t>
   </si>
   <si>
@@ -739,7 +778,7 @@
     <t xml:space="preserve">Group structure, exchange rates and intercompany data</t>
   </si>
   <si>
-    <t xml:space="preserve">Investment cost (USD)</t>
+    <t xml:space="preserve">Investment cost (holder's currency)</t>
   </si>
   <si>
     <t xml:space="preserve">Pre-acq. retained earnings (local)</t>
@@ -770,6 +809,9 @@
   </si>
   <si>
     <t xml:space="preserve">GBP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUB4</t>
   </si>
   <si>
     <t xml:space="preserve">Closing</t>
@@ -1444,8 +1486,8 @@
         <v>4</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">-(Consolidation!J21+Consolidation!J22)</f>
-        <v>24172</v>
+        <f aca="false">-(Consolidation!K21+Consolidation!K22)</f>
+        <v>25480</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1453,8 +1495,8 @@
         <v>5</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">-(Consolidation!J25+Consolidation!J26)</f>
-        <v>-14340</v>
+        <f aca="false">-(Consolidation!K25+Consolidation!K26)</f>
+        <v>-15168.4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1463,7 +1505,7 @@
       </c>
       <c r="C8" s="8" t="n">
         <f aca="false">C6+C7</f>
-        <v>9832</v>
+        <v>10311.6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1471,8 +1513,8 @@
         <v>7</v>
       </c>
       <c r="C9" s="6" t="n">
-        <f aca="false">-Consolidation!J27</f>
-        <v>-5306</v>
+        <f aca="false">-Consolidation!K27</f>
+        <v>-5556.7</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1481,7 +1523,7 @@
       </c>
       <c r="C10" s="8" t="n">
         <f aca="false">C8+C9</f>
-        <v>4526</v>
+        <v>4754.9</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1489,7 +1531,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="6" t="n">
-        <f aca="false">-Consolidation!J24</f>
+        <f aca="false">-Consolidation!K24</f>
         <v>259.718</v>
       </c>
     </row>
@@ -1498,7 +1540,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="6" t="n">
-        <f aca="false">-Consolidation!J23</f>
+        <f aca="false">-Consolidation!K23</f>
         <v>-0</v>
       </c>
     </row>
@@ -1507,8 +1549,8 @@
         <v>11</v>
       </c>
       <c r="C13" s="6" t="n">
-        <f aca="false">-Consolidation!J28</f>
-        <v>-398.3</v>
+        <f aca="false">-Consolidation!K28</f>
+        <v>-409.2</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1517,7 +1559,7 @@
       </c>
       <c r="C14" s="8" t="n">
         <f aca="false">SUM(C10:C13)</f>
-        <v>4387.418</v>
+        <v>4605.418</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1525,8 +1567,8 @@
         <v>13</v>
       </c>
       <c r="C15" s="6" t="n">
-        <f aca="false">-Consolidation!J29</f>
-        <v>-942.2</v>
+        <f aca="false">-Consolidation!K29</f>
+        <v>-996.7</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1535,7 +1577,7 @@
       </c>
       <c r="C16" s="9" t="n">
         <f aca="false">C14+C15</f>
-        <v>3445.218</v>
+        <v>3608.718</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1544,7 +1586,7 @@
       </c>
       <c r="C18" s="6" t="n">
         <f aca="false">C16-C19</f>
-        <v>3270.838</v>
+        <v>3368.938</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1552,8 +1594,8 @@
         <v>16</v>
       </c>
       <c r="C19" s="6" t="n">
-        <f aca="false">(1-Inputs!$J$7)*-SUM(Translation!I18:I25)+(1-Inputs!$J$8)*-SUM(Translation!L18:L25)+(1-Inputs!$J$9)*-SUM(Translation!O18:O25)</f>
-        <v>174.38</v>
+        <f aca="false">(1-Inputs!$J$7)*-SUM(Translation!I18:I25)+(1-Inputs!$J$8)*-SUM(Translation!L18:L25)+(1-Inputs!$J$9)*-SUM(Translation!O18:O25)+(1-Inputs!$J$10)*-SUM(Translation!R18:R25)</f>
+        <v>239.78</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1597,7 +1639,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1607,79 +1649,79 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">ROUND(ABS('Trial Balances'!E26)+ABS('Trial Balances'!F26)+ABS('Trial Balances'!G26)+ABS('Trial Balances'!H26),2)</f>
+        <f aca="false">ROUND(ABS('Trial Balances'!E26)+ABS('Trial Balances'!F26)+ABS('Trial Balances'!G26)+ABS('Trial Balances'!H26)+ABS('Trial Balances'!I26),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">ROUND(ABS(Eliminations!F55),2)</f>
+        <f aca="false">ROUND(ABS(Eliminations!F65),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="C8" s="6" t="n">
-        <f aca="false">ROUND(ABS(Consolidation!J30),2)</f>
+        <f aca="false">ROUND(ABS(Consolidation!K30),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="C9" s="6" t="n">
-        <f aca="false">ROUND(ABS(Consolidation!J8)+ABS(Consolidation!J15),2)</f>
+        <f aca="false">ROUND(ABS(Consolidation!K8)+ABS(Consolidation!K15),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="C10" s="6" t="n">
-        <f aca="false">ROUND(ABS(Consolidation!J22)+ABS(Consolidation!J26),2)</f>
+        <f aca="false">ROUND(ABS(Consolidation!K22)+ABS(Consolidation!K26),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="C11" s="6" t="n">
-        <f aca="false">ROUND(ABS(Consolidation!J11),2)</f>
+        <f aca="false">ROUND(ABS(Consolidation!K11),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="C12" s="6" t="n">
-        <f aca="false">ROUND(ABS(Consolidation!J23),2)</f>
+        <f aca="false">ROUND(ABS(Consolidation!K23),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="C13" s="6" t="n">
-        <f aca="false">ROUND(ABS(Consolidation!J12-Associates!F31),2)</f>
+        <f aca="false">ROUND(ABS(Consolidation!K12-Associates!F31),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="C14" s="6" t="n">
         <f aca="false">ROUND(ABS(Associates!F39),2)</f>
@@ -1688,7 +1730,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="C15" s="6" t="n">
         <f aca="false">ROUND(ABS('Consolidated BS'!C29),2)</f>
@@ -1697,7 +1739,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="7" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="C17" s="7" t="str">
         <f aca="false">IF(SUM(C6:C15)=0,"OK","ERROR")</f>
@@ -1754,8 +1796,8 @@
         <v>20</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">Consolidation!J13</f>
-        <v>576.2</v>
+        <f aca="false">Consolidation!K13</f>
+        <v>641</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1763,8 +1805,8 @@
         <v>21</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">Consolidation!J10</f>
-        <v>11587</v>
+        <f aca="false">Consolidation!K10</f>
+        <v>12343</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1772,7 +1814,7 @@
         <v>22</v>
       </c>
       <c r="C8" s="6" t="n">
-        <f aca="false">Consolidation!J12</f>
+        <f aca="false">Consolidation!K12</f>
         <v>1838.563</v>
       </c>
     </row>
@@ -1782,7 +1824,7 @@
       </c>
       <c r="C9" s="8" t="n">
         <f aca="false">SUM(C6:C8)</f>
-        <v>14001.763</v>
+        <v>14822.563</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1790,8 +1832,8 @@
         <v>24</v>
       </c>
       <c r="C10" s="6" t="n">
-        <f aca="false">Consolidation!J9</f>
-        <v>2918.6</v>
+        <f aca="false">Consolidation!K9</f>
+        <v>3080.6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1799,8 +1841,8 @@
         <v>25</v>
       </c>
       <c r="C11" s="6" t="n">
-        <f aca="false">Consolidation!J7</f>
-        <v>4073.5</v>
+        <f aca="false">Consolidation!K7</f>
+        <v>4289.5</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1808,7 +1850,7 @@
         <v>26</v>
       </c>
       <c r="C12" s="6" t="n">
-        <f aca="false">Consolidation!J8</f>
+        <f aca="false">Consolidation!K8</f>
         <v>0</v>
       </c>
     </row>
@@ -1817,8 +1859,8 @@
         <v>27</v>
       </c>
       <c r="C13" s="6" t="n">
-        <f aca="false">Consolidation!J6</f>
-        <v>2566.89</v>
+        <f aca="false">Consolidation!K6</f>
+        <v>2696.49</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1827,7 +1869,7 @@
       </c>
       <c r="C14" s="8" t="n">
         <f aca="false">SUM(C10:C13)</f>
-        <v>9558.99</v>
+        <v>10066.59</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1836,7 +1878,7 @@
       </c>
       <c r="C15" s="9" t="n">
         <f aca="false">C9+C14</f>
-        <v>23560.753</v>
+        <v>24889.153</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1844,7 +1886,7 @@
         <v>30</v>
       </c>
       <c r="C17" s="6" t="n">
-        <f aca="false">-Consolidation!J17</f>
+        <f aca="false">-Consolidation!K17</f>
         <v>5000</v>
       </c>
     </row>
@@ -1853,8 +1895,8 @@
         <v>31</v>
       </c>
       <c r="C18" s="6" t="n">
-        <f aca="false">-Consolidation!J18+'Consolidated IS'!C18</f>
-        <v>7097.773</v>
+        <f aca="false">-Consolidation!K18+'Consolidated IS'!C18</f>
+        <v>7274.473</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1862,8 +1904,8 @@
         <v>32</v>
       </c>
       <c r="C19" s="6" t="n">
-        <f aca="false">-Consolidation!J19</f>
-        <v>-15.0300000000001</v>
+        <f aca="false">-Consolidation!K19</f>
+        <v>-16.77</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1872,7 +1914,7 @@
       </c>
       <c r="C20" s="8" t="n">
         <f aca="false">SUM(C17:C19)</f>
-        <v>12082.743</v>
+        <v>12257.703</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1880,8 +1922,8 @@
         <v>34</v>
       </c>
       <c r="C21" s="6" t="n">
-        <f aca="false">-Consolidation!J20+'Consolidated IS'!C19</f>
-        <v>784.41</v>
+        <f aca="false">-Consolidation!K20+'Consolidated IS'!C19</f>
+        <v>1019.85</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1890,7 +1932,7 @@
       </c>
       <c r="C22" s="8" t="n">
         <f aca="false">C20+C21</f>
-        <v>12867.153</v>
+        <v>13277.553</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1898,8 +1940,8 @@
         <v>36</v>
       </c>
       <c r="C23" s="6" t="n">
-        <f aca="false">-Consolidation!J16</f>
-        <v>7629</v>
+        <f aca="false">-Consolidation!K16</f>
+        <v>8385</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1907,8 +1949,8 @@
         <v>37</v>
       </c>
       <c r="C24" s="6" t="n">
-        <f aca="false">-Consolidation!J14</f>
-        <v>3064.6</v>
+        <f aca="false">-Consolidation!K14</f>
+        <v>3226.6</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1916,7 +1958,7 @@
         <v>38</v>
       </c>
       <c r="C25" s="6" t="n">
-        <f aca="false">-Consolidation!J15</f>
+        <f aca="false">-Consolidation!K15</f>
         <v>-0</v>
       </c>
     </row>
@@ -1926,7 +1968,7 @@
       </c>
       <c r="C26" s="8" t="n">
         <f aca="false">SUM(C23:C25)</f>
-        <v>10693.6</v>
+        <v>11611.6</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1935,7 +1977,7 @@
       </c>
       <c r="C27" s="9" t="n">
         <f aca="false">C22+C26</f>
-        <v>23560.753</v>
+        <v>24889.153</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1963,7 +2005,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:G34"/>
+  <dimension ref="B1:G36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -2091,7 +2133,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="69" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="12" t="s">
         <v>68</v>
       </c>
@@ -2099,74 +2141,81 @@
         <v>69</v>
       </c>
       <c r="D10" s="15" t="n">
+        <f aca="false">Inputs!$E$10</f>
+        <v>0.75</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="69" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" s="15" t="n">
         <f aca="false">Associates!D8</f>
         <v>0.3</v>
       </c>
-      <c r="E10" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="69" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="12" t="s">
+      <c r="E11" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="F11" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="G11" s="13" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="69" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" s="15" t="n">
         <f aca="false">Associates!E8</f>
         <v>0.25</v>
       </c>
-      <c r="E11" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="2" t="s">
-        <v>77</v>
+      <c r="E12" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D15" s="16" t="s">
+      <c r="B15" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-    </row>
-    <row r="16" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="12" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-    </row>
-    <row r="17" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+    </row>
+    <row r="17" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="12" t="s">
         <v>84</v>
       </c>
@@ -2194,7 +2243,7 @@
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
     </row>
-    <row r="19" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="12" t="s">
         <v>90</v>
       </c>
@@ -2208,7 +2257,7 @@
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
     </row>
-    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="12" t="s">
         <v>93</v>
       </c>
@@ -2236,7 +2285,7 @@
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
     </row>
-    <row r="22" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="12" t="s">
         <v>99</v>
       </c>
@@ -2250,7 +2299,7 @@
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
     </row>
-    <row r="23" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="12" t="s">
         <v>102</v>
       </c>
@@ -2264,7 +2313,7 @@
       <c r="F23" s="18"/>
       <c r="G23" s="18"/>
     </row>
-    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="12" t="s">
         <v>105</v>
       </c>
@@ -2334,7 +2383,7 @@
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
     </row>
-    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="12" t="s">
         <v>120</v>
       </c>
@@ -2376,7 +2425,7 @@
       <c r="F31" s="18"/>
       <c r="G31" s="18"/>
     </row>
-    <row r="32" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="12" t="s">
         <v>129</v>
       </c>
@@ -2390,14 +2439,41 @@
       <c r="F32" s="18"/>
       <c r="G32" s="18"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="3" t="s">
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="12" t="s">
         <v>132</v>
       </c>
+      <c r="C33" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+    </row>
+    <row r="34" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="3" t="s">
+        <v>138</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="D15:G15"/>
+  <mergeCells count="19">
     <mergeCell ref="D16:G16"/>
     <mergeCell ref="D17:G17"/>
     <mergeCell ref="D18:G18"/>
@@ -2415,6 +2491,8 @@
     <mergeCell ref="D30:G30"/>
     <mergeCell ref="D31:G31"/>
     <mergeCell ref="D32:G32"/>
+    <mergeCell ref="D33:G33"/>
+    <mergeCell ref="D34:G34"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2431,13 +2509,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:J30"/>
+  <dimension ref="B1:K30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="4" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="4" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2447,7 +2525,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2457,31 +2535,34 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="J5" s="19" t="s">
-        <v>142</v>
+        <v>148</v>
+      </c>
+      <c r="K5" s="19" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2507,17 +2588,21 @@
         <f aca="false">Translation!O6</f>
         <v>203.2</v>
       </c>
-      <c r="H6" s="6" t="n">
-        <f aca="false">SUM(D6:G6)</f>
-        <v>2566.89</v>
-      </c>
-      <c r="I6" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B6)</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="21" t="n">
-        <f aca="false">H6+I6</f>
-        <v>2566.89</v>
+      <c r="H6" s="20" t="n">
+        <f aca="false">Translation!R6</f>
+        <v>129.6</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <f aca="false">SUM(D6:H6)</f>
+        <v>2696.49</v>
+      </c>
+      <c r="J6" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$64,Eliminations!$D$6:$D$64,$B6)</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="21" t="n">
+        <f aca="false">I6+J6</f>
+        <v>2696.49</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2543,17 +2628,21 @@
         <f aca="false">Translation!O7</f>
         <v>317.5</v>
       </c>
-      <c r="H7" s="6" t="n">
-        <f aca="false">SUM(D7:G7)</f>
-        <v>4073.5</v>
-      </c>
-      <c r="I7" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B7)</f>
-        <v>0</v>
-      </c>
-      <c r="J7" s="21" t="n">
-        <f aca="false">H7+I7</f>
-        <v>4073.5</v>
+      <c r="H7" s="20" t="n">
+        <f aca="false">Translation!R7</f>
+        <v>216</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <f aca="false">SUM(D7:H7)</f>
+        <v>4289.5</v>
+      </c>
+      <c r="J7" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$64,Eliminations!$D$6:$D$64,$B7)</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="21" t="n">
+        <f aca="false">I7+J7</f>
+        <v>4289.5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2561,7 +2650,7 @@
         <v>1150</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="D8" s="20" t="n">
         <f aca="false">Translation!F8</f>
@@ -2579,16 +2668,20 @@
         <f aca="false">Translation!O8</f>
         <v>0</v>
       </c>
-      <c r="H8" s="6" t="n">
-        <f aca="false">SUM(D8:G8)</f>
+      <c r="H8" s="20" t="n">
+        <f aca="false">Translation!R8</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <f aca="false">SUM(D8:H8)</f>
         <v>690</v>
       </c>
-      <c r="I8" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B8)</f>
+      <c r="J8" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$64,Eliminations!$D$6:$D$64,$B8)</f>
         <v>-690</v>
       </c>
-      <c r="J8" s="21" t="n">
-        <f aca="false">H8+I8</f>
+      <c r="K8" s="21" t="n">
+        <f aca="false">I8+J8</f>
         <v>0</v>
       </c>
     </row>
@@ -2615,17 +2708,21 @@
         <f aca="false">Translation!O9</f>
         <v>228.6</v>
       </c>
-      <c r="H9" s="6" t="n">
-        <f aca="false">SUM(D9:G9)</f>
-        <v>2968.6</v>
-      </c>
-      <c r="I9" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B9)</f>
+      <c r="H9" s="20" t="n">
+        <f aca="false">Translation!R9</f>
+        <v>162</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <f aca="false">SUM(D9:H9)</f>
+        <v>3130.6</v>
+      </c>
+      <c r="J9" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$64,Eliminations!$D$6:$D$64,$B9)</f>
         <v>-50</v>
       </c>
-      <c r="J9" s="21" t="n">
-        <f aca="false">H9+I9</f>
-        <v>2918.6</v>
+      <c r="K9" s="21" t="n">
+        <f aca="false">I9+J9</f>
+        <v>3080.6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2651,17 +2748,21 @@
         <f aca="false">Translation!O10</f>
         <v>1143</v>
       </c>
-      <c r="H10" s="6" t="n">
-        <f aca="false">SUM(D10:G10)</f>
-        <v>11587</v>
-      </c>
-      <c r="I10" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B10)</f>
-        <v>0</v>
-      </c>
-      <c r="J10" s="21" t="n">
-        <f aca="false">H10+I10</f>
-        <v>11587</v>
+      <c r="H10" s="20" t="n">
+        <f aca="false">Translation!R10</f>
+        <v>756</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <f aca="false">SUM(D10:H10)</f>
+        <v>12343</v>
+      </c>
+      <c r="J10" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$64,Eliminations!$D$6:$D$64,$B10)</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="21" t="n">
+        <f aca="false">I10+J10</f>
+        <v>12343</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2669,7 +2770,7 @@
         <v>1600</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="D11" s="20" t="n">
         <f aca="false">Translation!F11</f>
@@ -2681,22 +2782,26 @@
       </c>
       <c r="F11" s="20" t="n">
         <f aca="false">Translation!L11</f>
-        <v>0</v>
+        <v>486</v>
       </c>
       <c r="G11" s="20" t="n">
         <f aca="false">Translation!O11</f>
         <v>0</v>
       </c>
-      <c r="H11" s="6" t="n">
-        <f aca="false">SUM(D11:G11)</f>
-        <v>4180</v>
-      </c>
-      <c r="I11" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B11)</f>
-        <v>-4180</v>
-      </c>
-      <c r="J11" s="21" t="n">
-        <f aca="false">H11+I11</f>
+      <c r="H11" s="20" t="n">
+        <f aca="false">Translation!R11</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <f aca="false">SUM(D11:H11)</f>
+        <v>4666</v>
+      </c>
+      <c r="J11" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$64,Eliminations!$D$6:$D$64,$B11)</f>
+        <v>-4666</v>
+      </c>
+      <c r="K11" s="21" t="n">
+        <f aca="false">I11+J11</f>
         <v>0</v>
       </c>
     </row>
@@ -2705,7 +2810,7 @@
         <v>1650</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="D12" s="20" t="n">
         <f aca="false">Translation!F12</f>
@@ -2723,16 +2828,20 @@
         <f aca="false">Translation!O12</f>
         <v>0</v>
       </c>
-      <c r="H12" s="6" t="n">
-        <f aca="false">SUM(D12:G12)</f>
+      <c r="H12" s="20" t="n">
+        <f aca="false">Translation!R12</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <f aca="false">SUM(D12:H12)</f>
         <v>1500</v>
       </c>
-      <c r="I12" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B12)</f>
+      <c r="J12" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$64,Eliminations!$D$6:$D$64,$B12)</f>
         <v>338.563</v>
       </c>
-      <c r="J12" s="21" t="n">
-        <f aca="false">H12+I12</f>
+      <c r="K12" s="21" t="n">
+        <f aca="false">I12+J12</f>
         <v>1838.563</v>
       </c>
     </row>
@@ -2755,17 +2864,20 @@
       <c r="G13" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="6" t="n">
-        <f aca="false">SUM(D13:G13)</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B13)</f>
-        <v>576.2</v>
-      </c>
-      <c r="J13" s="21" t="n">
-        <f aca="false">H13+I13</f>
-        <v>576.2</v>
+      <c r="H13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <f aca="false">SUM(D13:H13)</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$64,Eliminations!$D$6:$D$64,$B13)</f>
+        <v>641</v>
+      </c>
+      <c r="K13" s="21" t="n">
+        <f aca="false">I13+J13</f>
+        <v>641</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2791,17 +2903,21 @@
         <f aca="false">Translation!O13</f>
         <v>-228.6</v>
       </c>
-      <c r="H14" s="6" t="n">
-        <f aca="false">SUM(D14:G14)</f>
-        <v>-3064.6</v>
-      </c>
-      <c r="I14" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B14)</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="21" t="n">
-        <f aca="false">H14+I14</f>
-        <v>-3064.6</v>
+      <c r="H14" s="20" t="n">
+        <f aca="false">Translation!R13</f>
+        <v>-162</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <f aca="false">SUM(D14:H14)</f>
+        <v>-3226.6</v>
+      </c>
+      <c r="J14" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$64,Eliminations!$D$6:$D$64,$B14)</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="21" t="n">
+        <f aca="false">I14+J14</f>
+        <v>-3226.6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2809,7 +2925,7 @@
         <v>2150</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D15" s="20" t="n">
         <f aca="false">Translation!F14</f>
@@ -2827,16 +2943,20 @@
         <f aca="false">Translation!O14</f>
         <v>0</v>
       </c>
-      <c r="H15" s="6" t="n">
-        <f aca="false">SUM(D15:G15)</f>
+      <c r="H15" s="20" t="n">
+        <f aca="false">Translation!R14</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <f aca="false">SUM(D15:H15)</f>
         <v>-690</v>
       </c>
-      <c r="I15" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B15)</f>
+      <c r="J15" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$64,Eliminations!$D$6:$D$64,$B15)</f>
         <v>690</v>
       </c>
-      <c r="J15" s="21" t="n">
-        <f aca="false">H15+I15</f>
+      <c r="K15" s="21" t="n">
+        <f aca="false">I15+J15</f>
         <v>0</v>
       </c>
     </row>
@@ -2857,23 +2977,27 @@
       </c>
       <c r="F16" s="20" t="n">
         <f aca="false">Translation!L15</f>
-        <v>-648</v>
+        <v>-1134</v>
       </c>
       <c r="G16" s="20" t="n">
         <f aca="false">Translation!O15</f>
         <v>-381</v>
       </c>
-      <c r="H16" s="6" t="n">
-        <f aca="false">SUM(D16:G16)</f>
-        <v>-7629</v>
-      </c>
-      <c r="I16" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B16)</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="21" t="n">
-        <f aca="false">H16+I16</f>
-        <v>-7629</v>
+      <c r="H16" s="20" t="n">
+        <f aca="false">Translation!R15</f>
+        <v>-270</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <f aca="false">SUM(D16:H16)</f>
+        <v>-8385</v>
+      </c>
+      <c r="J16" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$64,Eliminations!$D$6:$D$64,$B16)</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="21" t="n">
+        <f aca="false">I16+J16</f>
+        <v>-8385</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2899,16 +3023,20 @@
         <f aca="false">Translation!O16</f>
         <v>-625</v>
       </c>
-      <c r="H17" s="6" t="n">
-        <f aca="false">SUM(D17:G17)</f>
-        <v>-7725</v>
-      </c>
-      <c r="I17" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B17)</f>
-        <v>2725</v>
-      </c>
-      <c r="J17" s="21" t="n">
-        <f aca="false">H17+I17</f>
+      <c r="H17" s="20" t="n">
+        <f aca="false">Translation!R16</f>
+        <v>-440</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <f aca="false">SUM(D17:H17)</f>
+        <v>-8165</v>
+      </c>
+      <c r="J17" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$64,Eliminations!$D$6:$D$64,$B17)</f>
+        <v>3165</v>
+      </c>
+      <c r="K17" s="21" t="n">
+        <f aca="false">I17+J17</f>
         <v>-5000</v>
       </c>
     </row>
@@ -2917,7 +3045,7 @@
         <v>3100</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D18" s="20" t="n">
         <f aca="false">Translation!F17</f>
@@ -2935,17 +3063,21 @@
         <f aca="false">Translation!O17</f>
         <v>-377</v>
       </c>
-      <c r="H18" s="6" t="n">
-        <f aca="false">SUM(D18:G18)</f>
-        <v>-5097</v>
-      </c>
-      <c r="I18" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B18)</f>
-        <v>1270.065</v>
-      </c>
-      <c r="J18" s="21" t="n">
-        <f aca="false">H18+I18</f>
-        <v>-3826.935</v>
+      <c r="H18" s="20" t="n">
+        <f aca="false">Translation!R17</f>
+        <v>-241</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <f aca="false">SUM(D18:H18)</f>
+        <v>-5338</v>
+      </c>
+      <c r="J18" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$64,Eliminations!$D$6:$D$64,$B18)</f>
+        <v>1432.465</v>
+      </c>
+      <c r="K18" s="21" t="n">
+        <f aca="false">I18+J18</f>
+        <v>-3905.535</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2965,23 +3097,27 @@
       </c>
       <c r="F19" s="20" t="n">
         <f aca="false">Translation!L26</f>
-        <v>30.7000000000002</v>
+        <v>30.7000000000001</v>
       </c>
       <c r="G19" s="20" t="n">
         <f aca="false">Translation!O26</f>
         <v>-11.9</v>
       </c>
-      <c r="H19" s="6" t="n">
-        <f aca="false">SUM(D19:G19)</f>
-        <v>18.8000000000002</v>
-      </c>
-      <c r="I19" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B19)</f>
-        <v>-3.77000000000003</v>
-      </c>
-      <c r="J19" s="21" t="n">
-        <f aca="false">H19+I19</f>
-        <v>15.0300000000001</v>
+      <c r="H19" s="20" t="n">
+        <f aca="false">Translation!R26</f>
+        <v>12.8999999999999</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <f aca="false">SUM(D19:H19)</f>
+        <v>31.7</v>
+      </c>
+      <c r="J19" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$64,Eliminations!$D$6:$D$64,$B19)</f>
+        <v>-14.93</v>
+      </c>
+      <c r="K19" s="21" t="n">
+        <f aca="false">I19+J19</f>
+        <v>16.77</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3003,17 +3139,20 @@
       <c r="G20" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="6" t="n">
-        <f aca="false">SUM(D20:G20)</f>
-        <v>0</v>
-      </c>
-      <c r="I20" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B20)</f>
-        <v>-610.03</v>
-      </c>
-      <c r="J20" s="21" t="n">
-        <f aca="false">H20+I20</f>
-        <v>-610.03</v>
+      <c r="H20" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <f aca="false">SUM(D20:H20)</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$64,Eliminations!$D$6:$D$64,$B20)</f>
+        <v>-780.07</v>
+      </c>
+      <c r="K20" s="21" t="n">
+        <f aca="false">I20+J20</f>
+        <v>-780.07</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3039,17 +3178,21 @@
         <f aca="false">Translation!O18</f>
         <v>-2048</v>
       </c>
-      <c r="H21" s="6" t="n">
-        <f aca="false">SUM(D21:G21)</f>
-        <v>-24172</v>
-      </c>
-      <c r="I21" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B21)</f>
-        <v>0</v>
-      </c>
-      <c r="J21" s="21" t="n">
-        <f aca="false">H21+I21</f>
-        <v>-24172</v>
+      <c r="H21" s="20" t="n">
+        <f aca="false">Translation!R18</f>
+        <v>-1308</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <f aca="false">SUM(D21:H21)</f>
+        <v>-25480</v>
+      </c>
+      <c r="J21" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$64,Eliminations!$D$6:$D$64,$B21)</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="21" t="n">
+        <f aca="false">I21+J21</f>
+        <v>-25480</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3057,7 +3200,7 @@
         <v>4050</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="D22" s="20" t="n">
         <f aca="false">Translation!F19</f>
@@ -3075,16 +3218,20 @@
         <f aca="false">Translation!O19</f>
         <v>0</v>
       </c>
-      <c r="H22" s="6" t="n">
-        <f aca="false">SUM(D22:G22)</f>
+      <c r="H22" s="20" t="n">
+        <f aca="false">Translation!R19</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <f aca="false">SUM(D22:H22)</f>
         <v>-800</v>
       </c>
-      <c r="I22" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B22)</f>
+      <c r="J22" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$64,Eliminations!$D$6:$D$64,$B22)</f>
         <v>800</v>
       </c>
-      <c r="J22" s="21" t="n">
-        <f aca="false">H22+I22</f>
+      <c r="K22" s="21" t="n">
+        <f aca="false">I22+J22</f>
         <v>0</v>
       </c>
     </row>
@@ -3093,7 +3240,7 @@
         <v>4100</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="D23" s="20" t="n">
         <f aca="false">Translation!F20</f>
@@ -3111,16 +3258,20 @@
         <f aca="false">Translation!O20</f>
         <v>0</v>
       </c>
-      <c r="H23" s="6" t="n">
-        <f aca="false">SUM(D23:G23)</f>
+      <c r="H23" s="20" t="n">
+        <f aca="false">Translation!R20</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <f aca="false">SUM(D23:H23)</f>
         <v>-131.69</v>
       </c>
-      <c r="I23" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B23)</f>
+      <c r="J23" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$64,Eliminations!$D$6:$D$64,$B23)</f>
         <v>131.69</v>
       </c>
-      <c r="J23" s="21" t="n">
-        <f aca="false">H23+I23</f>
+      <c r="K23" s="21" t="n">
+        <f aca="false">I23+J23</f>
         <v>0</v>
       </c>
     </row>
@@ -3129,7 +3280,7 @@
         <v>4200</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D24" s="20" t="n">
         <v>0</v>
@@ -3143,16 +3294,19 @@
       <c r="G24" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="6" t="n">
-        <f aca="false">SUM(D24:G24)</f>
-        <v>0</v>
-      </c>
-      <c r="I24" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B24)</f>
+      <c r="H24" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <f aca="false">SUM(D24:H24)</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$64,Eliminations!$D$6:$D$64,$B24)</f>
         <v>-259.718</v>
       </c>
-      <c r="J24" s="21" t="n">
-        <f aca="false">H24+I24</f>
+      <c r="K24" s="21" t="n">
+        <f aca="false">I24+J24</f>
         <v>-259.718</v>
       </c>
     </row>
@@ -3179,17 +3333,21 @@
         <f aca="false">Translation!O21</f>
         <v>1280</v>
       </c>
-      <c r="H25" s="6" t="n">
-        <f aca="false">SUM(D25:G25)</f>
-        <v>14278</v>
-      </c>
-      <c r="I25" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B25)</f>
+      <c r="H25" s="20" t="n">
+        <f aca="false">Translation!R21</f>
+        <v>828.4</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <f aca="false">SUM(D25:H25)</f>
+        <v>15106.4</v>
+      </c>
+      <c r="J25" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$64,Eliminations!$D$6:$D$64,$B25)</f>
         <v>62</v>
       </c>
-      <c r="J25" s="21" t="n">
-        <f aca="false">H25+I25</f>
-        <v>14340</v>
+      <c r="K25" s="21" t="n">
+        <f aca="false">I25+J25</f>
+        <v>15168.4</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3197,7 +3355,7 @@
         <v>5050</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="D26" s="20" t="n">
         <f aca="false">Translation!F22</f>
@@ -3215,16 +3373,20 @@
         <f aca="false">Translation!O22</f>
         <v>0</v>
       </c>
-      <c r="H26" s="6" t="n">
-        <f aca="false">SUM(D26:G26)</f>
+      <c r="H26" s="20" t="n">
+        <f aca="false">Translation!R22</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <f aca="false">SUM(D26:H26)</f>
         <v>800</v>
       </c>
-      <c r="I26" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B26)</f>
+      <c r="J26" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$64,Eliminations!$D$6:$D$64,$B26)</f>
         <v>-800</v>
       </c>
-      <c r="J26" s="21" t="n">
-        <f aca="false">H26+I26</f>
+      <c r="K26" s="21" t="n">
+        <f aca="false">I26+J26</f>
         <v>0</v>
       </c>
     </row>
@@ -3251,17 +3413,21 @@
         <f aca="false">Translation!O23</f>
         <v>384</v>
       </c>
-      <c r="H27" s="6" t="n">
-        <f aca="false">SUM(D27:G27)</f>
-        <v>5306</v>
-      </c>
-      <c r="I27" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B27)</f>
-        <v>0</v>
-      </c>
-      <c r="J27" s="21" t="n">
-        <f aca="false">H27+I27</f>
-        <v>5306</v>
+      <c r="H27" s="20" t="n">
+        <f aca="false">Translation!R23</f>
+        <v>250.7</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <f aca="false">SUM(D27:H27)</f>
+        <v>5556.7</v>
+      </c>
+      <c r="J27" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$64,Eliminations!$D$6:$D$64,$B27)</f>
+        <v>0</v>
+      </c>
+      <c r="K27" s="21" t="n">
+        <f aca="false">I27+J27</f>
+        <v>5556.7</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3287,17 +3453,21 @@
         <f aca="false">Translation!O24</f>
         <v>25.6</v>
       </c>
-      <c r="H28" s="6" t="n">
-        <f aca="false">SUM(D28:G28)</f>
-        <v>398.3</v>
-      </c>
-      <c r="I28" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B28)</f>
-        <v>0</v>
-      </c>
-      <c r="J28" s="21" t="n">
-        <f aca="false">H28+I28</f>
-        <v>398.3</v>
+      <c r="H28" s="20" t="n">
+        <f aca="false">Translation!R24</f>
+        <v>10.9</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <f aca="false">SUM(D28:H28)</f>
+        <v>409.2</v>
+      </c>
+      <c r="J28" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$64,Eliminations!$D$6:$D$64,$B28)</f>
+        <v>0</v>
+      </c>
+      <c r="K28" s="21" t="n">
+        <f aca="false">I28+J28</f>
+        <v>409.2</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3323,22 +3493,26 @@
         <f aca="false">Translation!O25</f>
         <v>89.6</v>
       </c>
-      <c r="H29" s="6" t="n">
-        <f aca="false">SUM(D29:G29)</f>
-        <v>942.2</v>
-      </c>
-      <c r="I29" s="20" t="n">
-        <f aca="false">SUMIFS(Eliminations!$F$6:$F$54,Eliminations!$D$6:$D$54,$B29)</f>
-        <v>0</v>
-      </c>
-      <c r="J29" s="21" t="n">
-        <f aca="false">H29+I29</f>
-        <v>942.2</v>
+      <c r="H29" s="20" t="n">
+        <f aca="false">Translation!R25</f>
+        <v>54.5</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <f aca="false">SUM(D29:H29)</f>
+        <v>996.7</v>
+      </c>
+      <c r="J29" s="20" t="n">
+        <f aca="false">SUMIFS(Eliminations!$F$6:$F$64,Eliminations!$D$6:$D$64,$B29)</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="21" t="n">
+        <f aca="false">I29+J29</f>
+        <v>996.7</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C30" s="7" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="D30" s="8" t="n">
         <f aca="false">ROUND(SUM(D6:D29),2)</f>
@@ -3366,6 +3540,10 @@
       </c>
       <c r="J30" s="8" t="n">
         <f aca="false">ROUND(SUM(J6:J29),2)</f>
+        <v>0</v>
+      </c>
+      <c r="K30" s="8" t="n">
+        <f aca="false">ROUND(SUM(K6:K29),2)</f>
         <v>0</v>
       </c>
     </row>
@@ -3385,7 +3563,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:F55"/>
+  <dimension ref="B1:F65"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -3403,7 +3581,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3413,19 +3591,19 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3433,7 +3611,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>3000</v>
@@ -3451,16 +3629,16 @@
         <v>1</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>3100</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="F7" s="20" t="n">
-        <f aca="false">(Inputs!$G$7*Inputs!$F$13)</f>
+        <f aca="false">(Inputs!$G$7*Inputs!$F$14)</f>
         <v>1200</v>
       </c>
     </row>
@@ -3469,7 +3647,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>1700</v>
@@ -3478,7 +3656,7 @@
         <v>20</v>
       </c>
       <c r="F8" s="20" t="n">
-        <f aca="false">(Inputs!$J$6*Inputs!$F$7-Inputs!$J$7*((-Translation!I16)+(Inputs!$G$7*Inputs!$F$13)))*Inputs!$D$13/Inputs!$F$13</f>
+        <f aca="false">(Inputs!$J$6*(Inputs!$F$7*Inputs!$F$14)-Inputs!$J$7*((-Translation!I16)+(Inputs!$G$7*Inputs!$F$14)))*Inputs!$D$14/Inputs!$F$14</f>
         <v>500</v>
       </c>
     </row>
@@ -3487,16 +3665,16 @@
         <v>1</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>1600</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="F9" s="20" t="n">
-        <f aca="false">-Inputs!$F$7</f>
+        <f aca="false">-(Inputs!$F$7*Inputs!$D$14)</f>
         <v>-2700</v>
       </c>
     </row>
@@ -3505,7 +3683,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>3300</v>
@@ -3514,7 +3692,7 @@
         <v>34</v>
       </c>
       <c r="F10" s="20" t="n">
-        <f aca="false">-((1-Inputs!$J$7)*((-Translation!I16)+(Inputs!$G$7*Inputs!$F$13))-(1-Inputs!$J$6)*Inputs!$F$7)</f>
+        <f aca="false">-((1-Inputs!$J$7)*((-Translation!I16)+(Inputs!$G$7*Inputs!$F$14))-(1-Inputs!$J$6)*(Inputs!$F$7*Inputs!$D$14))</f>
         <v>-0</v>
       </c>
     </row>
@@ -3523,7 +3701,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>3000</v>
@@ -3541,16 +3719,16 @@
         <v>2</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>3100</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="F12" s="20" t="n">
-        <f aca="false">(Inputs!$G$8*Inputs!$F$14)</f>
+        <f aca="false">(Inputs!$G$8*Inputs!$F$15)</f>
         <v>0</v>
       </c>
     </row>
@@ -3559,7 +3737,7 @@
         <v>2</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>1700</v>
@@ -3568,7 +3746,7 @@
         <v>20</v>
       </c>
       <c r="F13" s="20" t="n">
-        <f aca="false">(Inputs!$J$6*Inputs!$F$8-Inputs!$J$8*((-Translation!L16)+(Inputs!$G$8*Inputs!$F$14)))*Inputs!$D$14/Inputs!$F$14</f>
+        <f aca="false">(Inputs!$J$6*(Inputs!$F$8*Inputs!$F$14)-Inputs!$J$8*((-Translation!L16)+(Inputs!$G$8*Inputs!$F$15)))*Inputs!$D$15/Inputs!$F$15</f>
         <v>0</v>
       </c>
     </row>
@@ -3577,16 +3755,16 @@
         <v>2</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>1600</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="F14" s="20" t="n">
-        <f aca="false">-Inputs!$F$8</f>
+        <f aca="false">-(Inputs!$F$8*Inputs!$D$14)</f>
         <v>-880</v>
       </c>
     </row>
@@ -3595,7 +3773,7 @@
         <v>2</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>3300</v>
@@ -3604,7 +3782,7 @@
         <v>34</v>
       </c>
       <c r="F15" s="20" t="n">
-        <f aca="false">-((1-Inputs!$J$8)*((-Translation!L16)+(Inputs!$G$8*Inputs!$F$14))-(1-Inputs!$J$6)*Inputs!$F$8)</f>
+        <f aca="false">-((1-Inputs!$J$8)*((-Translation!L16)+(Inputs!$G$8*Inputs!$F$15))-(1-Inputs!$J$6)*(Inputs!$F$8*Inputs!$D$14))</f>
         <v>-220</v>
       </c>
     </row>
@@ -3613,7 +3791,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>3200</v>
@@ -3622,7 +3800,7 @@
         <v>32</v>
       </c>
       <c r="F16" s="20" t="n">
-        <f aca="false">(Inputs!$J$6*Inputs!$F$8-Inputs!$J$8*((-Translation!L16)+(Inputs!$G$8*Inputs!$F$14)))*(1-Inputs!$D$14/Inputs!$F$14)</f>
+        <f aca="false">(Inputs!$J$6*(Inputs!$F$8*Inputs!$F$14)-Inputs!$J$8*((-Translation!L16)+(Inputs!$G$8*Inputs!$F$15)))*(1-Inputs!$D$15/Inputs!$F$15)+Inputs!$J$6*((Inputs!$F$8*Inputs!$D$14)-(Inputs!$F$8*Inputs!$F$14))</f>
         <v>0</v>
       </c>
     </row>
@@ -3631,16 +3809,16 @@
         <v>3</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="D17" s="5" t="n">
         <v>3100</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="F17" s="20" t="n">
-        <f aca="false">(1-Inputs!$J$8)*(-Translation!L17-(Inputs!$G$8*Inputs!$F$14))</f>
+        <f aca="false">(1-Inputs!$J$8)*(-Translation!L17-(Inputs!$G$8*Inputs!$F$15))</f>
         <v>92</v>
       </c>
     </row>
@@ -3649,7 +3827,7 @@
         <v>3</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>3300</v>
@@ -3658,7 +3836,7 @@
         <v>34</v>
       </c>
       <c r="F18" s="20" t="n">
-        <f aca="false">-(1-Inputs!$J$8)*(-Translation!L17-(Inputs!$G$8*Inputs!$F$14))</f>
+        <f aca="false">-(1-Inputs!$J$8)*(-Translation!L17-(Inputs!$G$8*Inputs!$F$15))</f>
         <v>-92</v>
       </c>
     </row>
@@ -3667,7 +3845,7 @@
         <v>3</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>3200</v>
@@ -3677,7 +3855,7 @@
       </c>
       <c r="F19" s="20" t="n">
         <f aca="false">-(1-Inputs!$J$8)*Translation!L26</f>
-        <v>-6.14000000000003</v>
+        <v>-6.14000000000002</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3685,7 +3863,7 @@
         <v>3</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>3300</v>
@@ -3695,7 +3873,7 @@
       </c>
       <c r="F20" s="20" t="n">
         <f aca="false">(1-Inputs!$J$8)*Translation!L26</f>
-        <v>6.14000000000003</v>
+        <v>6.14000000000002</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3703,7 +3881,7 @@
         <v>4</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>3000</v>
@@ -3721,16 +3899,16 @@
         <v>4</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>3100</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="F22" s="20" t="n">
-        <f aca="false">(Inputs!$G$9*Inputs!$F$16)</f>
+        <f aca="false">(Inputs!$G$9*Inputs!$F$17)</f>
         <v>125</v>
       </c>
     </row>
@@ -3739,7 +3917,7 @@
         <v>4</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>1700</v>
@@ -3748,7 +3926,7 @@
         <v>20</v>
       </c>
       <c r="F23" s="20" t="n">
-        <f aca="false">(Inputs!$J$7*Inputs!$F$9-Inputs!$J$9*((-Translation!O16)+(Inputs!$G$9*Inputs!$F$16)))*Inputs!$D$16/Inputs!$F$16</f>
+        <f aca="false">(Inputs!$J$7*(Inputs!$F$9*Inputs!$F$14)-Inputs!$J$9*((-Translation!O16)+(Inputs!$G$9*Inputs!$F$17)))*Inputs!$D$17/Inputs!$F$17</f>
         <v>76.2</v>
       </c>
     </row>
@@ -3757,16 +3935,16 @@
         <v>4</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>1600</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="F24" s="20" t="n">
-        <f aca="false">-Inputs!$F$9</f>
+        <f aca="false">-(Inputs!$F$9*Inputs!$D$14)</f>
         <v>-600</v>
       </c>
     </row>
@@ -3775,7 +3953,7 @@
         <v>4</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D25" s="5" t="n">
         <v>3300</v>
@@ -3784,7 +3962,7 @@
         <v>34</v>
       </c>
       <c r="F25" s="20" t="n">
-        <f aca="false">-((1-Inputs!$J$9)*((-Translation!O16)+(Inputs!$G$9*Inputs!$F$16))-(1-Inputs!$J$7)*Inputs!$F$9)</f>
+        <f aca="false">-((1-Inputs!$J$9)*((-Translation!O16)+(Inputs!$G$9*Inputs!$F$17))-(1-Inputs!$J$7)*(Inputs!$F$9*Inputs!$D$14))</f>
         <v>-225</v>
       </c>
     </row>
@@ -3793,7 +3971,7 @@
         <v>4</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>3200</v>
@@ -3802,7 +3980,7 @@
         <v>32</v>
       </c>
       <c r="F26" s="20" t="n">
-        <f aca="false">(Inputs!$J$7*Inputs!$F$9-Inputs!$J$9*((-Translation!O16)+(Inputs!$G$9*Inputs!$F$16)))*(1-Inputs!$D$16/Inputs!$F$16)</f>
+        <f aca="false">(Inputs!$J$7*(Inputs!$F$9*Inputs!$F$14)-Inputs!$J$9*((-Translation!O16)+(Inputs!$G$9*Inputs!$F$17)))*(1-Inputs!$D$17/Inputs!$F$17)+Inputs!$J$7*((Inputs!$F$9*Inputs!$D$14)-(Inputs!$F$9*Inputs!$F$14))</f>
         <v>-1.2</v>
       </c>
     </row>
@@ -3811,16 +3989,16 @@
         <v>5</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="D27" s="5" t="n">
         <v>3100</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="F27" s="20" t="n">
-        <f aca="false">(1-Inputs!$J$9)*(-Translation!O17-(Inputs!$G$9*Inputs!$F$16))</f>
+        <f aca="false">(1-Inputs!$J$9)*(-Translation!O17-(Inputs!$G$9*Inputs!$F$17))</f>
         <v>75.6</v>
       </c>
     </row>
@@ -3829,7 +4007,7 @@
         <v>5</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="D28" s="5" t="n">
         <v>3300</v>
@@ -3838,7 +4016,7 @@
         <v>34</v>
       </c>
       <c r="F28" s="20" t="n">
-        <f aca="false">-(1-Inputs!$J$9)*(-Translation!O17-(Inputs!$G$9*Inputs!$F$16))</f>
+        <f aca="false">-(1-Inputs!$J$9)*(-Translation!O17-(Inputs!$G$9*Inputs!$F$17))</f>
         <v>-75.6</v>
       </c>
     </row>
@@ -3847,7 +4025,7 @@
         <v>5</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="D29" s="5" t="n">
         <v>3200</v>
@@ -3865,7 +4043,7 @@
         <v>5</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>3300</v>
@@ -3883,17 +4061,17 @@
         <v>6</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>2150</v>
+        <v>3000</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>146</v>
+        <v>30</v>
       </c>
       <c r="F31" s="20" t="n">
-        <f aca="false">Inputs!$F$20</f>
-        <v>150</v>
+        <f aca="false">(-Translation!R16)</f>
+        <v>440</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3901,421 +4079,601 @@
         <v>6</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>1150</v>
+        <v>3100</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="F32" s="20" t="n">
-        <f aca="false">-Inputs!$F$20</f>
-        <v>-150</v>
+        <f aca="false">(Inputs!$G$10*Inputs!$F$15)</f>
+        <v>110</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>2150</v>
+        <v>1700</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="F33" s="20" t="n">
-        <f aca="false">Inputs!$F$21</f>
-        <v>540</v>
+        <f aca="false">(Inputs!$J$8*(Inputs!$F$10*Inputs!$F$15)-Inputs!$J$10*((-Translation!R16)+(Inputs!$G$10*Inputs!$F$15)))*Inputs!$D$15/Inputs!$F$15</f>
+        <v>64.7999999999999</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>1150</v>
+        <v>1600</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="F34" s="20" t="n">
-        <f aca="false">-Inputs!$F$21</f>
-        <v>-540</v>
+        <f aca="false">-(Inputs!$F$10*Inputs!$D$15)</f>
+        <v>-486</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>4050</v>
+        <v>3300</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>148</v>
+        <v>34</v>
       </c>
       <c r="F35" s="20" t="n">
-        <f aca="false">Inputs!$F$22</f>
-        <v>800</v>
+        <f aca="false">-((1-Inputs!$J$10)*((-Translation!R16)+(Inputs!$G$10*Inputs!$F$15))-(1-Inputs!$J$8)*(Inputs!$F$10*Inputs!$D$15))</f>
+        <v>-122.8</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>5050</v>
+        <v>3200</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="F36" s="20" t="n">
-        <f aca="false">-Inputs!$F$22</f>
-        <v>-800</v>
+        <f aca="false">(Inputs!$J$8*(Inputs!$F$10*Inputs!$F$15)-Inputs!$J$10*((-Translation!R16)+(Inputs!$G$10*Inputs!$F$15)))*(1-Inputs!$D$15/Inputs!$F$15)+Inputs!$J$8*((Inputs!$F$10*Inputs!$D$15)-(Inputs!$F$10*Inputs!$F$15))</f>
+        <v>-6</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>5000</v>
+        <v>3100</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>5</v>
+        <v>154</v>
       </c>
       <c r="F37" s="20" t="n">
-        <f aca="false">Inputs!$F$23</f>
-        <v>50</v>
+        <f aca="false">(1-Inputs!$J$10)*(-Translation!R17-(Inputs!$G$10*Inputs!$F$15))</f>
+        <v>52.4</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>1200</v>
+        <v>3300</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F38" s="20" t="n">
-        <f aca="false">-Inputs!$F$23</f>
-        <v>-50</v>
+        <f aca="false">-(1-Inputs!$J$10)*(-Translation!R17-(Inputs!$G$10*Inputs!$F$15))</f>
+        <v>-52.4</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>3200</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F39" s="20" t="n">
+        <f aca="false">-(1-Inputs!$J$10)*Translation!R26</f>
+        <v>-5.15999999999997</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>3300</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F40" s="20" t="n">
+        <f aca="false">(1-Inputs!$J$10)*Translation!R26</f>
+        <v>5.15999999999997</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>2150</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="F41" s="20" t="n">
+        <f aca="false">Inputs!$F$21</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>1150</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="F42" s="20" t="n">
+        <f aca="false">-Inputs!$F$21</f>
+        <v>-150</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>2150</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="F43" s="20" t="n">
+        <f aca="false">Inputs!$F$22</f>
+        <v>540</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>1150</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="F44" s="20" t="n">
+        <f aca="false">-Inputs!$F$22</f>
+        <v>-540</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="C39" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="D39" s="5" t="n">
+      <c r="C45" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>4050</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="F45" s="20" t="n">
+        <f aca="false">Inputs!$F$23</f>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>5050</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="F46" s="20" t="n">
+        <f aca="false">-Inputs!$F$23</f>
+        <v>-800</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="20" t="n">
+        <f aca="false">Inputs!$F$24</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F48" s="20" t="n">
+        <f aca="false">-Inputs!$F$24</f>
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D49" s="5" t="n">
         <v>1650</v>
       </c>
-      <c r="E39" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F39" s="20" t="n">
+      <c r="E49" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F49" s="20" t="n">
         <f aca="false">Associates!D25</f>
         <v>122.535</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="D40" s="5" t="n">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D50" s="5" t="n">
         <v>3100</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="F40" s="20" t="n">
+      <c r="E50" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F50" s="20" t="n">
         <f aca="false">-Associates!D25</f>
         <v>-122.535</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D41" s="5" t="n">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D51" s="5" t="n">
         <v>1650</v>
       </c>
-      <c r="E41" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F41" s="20" t="n">
+      <c r="E51" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F51" s="20" t="n">
         <f aca="false">Associates!D27</f>
         <v>179.718</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D42" s="5" t="n">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D52" s="5" t="n">
         <v>4200</v>
       </c>
-      <c r="E42" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="F42" s="20" t="n">
+      <c r="E52" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="F52" s="20" t="n">
         <f aca="false">-Associates!D27</f>
         <v>-179.718</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="D43" s="5" t="n">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D53" s="5" t="n">
         <v>4100</v>
       </c>
-      <c r="E43" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="F43" s="20" t="n">
+      <c r="E53" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="F53" s="20" t="n">
         <f aca="false">-Associates!D28</f>
         <v>81.69</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="D44" s="5" t="n">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D54" s="5" t="n">
         <v>1650</v>
       </c>
-      <c r="E44" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F44" s="20" t="n">
+      <c r="E54" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F54" s="20" t="n">
         <f aca="false">Associates!D28</f>
         <v>-81.69</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="D45" s="5" t="n">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D55" s="5" t="n">
         <v>5000</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="E55" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F45" s="20" t="n">
+      <c r="F55" s="20" t="n">
         <f aca="false">-Associates!D30</f>
         <v>12</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="D46" s="5" t="n">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D56" s="5" t="n">
         <v>1650</v>
       </c>
-      <c r="E46" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F46" s="20" t="n">
+      <c r="E56" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F56" s="20" t="n">
         <f aca="false">Associates!D30</f>
         <v>-12</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D47" s="5" t="n">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D57" s="5" t="n">
         <v>1650</v>
       </c>
-      <c r="E47" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F47" s="20" t="n">
+      <c r="E57" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F57" s="20" t="n">
         <f aca="false">Associates!E25</f>
         <v>100</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D48" s="5" t="n">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D58" s="5" t="n">
         <v>3100</v>
       </c>
-      <c r="E48" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="F48" s="20" t="n">
+      <c r="E58" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F58" s="20" t="n">
         <f aca="false">-Associates!E25</f>
         <v>-100</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="D49" s="5" t="n">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D59" s="5" t="n">
         <v>1650</v>
       </c>
-      <c r="E49" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F49" s="20" t="n">
+      <c r="E59" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F59" s="20" t="n">
         <f aca="false">Associates!E27</f>
         <v>120</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="D50" s="5" t="n">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D60" s="5" t="n">
         <v>4200</v>
       </c>
-      <c r="E50" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="F50" s="20" t="n">
+      <c r="E60" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="F60" s="20" t="n">
         <f aca="false">-Associates!E27</f>
         <v>-120</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D51" s="5" t="n">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D61" s="5" t="n">
         <v>4100</v>
       </c>
-      <c r="E51" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="F51" s="20" t="n">
+      <c r="E61" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="F61" s="20" t="n">
         <f aca="false">-Associates!E28</f>
         <v>50</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D52" s="5" t="n">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D62" s="5" t="n">
         <v>1650</v>
       </c>
-      <c r="E52" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F52" s="20" t="n">
+      <c r="E62" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F62" s="20" t="n">
         <f aca="false">Associates!E28</f>
         <v>-50</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D53" s="5" t="n">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D63" s="5" t="n">
         <v>4200</v>
       </c>
-      <c r="E53" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="F53" s="20" t="n">
+      <c r="E63" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="F63" s="20" t="n">
         <f aca="false">-Associates!E29</f>
         <v>40</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D54" s="5" t="n">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D64" s="5" t="n">
         <v>1650</v>
       </c>
-      <c r="E54" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F54" s="20" t="n">
+      <c r="E64" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F64" s="20" t="n">
         <f aca="false">Associates!E29</f>
         <v>-40</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E55" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="F55" s="8" t="n">
-        <f aca="false">ROUND(SUM(F6:F54),2)</f>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E65" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="F65" s="8" t="n">
+        <f aca="false">ROUND(SUM(F6:F64),2)</f>
         <v>0</v>
       </c>
     </row>
@@ -4351,7 +4709,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4363,35 +4721,35 @@
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="19" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4407,7 +4765,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>900</v>
@@ -4422,7 +4780,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>9000</v>
@@ -4433,7 +4791,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>3000</v>
@@ -4444,7 +4802,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>4500</v>
@@ -4455,7 +4813,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>2200</v>
@@ -4466,7 +4824,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>1000</v>
@@ -4477,7 +4835,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>0</v>
@@ -4492,51 +4850,51 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="D16" s="25" t="n">
-        <f aca="false">Inputs!$F$15</f>
+        <f aca="false">Inputs!$F$16</f>
         <v>0.2723</v>
       </c>
       <c r="E16" s="25" t="n">
-        <f aca="false">Inputs!$F$13</f>
+        <f aca="false">Inputs!$F$14</f>
         <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="D17" s="25" t="n">
-        <f aca="false">Inputs!$E$15</f>
+        <f aca="false">Inputs!$E$16</f>
         <v>0.2723</v>
       </c>
       <c r="E17" s="25" t="n">
-        <f aca="false">Inputs!$E$13</f>
+        <f aca="false">Inputs!$E$14</f>
         <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D18" s="25" t="n">
-        <f aca="false">Inputs!$D$15</f>
+        <f aca="false">Inputs!$D$16</f>
         <v>0.2723</v>
       </c>
       <c r="E18" s="25" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="7" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="D21" s="26" t="n">
         <f aca="false">D8*D10*D16</f>
@@ -4553,7 +4911,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="D22" s="26" t="n">
         <f aca="false">D9-D21</f>
@@ -4570,7 +4928,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="D24" s="26" t="n">
         <f aca="false">D9</f>
@@ -4587,7 +4945,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="5" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="D25" s="26" t="n">
         <f aca="false">D8*(D12-D11)*D16</f>
@@ -4604,7 +4962,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="7" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="D26" s="27" t="n">
         <f aca="false">D24+D25</f>
@@ -4621,7 +4979,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="5" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="D27" s="26" t="n">
         <f aca="false">D8*D13*D17</f>
@@ -4638,7 +4996,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="5" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="D28" s="26" t="n">
         <f aca="false">-D8*D14*D17</f>
@@ -4655,7 +5013,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="5" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="D29" s="26" t="n">
         <f aca="false">-D15</f>
@@ -4672,14 +5030,14 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="D30" s="26" t="n">
-        <f aca="false">-D8*SUMIFS(Inputs!$F$20:$F$24,Inputs!$B$20:$B$24,"associate_unrealised_profit",Inputs!$E$20:$E$24,"ASSOC1")</f>
+        <f aca="false">-D8*SUMIFS(Inputs!$F$21:$F$25,Inputs!$B$21:$B$25,"associate_unrealised_profit",Inputs!$E$21:$E$25,"ASSOC1")</f>
         <v>-12</v>
       </c>
       <c r="E30" s="26" t="n">
-        <f aca="false">-E8*SUMIFS(Inputs!$F$20:$F$24,Inputs!$B$20:$B$24,"associate_unrealised_profit",Inputs!$E$20:$E$24,"ASSOC2")</f>
+        <f aca="false">-E8*SUMIFS(Inputs!$F$21:$F$25,Inputs!$B$21:$B$25,"associate_unrealised_profit",Inputs!$E$21:$E$25,"ASSOC2")</f>
         <v>-0</v>
       </c>
       <c r="F30" s="21" t="n">
@@ -4689,7 +5047,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="7" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="D31" s="28" t="n">
         <f aca="false">SUM(D26:D30)</f>
@@ -4706,12 +5064,12 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="7" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="5" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="D34" s="26" t="n">
         <f aca="false">D10+D12-D11+D13-D14</f>
@@ -4724,7 +5082,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="5" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="D35" s="26" t="n">
         <f aca="false">D8*D34*D18</f>
@@ -4758,7 +5116,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="5" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="D37" s="26" t="n">
         <f aca="false">D29</f>
@@ -4775,7 +5133,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="5" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="D38" s="26" t="n">
         <f aca="false">D30</f>
@@ -4792,7 +5150,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="5" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="D39" s="26" t="n">
         <f aca="false">D31-SUM(D35:D38)</f>
@@ -4809,7 +5167,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="7" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="D40" s="28" t="n">
         <f aca="false">SUM(D35:D39)</f>
@@ -4826,14 +5184,14 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="5" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="D42" s="26" t="n">
-        <f aca="false">D8*SUMIFS(Inputs!$F$20:$F$24,Inputs!$B$20:$B$24,"associate_unrealised_profit",Inputs!$D$20:$D$24,"ASSOC1")</f>
+        <f aca="false">D8*SUMIFS(Inputs!$F$21:$F$25,Inputs!$B$21:$B$25,"associate_unrealised_profit",Inputs!$D$21:$D$25,"ASSOC1")</f>
         <v>0</v>
       </c>
       <c r="E42" s="26" t="n">
-        <f aca="false">E8*SUMIFS(Inputs!$F$20:$F$24,Inputs!$B$20:$B$24,"associate_unrealised_profit",Inputs!$D$20:$D$24,"ASSOC2")</f>
+        <f aca="false">E8*SUMIFS(Inputs!$F$21:$F$25,Inputs!$B$21:$B$25,"associate_unrealised_profit",Inputs!$D$21:$D$25,"ASSOC2")</f>
         <v>0</v>
       </c>
       <c r="F42" s="21" t="n">
@@ -4843,7 +5201,7 @@
     </row>
     <row r="44" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="29" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -4862,7 +5220,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:O28"/>
+  <dimension ref="B1:R28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -4876,7 +5234,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4886,7 +5246,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4896,46 +5256,55 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="J5" s="19" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="L5" s="19" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="M5" s="19" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="N5" s="19" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="O5" s="19" t="s">
-        <v>223</v>
+        <v>232</v>
+      </c>
+      <c r="P5" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q5" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="R5" s="19" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4950,7 +5319,7 @@
         <v>1331.69</v>
       </c>
       <c r="E6" s="30" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1</v>
       </c>
       <c r="F6" s="6" t="n">
@@ -4962,7 +5331,7 @@
         <v>600</v>
       </c>
       <c r="H6" s="30" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1</v>
       </c>
       <c r="I6" s="6" t="n">
@@ -4974,7 +5343,7 @@
         <v>400</v>
       </c>
       <c r="K6" s="30" t="n">
-        <f aca="false">Inputs!$D$14</f>
+        <f aca="false">Inputs!$D$15</f>
         <v>1.08</v>
       </c>
       <c r="L6" s="6" t="n">
@@ -4986,13 +5355,25 @@
         <v>160</v>
       </c>
       <c r="N6" s="30" t="n">
-        <f aca="false">Inputs!$D$16</f>
+        <f aca="false">Inputs!$D$17</f>
         <v>1.27</v>
       </c>
       <c r="O6" s="6" t="n">
         <f aca="false">M6*N6</f>
         <v>203.2</v>
       </c>
+      <c r="P6" s="20" t="n">
+        <f aca="false">'Trial Balances'!I6</f>
+        <v>120</v>
+      </c>
+      <c r="Q6" s="30" t="n">
+        <f aca="false">Inputs!$D$15</f>
+        <v>1.08</v>
+      </c>
+      <c r="R6" s="6" t="n">
+        <f aca="false">P6*Q6</f>
+        <v>129.6</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="n">
@@ -5006,7 +5387,7 @@
         <v>2100</v>
       </c>
       <c r="E7" s="30" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1</v>
       </c>
       <c r="F7" s="6" t="n">
@@ -5018,7 +5399,7 @@
         <v>900</v>
       </c>
       <c r="H7" s="30" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1</v>
       </c>
       <c r="I7" s="6" t="n">
@@ -5030,7 +5411,7 @@
         <v>700</v>
       </c>
       <c r="K7" s="30" t="n">
-        <f aca="false">Inputs!$D$14</f>
+        <f aca="false">Inputs!$D$15</f>
         <v>1.08</v>
       </c>
       <c r="L7" s="6" t="n">
@@ -5042,27 +5423,39 @@
         <v>250</v>
       </c>
       <c r="N7" s="30" t="n">
-        <f aca="false">Inputs!$D$16</f>
+        <f aca="false">Inputs!$D$17</f>
         <v>1.27</v>
       </c>
       <c r="O7" s="6" t="n">
         <f aca="false">M7*N7</f>
         <v>317.5</v>
       </c>
+      <c r="P7" s="20" t="n">
+        <f aca="false">'Trial Balances'!I7</f>
+        <v>200</v>
+      </c>
+      <c r="Q7" s="30" t="n">
+        <f aca="false">Inputs!$D$15</f>
+        <v>1.08</v>
+      </c>
+      <c r="R7" s="6" t="n">
+        <f aca="false">P7*Q7</f>
+        <v>216</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="n">
         <v>1150</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="D8" s="20" t="n">
         <f aca="false">'Trial Balances'!E8</f>
         <v>540</v>
       </c>
       <c r="E8" s="30" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1</v>
       </c>
       <c r="F8" s="6" t="n">
@@ -5074,7 +5467,7 @@
         <v>150</v>
       </c>
       <c r="H8" s="30" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1</v>
       </c>
       <c r="I8" s="6" t="n">
@@ -5086,7 +5479,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="30" t="n">
-        <f aca="false">Inputs!$D$14</f>
+        <f aca="false">Inputs!$D$15</f>
         <v>1.08</v>
       </c>
       <c r="L8" s="6" t="n">
@@ -5098,11 +5491,23 @@
         <v>0</v>
       </c>
       <c r="N8" s="30" t="n">
-        <f aca="false">Inputs!$D$16</f>
+        <f aca="false">Inputs!$D$17</f>
         <v>1.27</v>
       </c>
       <c r="O8" s="6" t="n">
         <f aca="false">M8*N8</f>
+        <v>0</v>
+      </c>
+      <c r="P8" s="20" t="n">
+        <f aca="false">'Trial Balances'!I8</f>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="30" t="n">
+        <f aca="false">Inputs!$D$15</f>
+        <v>1.08</v>
+      </c>
+      <c r="R8" s="6" t="n">
+        <f aca="false">P8*Q8</f>
         <v>0</v>
       </c>
     </row>
@@ -5118,7 +5523,7 @@
         <v>1500</v>
       </c>
       <c r="E9" s="30" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
@@ -5130,7 +5535,7 @@
         <v>700</v>
       </c>
       <c r="H9" s="30" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1</v>
       </c>
       <c r="I9" s="6" t="n">
@@ -5142,7 +5547,7 @@
         <v>500</v>
       </c>
       <c r="K9" s="30" t="n">
-        <f aca="false">Inputs!$D$14</f>
+        <f aca="false">Inputs!$D$15</f>
         <v>1.08</v>
       </c>
       <c r="L9" s="6" t="n">
@@ -5154,13 +5559,25 @@
         <v>180</v>
       </c>
       <c r="N9" s="30" t="n">
-        <f aca="false">Inputs!$D$16</f>
+        <f aca="false">Inputs!$D$17</f>
         <v>1.27</v>
       </c>
       <c r="O9" s="6" t="n">
         <f aca="false">M9*N9</f>
         <v>228.6</v>
       </c>
+      <c r="P9" s="20" t="n">
+        <f aca="false">'Trial Balances'!I9</f>
+        <v>150</v>
+      </c>
+      <c r="Q9" s="30" t="n">
+        <f aca="false">Inputs!$D$15</f>
+        <v>1.08</v>
+      </c>
+      <c r="R9" s="6" t="n">
+        <f aca="false">P9*Q9</f>
+        <v>162</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="n">
@@ -5174,7 +5591,7 @@
         <v>6000</v>
       </c>
       <c r="E10" s="30" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1</v>
       </c>
       <c r="F10" s="6" t="n">
@@ -5186,7 +5603,7 @@
         <v>2500</v>
       </c>
       <c r="H10" s="30" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1</v>
       </c>
       <c r="I10" s="6" t="n">
@@ -5198,7 +5615,7 @@
         <v>1800</v>
       </c>
       <c r="K10" s="30" t="n">
-        <f aca="false">Inputs!$D$14</f>
+        <f aca="false">Inputs!$D$15</f>
         <v>1.08</v>
       </c>
       <c r="L10" s="6" t="n">
@@ -5210,27 +5627,39 @@
         <v>900</v>
       </c>
       <c r="N10" s="30" t="n">
-        <f aca="false">Inputs!$D$16</f>
+        <f aca="false">Inputs!$D$17</f>
         <v>1.27</v>
       </c>
       <c r="O10" s="6" t="n">
         <f aca="false">M10*N10</f>
         <v>1143</v>
       </c>
+      <c r="P10" s="20" t="n">
+        <f aca="false">'Trial Balances'!I10</f>
+        <v>700</v>
+      </c>
+      <c r="Q10" s="30" t="n">
+        <f aca="false">Inputs!$D$15</f>
+        <v>1.08</v>
+      </c>
+      <c r="R10" s="6" t="n">
+        <f aca="false">P10*Q10</f>
+        <v>756</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="n">
         <v>1600</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="D11" s="20" t="n">
         <f aca="false">'Trial Balances'!E11</f>
         <v>3580</v>
       </c>
       <c r="E11" s="30" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1</v>
       </c>
       <c r="F11" s="6" t="n">
@@ -5242,7 +5671,7 @@
         <v>600</v>
       </c>
       <c r="H11" s="30" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1</v>
       </c>
       <c r="I11" s="6" t="n">
@@ -5251,26 +5680,38 @@
       </c>
       <c r="J11" s="20" t="n">
         <f aca="false">'Trial Balances'!G11</f>
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="K11" s="30" t="n">
-        <f aca="false">Inputs!$D$14</f>
+        <f aca="false">Inputs!$D$15</f>
         <v>1.08</v>
       </c>
       <c r="L11" s="6" t="n">
         <f aca="false">J11*K11</f>
-        <v>0</v>
+        <v>486</v>
       </c>
       <c r="M11" s="20" t="n">
         <f aca="false">'Trial Balances'!H11</f>
         <v>0</v>
       </c>
       <c r="N11" s="30" t="n">
-        <f aca="false">Inputs!$D$16</f>
+        <f aca="false">Inputs!$D$17</f>
         <v>1.27</v>
       </c>
       <c r="O11" s="6" t="n">
         <f aca="false">M11*N11</f>
+        <v>0</v>
+      </c>
+      <c r="P11" s="20" t="n">
+        <f aca="false">'Trial Balances'!I11</f>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="30" t="n">
+        <f aca="false">Inputs!$D$15</f>
+        <v>1.08</v>
+      </c>
+      <c r="R11" s="6" t="n">
+        <f aca="false">P11*Q11</f>
         <v>0</v>
       </c>
     </row>
@@ -5279,14 +5720,14 @@
         <v>1650</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="D12" s="20" t="n">
         <f aca="false">'Trial Balances'!E12</f>
         <v>1500</v>
       </c>
       <c r="E12" s="30" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1</v>
       </c>
       <c r="F12" s="6" t="n">
@@ -5298,7 +5739,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="30" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1</v>
       </c>
       <c r="I12" s="6" t="n">
@@ -5310,7 +5751,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="30" t="n">
-        <f aca="false">Inputs!$D$14</f>
+        <f aca="false">Inputs!$D$15</f>
         <v>1.08</v>
       </c>
       <c r="L12" s="6" t="n">
@@ -5322,11 +5763,23 @@
         <v>0</v>
       </c>
       <c r="N12" s="30" t="n">
-        <f aca="false">Inputs!$D$16</f>
+        <f aca="false">Inputs!$D$17</f>
         <v>1.27</v>
       </c>
       <c r="O12" s="6" t="n">
         <f aca="false">M12*N12</f>
+        <v>0</v>
+      </c>
+      <c r="P12" s="20" t="n">
+        <f aca="false">'Trial Balances'!I12</f>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="30" t="n">
+        <f aca="false">Inputs!$D$15</f>
+        <v>1.08</v>
+      </c>
+      <c r="R12" s="6" t="n">
+        <f aca="false">P12*Q12</f>
         <v>0</v>
       </c>
     </row>
@@ -5342,7 +5795,7 @@
         <v>-1700</v>
       </c>
       <c r="E13" s="30" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
@@ -5354,7 +5807,7 @@
         <v>-650</v>
       </c>
       <c r="H13" s="30" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1</v>
       </c>
       <c r="I13" s="6" t="n">
@@ -5366,7 +5819,7 @@
         <v>-450</v>
       </c>
       <c r="K13" s="30" t="n">
-        <f aca="false">Inputs!$D$14</f>
+        <f aca="false">Inputs!$D$15</f>
         <v>1.08</v>
       </c>
       <c r="L13" s="6" t="n">
@@ -5378,27 +5831,39 @@
         <v>-180</v>
       </c>
       <c r="N13" s="30" t="n">
-        <f aca="false">Inputs!$D$16</f>
+        <f aca="false">Inputs!$D$17</f>
         <v>1.27</v>
       </c>
       <c r="O13" s="6" t="n">
         <f aca="false">M13*N13</f>
         <v>-228.6</v>
       </c>
+      <c r="P13" s="20" t="n">
+        <f aca="false">'Trial Balances'!I13</f>
+        <v>-150</v>
+      </c>
+      <c r="Q13" s="30" t="n">
+        <f aca="false">Inputs!$D$15</f>
+        <v>1.08</v>
+      </c>
+      <c r="R13" s="6" t="n">
+        <f aca="false">P13*Q13</f>
+        <v>-162</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="n">
         <v>2150</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D14" s="20" t="n">
         <f aca="false">'Trial Balances'!E14</f>
         <v>-150</v>
       </c>
       <c r="E14" s="30" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1</v>
       </c>
       <c r="F14" s="6" t="n">
@@ -5410,7 +5875,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="30" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1</v>
       </c>
       <c r="I14" s="6" t="n">
@@ -5422,7 +5887,7 @@
         <v>-500</v>
       </c>
       <c r="K14" s="30" t="n">
-        <f aca="false">Inputs!$D$14</f>
+        <f aca="false">Inputs!$D$15</f>
         <v>1.08</v>
       </c>
       <c r="L14" s="6" t="n">
@@ -5434,11 +5899,23 @@
         <v>0</v>
       </c>
       <c r="N14" s="30" t="n">
-        <f aca="false">Inputs!$D$16</f>
+        <f aca="false">Inputs!$D$17</f>
         <v>1.27</v>
       </c>
       <c r="O14" s="6" t="n">
         <f aca="false">M14*N14</f>
+        <v>0</v>
+      </c>
+      <c r="P14" s="20" t="n">
+        <f aca="false">'Trial Balances'!I14</f>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="30" t="n">
+        <f aca="false">Inputs!$D$15</f>
+        <v>1.08</v>
+      </c>
+      <c r="R14" s="6" t="n">
+        <f aca="false">P14*Q14</f>
         <v>0</v>
       </c>
     </row>
@@ -5454,7 +5931,7 @@
         <v>-5000</v>
       </c>
       <c r="E15" s="30" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1</v>
       </c>
       <c r="F15" s="6" t="n">
@@ -5466,7 +5943,7 @@
         <v>-1600</v>
       </c>
       <c r="H15" s="30" t="n">
-        <f aca="false">Inputs!$D$13</f>
+        <f aca="false">Inputs!$D$14</f>
         <v>1</v>
       </c>
       <c r="I15" s="6" t="n">
@@ -5475,28 +5952,40 @@
       </c>
       <c r="J15" s="20" t="n">
         <f aca="false">'Trial Balances'!G15</f>
-        <v>-600</v>
+        <v>-1050</v>
       </c>
       <c r="K15" s="30" t="n">
-        <f aca="false">Inputs!$D$14</f>
+        <f aca="false">Inputs!$D$15</f>
         <v>1.08</v>
       </c>
       <c r="L15" s="6" t="n">
         <f aca="false">J15*K15</f>
-        <v>-648</v>
+        <v>-1134</v>
       </c>
       <c r="M15" s="20" t="n">
         <f aca="false">'Trial Balances'!H15</f>
         <v>-300</v>
       </c>
       <c r="N15" s="30" t="n">
-        <f aca="false">Inputs!$D$16</f>
+        <f aca="false">Inputs!$D$17</f>
         <v>1.27</v>
       </c>
       <c r="O15" s="6" t="n">
         <f aca="false">M15*N15</f>
         <v>-381</v>
       </c>
+      <c r="P15" s="20" t="n">
+        <f aca="false">'Trial Balances'!I15</f>
+        <v>-250</v>
+      </c>
+      <c r="Q15" s="30" t="n">
+        <f aca="false">Inputs!$D$15</f>
+        <v>1.08</v>
+      </c>
+      <c r="R15" s="6" t="n">
+        <f aca="false">P15*Q15</f>
+        <v>-270</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="n">
@@ -5510,7 +5999,7 @@
         <v>-5000</v>
       </c>
       <c r="E16" s="30" t="n">
-        <f aca="false">Inputs!$F$13</f>
+        <f aca="false">Inputs!$F$14</f>
         <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
@@ -5522,7 +6011,7 @@
         <v>-1000</v>
       </c>
       <c r="H16" s="30" t="n">
-        <f aca="false">Inputs!$F$13</f>
+        <f aca="false">Inputs!$F$14</f>
         <v>1</v>
       </c>
       <c r="I16" s="6" t="n">
@@ -5534,7 +6023,7 @@
         <v>-1000</v>
       </c>
       <c r="K16" s="30" t="n">
-        <f aca="false">Inputs!$F$14</f>
+        <f aca="false">Inputs!$F$15</f>
         <v>1.1</v>
       </c>
       <c r="L16" s="6" t="n">
@@ -5546,27 +6035,39 @@
         <v>-500</v>
       </c>
       <c r="N16" s="30" t="n">
-        <f aca="false">Inputs!$F$16</f>
+        <f aca="false">Inputs!$F$17</f>
         <v>1.25</v>
       </c>
       <c r="O16" s="6" t="n">
         <f aca="false">M16*N16</f>
         <v>-625</v>
       </c>
+      <c r="P16" s="20" t="n">
+        <f aca="false">'Trial Balances'!I16</f>
+        <v>-400</v>
+      </c>
+      <c r="Q16" s="30" t="n">
+        <f aca="false">Inputs!$F$15</f>
+        <v>1.1</v>
+      </c>
+      <c r="R16" s="6" t="n">
+        <f aca="false">P16*Q16</f>
+        <v>-440</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="n">
         <v>3100</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D17" s="20" t="n">
         <f aca="false">'Trial Balances'!E17</f>
         <v>-2800</v>
       </c>
       <c r="E17" s="30" t="n">
-        <f aca="false">Inputs!$F$13</f>
+        <f aca="false">Inputs!$F$14</f>
         <v>1</v>
       </c>
       <c r="F17" s="6" t="n">
@@ -5578,7 +6079,7 @@
         <v>-1460</v>
       </c>
       <c r="H17" s="30" t="n">
-        <f aca="false">Inputs!$F$13</f>
+        <f aca="false">Inputs!$F$14</f>
         <v>1</v>
       </c>
       <c r="I17" s="6" t="n">
@@ -5609,6 +6110,18 @@
         <f aca="false">-Inputs!$H$9</f>
         <v>-377</v>
       </c>
+      <c r="P17" s="20" t="n">
+        <f aca="false">'Trial Balances'!I17</f>
+        <v>-220</v>
+      </c>
+      <c r="Q17" s="30" t="n">
+        <f aca="false">IF(P17=0,0,R17/P17)</f>
+        <v>1.09545454545455</v>
+      </c>
+      <c r="R17" s="6" t="n">
+        <f aca="false">-Inputs!$H$10</f>
+        <v>-241</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="n">
@@ -5622,7 +6135,7 @@
         <v>-14000</v>
       </c>
       <c r="E18" s="30" t="n">
-        <f aca="false">Inputs!$E$13</f>
+        <f aca="false">Inputs!$E$14</f>
         <v>1</v>
       </c>
       <c r="F18" s="6" t="n">
@@ -5634,7 +6147,7 @@
         <v>-4200</v>
       </c>
       <c r="H18" s="30" t="n">
-        <f aca="false">Inputs!$E$13</f>
+        <f aca="false">Inputs!$E$14</f>
         <v>1</v>
       </c>
       <c r="I18" s="6" t="n">
@@ -5646,7 +6159,7 @@
         <v>-3600</v>
       </c>
       <c r="K18" s="30" t="n">
-        <f aca="false">Inputs!$E$14</f>
+        <f aca="false">Inputs!$E$15</f>
         <v>1.09</v>
       </c>
       <c r="L18" s="6" t="n">
@@ -5658,27 +6171,39 @@
         <v>-1600</v>
       </c>
       <c r="N18" s="30" t="n">
-        <f aca="false">Inputs!$E$16</f>
+        <f aca="false">Inputs!$E$17</f>
         <v>1.28</v>
       </c>
       <c r="O18" s="6" t="n">
         <f aca="false">M18*N18</f>
         <v>-2048</v>
       </c>
+      <c r="P18" s="20" t="n">
+        <f aca="false">'Trial Balances'!I18</f>
+        <v>-1200</v>
+      </c>
+      <c r="Q18" s="30" t="n">
+        <f aca="false">Inputs!$E$15</f>
+        <v>1.09</v>
+      </c>
+      <c r="R18" s="6" t="n">
+        <f aca="false">P18*Q18</f>
+        <v>-1308</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="5" t="n">
         <v>4050</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="D19" s="20" t="n">
         <f aca="false">'Trial Balances'!E19</f>
         <v>0</v>
       </c>
       <c r="E19" s="30" t="n">
-        <f aca="false">Inputs!$E$13</f>
+        <f aca="false">Inputs!$E$14</f>
         <v>1</v>
       </c>
       <c r="F19" s="6" t="n">
@@ -5690,7 +6215,7 @@
         <v>-800</v>
       </c>
       <c r="H19" s="30" t="n">
-        <f aca="false">Inputs!$E$13</f>
+        <f aca="false">Inputs!$E$14</f>
         <v>1</v>
       </c>
       <c r="I19" s="6" t="n">
@@ -5702,7 +6227,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="30" t="n">
-        <f aca="false">Inputs!$E$14</f>
+        <f aca="false">Inputs!$E$15</f>
         <v>1.09</v>
       </c>
       <c r="L19" s="6" t="n">
@@ -5714,11 +6239,23 @@
         <v>0</v>
       </c>
       <c r="N19" s="30" t="n">
-        <f aca="false">Inputs!$E$16</f>
+        <f aca="false">Inputs!$E$17</f>
         <v>1.28</v>
       </c>
       <c r="O19" s="6" t="n">
         <f aca="false">M19*N19</f>
+        <v>0</v>
+      </c>
+      <c r="P19" s="20" t="n">
+        <f aca="false">'Trial Balances'!I19</f>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="30" t="n">
+        <f aca="false">Inputs!$E$15</f>
+        <v>1.09</v>
+      </c>
+      <c r="R19" s="6" t="n">
+        <f aca="false">P19*Q19</f>
         <v>0</v>
       </c>
     </row>
@@ -5727,14 +6264,14 @@
         <v>4100</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="D20" s="20" t="n">
         <f aca="false">'Trial Balances'!E20</f>
         <v>-131.69</v>
       </c>
       <c r="E20" s="30" t="n">
-        <f aca="false">Inputs!$E$13</f>
+        <f aca="false">Inputs!$E$14</f>
         <v>1</v>
       </c>
       <c r="F20" s="6" t="n">
@@ -5746,7 +6283,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="30" t="n">
-        <f aca="false">Inputs!$E$13</f>
+        <f aca="false">Inputs!$E$14</f>
         <v>1</v>
       </c>
       <c r="I20" s="6" t="n">
@@ -5758,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="30" t="n">
-        <f aca="false">Inputs!$E$14</f>
+        <f aca="false">Inputs!$E$15</f>
         <v>1.09</v>
       </c>
       <c r="L20" s="6" t="n">
@@ -5770,11 +6307,23 @@
         <v>0</v>
       </c>
       <c r="N20" s="30" t="n">
-        <f aca="false">Inputs!$E$16</f>
+        <f aca="false">Inputs!$E$17</f>
         <v>1.28</v>
       </c>
       <c r="O20" s="6" t="n">
         <f aca="false">M20*N20</f>
+        <v>0</v>
+      </c>
+      <c r="P20" s="20" t="n">
+        <f aca="false">'Trial Balances'!I20</f>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="30" t="n">
+        <f aca="false">Inputs!$E$15</f>
+        <v>1.09</v>
+      </c>
+      <c r="R20" s="6" t="n">
+        <f aca="false">P20*Q20</f>
         <v>0</v>
       </c>
     </row>
@@ -5790,7 +6339,7 @@
         <v>7600</v>
       </c>
       <c r="E21" s="30" t="n">
-        <f aca="false">Inputs!$E$13</f>
+        <f aca="false">Inputs!$E$14</f>
         <v>1</v>
       </c>
       <c r="F21" s="6" t="n">
@@ -5802,7 +6351,7 @@
         <v>3000</v>
       </c>
       <c r="H21" s="30" t="n">
-        <f aca="false">Inputs!$E$13</f>
+        <f aca="false">Inputs!$E$14</f>
         <v>1</v>
       </c>
       <c r="I21" s="6" t="n">
@@ -5814,7 +6363,7 @@
         <v>2200</v>
       </c>
       <c r="K21" s="30" t="n">
-        <f aca="false">Inputs!$E$14</f>
+        <f aca="false">Inputs!$E$15</f>
         <v>1.09</v>
       </c>
       <c r="L21" s="6" t="n">
@@ -5826,27 +6375,39 @@
         <v>1000</v>
       </c>
       <c r="N21" s="30" t="n">
-        <f aca="false">Inputs!$E$16</f>
+        <f aca="false">Inputs!$E$17</f>
         <v>1.28</v>
       </c>
       <c r="O21" s="6" t="n">
         <f aca="false">M21*N21</f>
         <v>1280</v>
       </c>
+      <c r="P21" s="20" t="n">
+        <f aca="false">'Trial Balances'!I21</f>
+        <v>760</v>
+      </c>
+      <c r="Q21" s="30" t="n">
+        <f aca="false">Inputs!$E$15</f>
+        <v>1.09</v>
+      </c>
+      <c r="R21" s="6" t="n">
+        <f aca="false">P21*Q21</f>
+        <v>828.4</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="n">
         <v>5050</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="D22" s="20" t="n">
         <f aca="false">'Trial Balances'!E22</f>
         <v>800</v>
       </c>
       <c r="E22" s="30" t="n">
-        <f aca="false">Inputs!$E$13</f>
+        <f aca="false">Inputs!$E$14</f>
         <v>1</v>
       </c>
       <c r="F22" s="6" t="n">
@@ -5858,7 +6419,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="30" t="n">
-        <f aca="false">Inputs!$E$13</f>
+        <f aca="false">Inputs!$E$14</f>
         <v>1</v>
       </c>
       <c r="I22" s="6" t="n">
@@ -5870,7 +6431,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="30" t="n">
-        <f aca="false">Inputs!$E$14</f>
+        <f aca="false">Inputs!$E$15</f>
         <v>1.09</v>
       </c>
       <c r="L22" s="6" t="n">
@@ -5882,11 +6443,23 @@
         <v>0</v>
       </c>
       <c r="N22" s="30" t="n">
-        <f aca="false">Inputs!$E$16</f>
+        <f aca="false">Inputs!$E$17</f>
         <v>1.28</v>
       </c>
       <c r="O22" s="6" t="n">
         <f aca="false">M22*N22</f>
+        <v>0</v>
+      </c>
+      <c r="P22" s="20" t="n">
+        <f aca="false">'Trial Balances'!I22</f>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="30" t="n">
+        <f aca="false">Inputs!$E$15</f>
+        <v>1.09</v>
+      </c>
+      <c r="R22" s="6" t="n">
+        <f aca="false">P22*Q22</f>
         <v>0</v>
       </c>
     </row>
@@ -5902,7 +6475,7 @@
         <v>3100</v>
       </c>
       <c r="E23" s="30" t="n">
-        <f aca="false">Inputs!$E$13</f>
+        <f aca="false">Inputs!$E$14</f>
         <v>1</v>
       </c>
       <c r="F23" s="6" t="n">
@@ -5914,7 +6487,7 @@
         <v>950</v>
       </c>
       <c r="H23" s="30" t="n">
-        <f aca="false">Inputs!$E$13</f>
+        <f aca="false">Inputs!$E$14</f>
         <v>1</v>
       </c>
       <c r="I23" s="6" t="n">
@@ -5926,7 +6499,7 @@
         <v>800</v>
       </c>
       <c r="K23" s="30" t="n">
-        <f aca="false">Inputs!$E$14</f>
+        <f aca="false">Inputs!$E$15</f>
         <v>1.09</v>
       </c>
       <c r="L23" s="6" t="n">
@@ -5938,13 +6511,25 @@
         <v>300</v>
       </c>
       <c r="N23" s="30" t="n">
-        <f aca="false">Inputs!$E$16</f>
+        <f aca="false">Inputs!$E$17</f>
         <v>1.28</v>
       </c>
       <c r="O23" s="6" t="n">
         <f aca="false">M23*N23</f>
         <v>384</v>
       </c>
+      <c r="P23" s="20" t="n">
+        <f aca="false">'Trial Balances'!I23</f>
+        <v>230</v>
+      </c>
+      <c r="Q23" s="30" t="n">
+        <f aca="false">Inputs!$E$15</f>
+        <v>1.09</v>
+      </c>
+      <c r="R23" s="6" t="n">
+        <f aca="false">P23*Q23</f>
+        <v>250.7</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="n">
@@ -5958,7 +6543,7 @@
         <v>280</v>
       </c>
       <c r="E24" s="30" t="n">
-        <f aca="false">Inputs!$E$13</f>
+        <f aca="false">Inputs!$E$14</f>
         <v>1</v>
       </c>
       <c r="F24" s="6" t="n">
@@ -5970,7 +6555,7 @@
         <v>60</v>
       </c>
       <c r="H24" s="30" t="n">
-        <f aca="false">Inputs!$E$13</f>
+        <f aca="false">Inputs!$E$14</f>
         <v>1</v>
       </c>
       <c r="I24" s="6" t="n">
@@ -5982,7 +6567,7 @@
         <v>30</v>
       </c>
       <c r="K24" s="30" t="n">
-        <f aca="false">Inputs!$E$14</f>
+        <f aca="false">Inputs!$E$15</f>
         <v>1.09</v>
       </c>
       <c r="L24" s="6" t="n">
@@ -5994,13 +6579,25 @@
         <v>20</v>
       </c>
       <c r="N24" s="30" t="n">
-        <f aca="false">Inputs!$E$16</f>
+        <f aca="false">Inputs!$E$17</f>
         <v>1.28</v>
       </c>
       <c r="O24" s="6" t="n">
         <f aca="false">M24*N24</f>
         <v>25.6</v>
       </c>
+      <c r="P24" s="20" t="n">
+        <f aca="false">'Trial Balances'!I24</f>
+        <v>10</v>
+      </c>
+      <c r="Q24" s="30" t="n">
+        <f aca="false">Inputs!$E$15</f>
+        <v>1.09</v>
+      </c>
+      <c r="R24" s="6" t="n">
+        <f aca="false">P24*Q24</f>
+        <v>10.9</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="5" t="n">
@@ -6014,7 +6611,7 @@
         <v>450</v>
       </c>
       <c r="E25" s="30" t="n">
-        <f aca="false">Inputs!$E$13</f>
+        <f aca="false">Inputs!$E$14</f>
         <v>1</v>
       </c>
       <c r="F25" s="6" t="n">
@@ -6026,7 +6623,7 @@
         <v>250</v>
       </c>
       <c r="H25" s="30" t="n">
-        <f aca="false">Inputs!$E$13</f>
+        <f aca="false">Inputs!$E$14</f>
         <v>1</v>
       </c>
       <c r="I25" s="6" t="n">
@@ -6038,7 +6635,7 @@
         <v>140</v>
       </c>
       <c r="K25" s="30" t="n">
-        <f aca="false">Inputs!$E$14</f>
+        <f aca="false">Inputs!$E$15</f>
         <v>1.09</v>
       </c>
       <c r="L25" s="6" t="n">
@@ -6050,13 +6647,25 @@
         <v>70</v>
       </c>
       <c r="N25" s="30" t="n">
-        <f aca="false">Inputs!$E$16</f>
+        <f aca="false">Inputs!$E$17</f>
         <v>1.28</v>
       </c>
       <c r="O25" s="6" t="n">
         <f aca="false">M25*N25</f>
         <v>89.6</v>
       </c>
+      <c r="P25" s="20" t="n">
+        <f aca="false">'Trial Balances'!I25</f>
+        <v>50</v>
+      </c>
+      <c r="Q25" s="30" t="n">
+        <f aca="false">Inputs!$E$15</f>
+        <v>1.09</v>
+      </c>
+      <c r="R25" s="6" t="n">
+        <f aca="false">P25*Q25</f>
+        <v>54.5</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="n">
@@ -6075,16 +6684,20 @@
       </c>
       <c r="L26" s="8" t="n">
         <f aca="false">-SUM(L6:L25)</f>
-        <v>30.7000000000002</v>
+        <v>30.7000000000001</v>
       </c>
       <c r="O26" s="8" t="n">
         <f aca="false">-SUM(O6:O25)</f>
         <v>-11.9</v>
       </c>
+      <c r="R26" s="8" t="n">
+        <f aca="false">-SUM(R6:R25)</f>
+        <v>12.8999999999999</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="3" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -6103,14 +6716,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:H26"/>
+  <dimension ref="B1:I26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="5" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="5" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6120,35 +6733,38 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="3" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>229</v>
+        <v>241</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6159,7 +6775,7 @@
         <v>27</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E6" s="31" t="n">
         <v>1331.69</v>
@@ -6172,6 +6788,9 @@
       </c>
       <c r="H6" s="31" t="n">
         <v>160</v>
+      </c>
+      <c r="I6" s="31" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6182,7 +6801,7 @@
         <v>25</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E7" s="31" t="n">
         <v>2100</v>
@@ -6195,6 +6814,9 @@
       </c>
       <c r="H7" s="31" t="n">
         <v>250</v>
+      </c>
+      <c r="I7" s="31" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6202,10 +6824,10 @@
         <v>1150</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E8" s="31" t="n">
         <v>540</v>
@@ -6217,6 +6839,9 @@
         <v>0</v>
       </c>
       <c r="H8" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6228,7 +6853,7 @@
         <v>24</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E9" s="31" t="n">
         <v>1500</v>
@@ -6241,6 +6866,9 @@
       </c>
       <c r="H9" s="31" t="n">
         <v>180</v>
+      </c>
+      <c r="I9" s="31" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6251,7 +6879,7 @@
         <v>21</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E10" s="31" t="n">
         <v>6000</v>
@@ -6264,6 +6892,9 @@
       </c>
       <c r="H10" s="31" t="n">
         <v>900</v>
+      </c>
+      <c r="I10" s="31" t="n">
+        <v>700</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6271,10 +6902,10 @@
         <v>1600</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E11" s="31" t="n">
         <v>3580</v>
@@ -6283,9 +6914,12 @@
         <v>600</v>
       </c>
       <c r="G11" s="31" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="H11" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6294,10 +6928,10 @@
         <v>1650</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E12" s="31" t="n">
         <v>1500</v>
@@ -6309,6 +6943,9 @@
         <v>0</v>
       </c>
       <c r="H12" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6320,7 +6957,7 @@
         <v>37</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="E13" s="31" t="n">
         <v>-1700</v>
@@ -6333,6 +6970,9 @@
       </c>
       <c r="H13" s="31" t="n">
         <v>-180</v>
+      </c>
+      <c r="I13" s="31" t="n">
+        <v>-150</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6340,10 +6980,10 @@
         <v>2150</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="E14" s="31" t="n">
         <v>-150</v>
@@ -6355,6 +6995,9 @@
         <v>-500</v>
       </c>
       <c r="H14" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6366,7 +7009,7 @@
         <v>36</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="E15" s="31" t="n">
         <v>-5000</v>
@@ -6375,10 +7018,13 @@
         <v>-1600</v>
       </c>
       <c r="G15" s="31" t="n">
-        <v>-600</v>
+        <v>-1050</v>
       </c>
       <c r="H15" s="31" t="n">
         <v>-300</v>
+      </c>
+      <c r="I15" s="31" t="n">
+        <v>-250</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6389,7 +7035,7 @@
         <v>30</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="E16" s="31" t="n">
         <v>-5000</v>
@@ -6402,6 +7048,9 @@
       </c>
       <c r="H16" s="31" t="n">
         <v>-500</v>
+      </c>
+      <c r="I16" s="31" t="n">
+        <v>-400</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6409,10 +7058,10 @@
         <v>3100</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="E17" s="31" t="n">
         <v>-2800</v>
@@ -6425,6 +7074,9 @@
       </c>
       <c r="H17" s="31" t="n">
         <v>-300</v>
+      </c>
+      <c r="I17" s="31" t="n">
+        <v>-220</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6435,7 +7087,7 @@
         <v>4</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="E18" s="31" t="n">
         <v>-14000</v>
@@ -6448,6 +7100,9 @@
       </c>
       <c r="H18" s="31" t="n">
         <v>-1600</v>
+      </c>
+      <c r="I18" s="31" t="n">
+        <v>-1200</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6455,10 +7110,10 @@
         <v>4050</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="E19" s="31" t="n">
         <v>0</v>
@@ -6470,6 +7125,9 @@
         <v>0</v>
       </c>
       <c r="H19" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6478,10 +7136,10 @@
         <v>4100</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="E20" s="31" t="n">
         <v>-131.69</v>
@@ -6493,6 +7151,9 @@
         <v>0</v>
       </c>
       <c r="H20" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6504,7 +7165,7 @@
         <v>5</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="E21" s="31" t="n">
         <v>7600</v>
@@ -6517,6 +7178,9 @@
       </c>
       <c r="H21" s="31" t="n">
         <v>1000</v>
+      </c>
+      <c r="I21" s="31" t="n">
+        <v>760</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6524,10 +7188,10 @@
         <v>5050</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="E22" s="31" t="n">
         <v>800</v>
@@ -6539,6 +7203,9 @@
         <v>0</v>
       </c>
       <c r="H22" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6550,7 +7217,7 @@
         <v>7</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="E23" s="31" t="n">
         <v>3100</v>
@@ -6563,6 +7230,9 @@
       </c>
       <c r="H23" s="31" t="n">
         <v>300</v>
+      </c>
+      <c r="I23" s="31" t="n">
+        <v>230</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6573,7 +7243,7 @@
         <v>11</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="E24" s="31" t="n">
         <v>280</v>
@@ -6586,6 +7256,9 @@
       </c>
       <c r="H24" s="31" t="n">
         <v>20</v>
+      </c>
+      <c r="I24" s="31" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6596,7 +7269,7 @@
         <v>13</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="E25" s="31" t="n">
         <v>450</v>
@@ -6610,10 +7283,13 @@
       <c r="H25" s="31" t="n">
         <v>70</v>
       </c>
+      <c r="I25" s="31" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="7" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E26" s="8" t="n">
         <f aca="false">SUM(E6:E25)</f>
@@ -6629,6 +7305,10 @@
       </c>
       <c r="H26" s="8" t="n">
         <f aca="false">SUM(H6:H25)</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="8" t="n">
+        <f aca="false">SUM(I6:I25)</f>
         <v>0</v>
       </c>
     </row>
@@ -6648,7 +7328,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:J24"/>
+  <dimension ref="B1:J25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -6670,7 +7350,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6678,44 +7358,44 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
         <v>44</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="E5" s="19" t="s">
         <v>46</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="J5" s="19" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>50</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
@@ -6734,13 +7414,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>55</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>1</v>
@@ -6753,7 +7433,7 @@
       </c>
       <c r="H7" s="31"/>
       <c r="I7" s="26" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="J7" s="33" t="n">
         <f aca="false">E7*J6</f>
@@ -6762,13 +7442,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>60</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>0.8</v>
@@ -6783,7 +7463,7 @@
         <v>460</v>
       </c>
       <c r="I8" s="26" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="J8" s="33" t="n">
         <f aca="false">E8*J6</f>
@@ -6792,13 +7472,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>65</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>0.7</v>
@@ -6813,183 +7493,213 @@
         <v>377</v>
       </c>
       <c r="I9" s="26" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="J9" s="33" t="n">
         <f aca="false">E9*J7</f>
         <v>0.7</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>249</v>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="E10" s="32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F10" s="31" t="n">
+        <v>450</v>
+      </c>
+      <c r="G10" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="H10" s="31" t="n">
+        <v>241</v>
+      </c>
+      <c r="I10" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="J10" s="33" t="n">
+        <f aca="false">E10*J8</f>
+        <v>0.6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D13" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="34" t="n">
-        <v>1</v>
+      <c r="B13" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>244</v>
+        <v>191</v>
       </c>
       <c r="D14" s="34" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="E14" s="34" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="F14" s="34" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>181</v>
+        <v>257</v>
       </c>
       <c r="D15" s="34" t="n">
-        <v>0.2723</v>
+        <v>1.08</v>
       </c>
       <c r="E15" s="34" t="n">
-        <v>0.2723</v>
+        <v>1.09</v>
       </c>
       <c r="F15" s="34" t="n">
-        <v>0.2723</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
-        <v>246</v>
+        <v>190</v>
       </c>
       <c r="D16" s="34" t="n">
+        <v>0.2723</v>
+      </c>
+      <c r="E16" s="34" t="n">
+        <v>0.2723</v>
+      </c>
+      <c r="F16" s="34" t="n">
+        <v>0.2723</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="D17" s="34" t="n">
         <v>1.27</v>
       </c>
-      <c r="E16" s="34" t="n">
+      <c r="E17" s="34" t="n">
         <v>1.28</v>
       </c>
-      <c r="F16" s="34" t="n">
+      <c r="F17" s="34" t="n">
         <v>1.25</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="F19" s="19" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="F20" s="31" t="n">
-        <v>150</v>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="C21" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>241</v>
-      </c>
       <c r="E21" s="5" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="F21" s="31" t="n">
-        <v>540</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="E22" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>241</v>
-      </c>
       <c r="F22" s="31" t="n">
-        <v>800</v>
+        <v>540</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="F23" s="31" t="n">
-        <v>50</v>
+        <v>800</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>176</v>
+        <v>254</v>
       </c>
       <c r="F24" s="31" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="F25" s="31" t="n">
         <v>40</v>
       </c>
     </row>
